--- a/data/input/Low Level Field Detail Design(6).xlsx
+++ b/data/input/Low Level Field Detail Design(6).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgroupcloud.sharepoint.com/teams/CampaignManagementTransformation/Shared Documents/ROI and Attribution/Data Engineering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE7BD825-E682-46FD-8794-23D0D4099FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBCDC2F9-3417-498A-AD9F-9C1048427BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
   </bookViews>
   <sheets>
     <sheet name="objects" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Interaction Types" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Attributes!$A$1:$J$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Attributes!$A$1:$J$173</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Channels!$A$1:$F$20</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -52,7 +52,6 @@
     <author>tc={F565C7A7-7FF2-4D3F-BF6D-DAD651623CF7}</author>
     <author>tc={710AF4BE-211D-4E73-BD3F-C39C02D0E5DC}</author>
     <author>tc={B1C76761-6506-4B3F-A378-69D1147B5870}</author>
-    <author>tc={53BF789D-732F-480E-97B9-73E27DB0995E}</author>
     <author>tc={8497C7DA-1239-4373-88D7-CCD3FD1374B1}</author>
     <author>tc={B341755A-7D9C-4B12-B3E8-F721DABD8A3A}</author>
     <author>tc={0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}</author>
@@ -111,21 +110,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="B60" authorId="5" shapeId="0" xr:uid="{53BF789D-732F-480E-97B9-73E27DB0995E}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    @David Irvine 
-May need to be product group of the Asset like Broadbrand , BT net etc) not Marketing Asset (like bulletin board, pamphlet etc)
-Reply:
-    We are identifying here the product that the marketing asset is aimed at promoting or is containing information about.
-The "Outcome" Product will also be tracked. We need both as they may match or differ.
-Reply:
-    @srini Reports from Base movement reference Product Tower and product Type. These might be equivilent / additional, We need to review, understand the product hierarchy and ensure we are aligned.</t>
-      </text>
-    </comment>
-    <comment ref="B61" authorId="6" shapeId="0" xr:uid="{8497C7DA-1239-4373-88D7-CCD3FD1374B1}">
+    <comment ref="B61" authorId="5" shapeId="0" xr:uid="{8497C7DA-1239-4373-88D7-CCD3FD1374B1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -136,7 +121,7 @@
     See comment on product family</t>
       </text>
     </comment>
-    <comment ref="C98" authorId="7" shapeId="0" xr:uid="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
+    <comment ref="C104" authorId="6" shapeId="0" xr:uid="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -146,7 +131,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="C101" authorId="8" shapeId="0" xr:uid="{0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}">
+    <comment ref="C107" authorId="7" shapeId="0" xr:uid="{0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -157,7 +142,7 @@
     Updated</t>
       </text>
     </comment>
-    <comment ref="C105" authorId="9" shapeId="0" xr:uid="{743A8CEB-662A-4266-9865-AE4208BB8853}">
+    <comment ref="C111" authorId="8" shapeId="0" xr:uid="{743A8CEB-662A-4266-9865-AE4208BB8853}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -173,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="745">
   <si>
     <t>Name</t>
   </si>
@@ -200,6 +185,9 @@
   </si>
   <si>
     <t>generation_order</t>
+  </si>
+  <si>
+    <t>Generate_Rows</t>
   </si>
   <si>
     <t xml:space="preserve">existing consumption project </t>
@@ -261,7 +249,7 @@
 But within Email there wouldn’t be different channels for the different email clients a person may recieve an email with.</t>
   </si>
   <si>
-    <t>n</t>
+    <t>Y</t>
   </si>
   <si>
     <t>Facilitation Tool</t>
@@ -442,9 +430,6 @@
   <si>
     <t>Each row represents a the role a person has with a company.
 The same person may be linked to the same company multiple times with different roles. this would be multiple rows.</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>Orders</t>
@@ -489,6 +474,9 @@
       </rPr>
       <t>Ultimately this should match the current in system opportunity grain.</t>
     </r>
+  </si>
+  <si>
+    <t>n</t>
   </si>
   <si>
     <t>Customer Value Change</t>
@@ -1370,22 +1358,19 @@
     <t>If interaction came from a separate interaction. I.E. click on link -&gt; View Webpage -&gt; Submit Form</t>
   </si>
   <si>
-    <t>Activity</t>
-  </si>
-  <si>
     <t>What was the Activity this interaction is related to.</t>
   </si>
   <si>
     <t>Optional Needs One of person or company</t>
   </si>
   <si>
-    <t>Person Interacted</t>
+    <t>Interacted Person ID</t>
   </si>
   <si>
     <t>Identifies the person that carried out the interaction.</t>
   </si>
   <si>
-    <t>Company Interacted</t>
+    <t>Interacted Company ID</t>
   </si>
   <si>
     <t>Identifies the company that carried out the interaction.</t>
@@ -1406,7 +1391,13 @@
     <t>Which system tracked this interaction</t>
   </si>
   <si>
-    <t>Content</t>
+    <t>Marketing Asset ID</t>
+  </si>
+  <si>
+    <t>Primary key for each unique Marketing Asset</t>
+  </si>
+  <si>
+    <t>Uses Dynamic Content</t>
   </si>
   <si>
     <t>identifies if the content contains dynamic personalisation specific to the audience.</t>
@@ -1430,49 +1421,61 @@
     <t>* Should this differentiate the asset or be on the activity, Or actual a sub Object.</t>
   </si>
   <si>
-    <t>Identifies the product family being promoted by the marketing asset. This could be a link to an external product family table. Not every marketing asset might be specific to a product family, there may be assets that are generic brand awareness / building.</t>
-  </si>
-  <si>
-    <t>Used to match the target product family for a marketing asset with outcomes for the same product family as a potential differentiator for attribution.</t>
-  </si>
-  <si>
-    <t>Allows grouping and comparison of marketing assets by the product family they are promoting.</t>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Links to the product or product family that this asset is promoting.</t>
+  </si>
+  <si>
+    <t>Used to match the target product for a marketing asset with outcomes for the same product family as a potential differentiator for attribution.</t>
+  </si>
+  <si>
+    <t>Allows grouping and comparison of marketing assets by the product they are promoting.</t>
   </si>
   <si>
     <t>Optional</t>
   </si>
   <si>
+    <t>Source Table</t>
+  </si>
+  <si>
+    <t>Identifies the GCP table that this Row is sourced from</t>
+  </si>
+  <si>
+    <t>Source ID Field</t>
+  </si>
+  <si>
+    <t>Identifies the PK field of that table.</t>
+  </si>
+  <si>
+    <t>Source ID</t>
+  </si>
+  <si>
+    <t>The Source Table PK Value.</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Unique Identifier for this order.</t>
+  </si>
+  <si>
+    <t>Unique Friendly name of the order, May be a concatenation of product, Time and company.</t>
+  </si>
+  <si>
+    <t>Which Product Family the product being sold in the order belongs to.</t>
+  </si>
+  <si>
+    <t>String Enum</t>
+  </si>
+  <si>
+    <t>Product Group</t>
+  </si>
+  <si>
+    <t>Which product group the product being sold in the order belongs to.</t>
+  </si>
+  <si>
     <t>Product</t>
-  </si>
-  <si>
-    <t>Identifies the specific product being promoted where know. This could be a link to an external product.  Not every Marketing asset might be specific to a particular product, The data may not be tracked at the right level for all types of assets.</t>
-  </si>
-  <si>
-    <t>Used to match the target product for a marketing asset with outcomes for the same product family as a potential differentiator for attribution.</t>
-  </si>
-  <si>
-    <t>Allows grouping and comparison of marketing assets by the product they are promoting.</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Unique Identifier for this order.</t>
-  </si>
-  <si>
-    <t>Unique Friendly name of the order, May be a concatenation of product, Time and company.</t>
-  </si>
-  <si>
-    <t>Which Product Family the product being sold in the order belongs to.</t>
-  </si>
-  <si>
-    <t>String Enum</t>
-  </si>
-  <si>
-    <t>Product Group</t>
-  </si>
-  <si>
-    <t>Which product group the product being sold in the order belongs to.</t>
   </si>
   <si>
     <t>Which particular product was being sold in the order. *It might be actual we relate the order to a more complex product table depending on how the source data is structured</t>
@@ -1619,96 +1622,111 @@
     <t>Used to limit which people / companies are likely to have been impacted by this activity</t>
   </si>
   <si>
+    <t>Reach Individuals</t>
+  </si>
+  <si>
+    <t>The estimated or actual number of individuals that would have had an opportunity to interact with this activity</t>
+  </si>
+  <si>
+    <t>Combine with the audience size to estimate the likelyhood that anyone in the audience was impacted by this activity.</t>
+  </si>
+  <si>
+    <t>potential Metric for future dashboards that are not currently in scope</t>
+  </si>
+  <si>
+    <t>Reach Companies</t>
+  </si>
+  <si>
+    <t>The estimated or actual number of companies that would have had the opportunity to interact with this activity. * Company Granularity to be determined</t>
+  </si>
+  <si>
+    <t>Identifies the marketing asset that this marketing activity shares</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Identifies if this record is actual part of the control for this campaign, As such wasn't sent the communications * Might be better handled in a different way.</t>
+  </si>
+  <si>
+    <t>Needed to support automating the control cell measurement which is a guardrail for our attribution model. Also Identifies those that for modelling purposes have been excluded so shouldn't have any revenue attributed due to this activity</t>
+  </si>
+  <si>
+    <t>Needed to showcase at a campaign level the control cell vs not for control cell uplift visualisation.</t>
+  </si>
+  <si>
+    <t>Boolean</t>
+  </si>
+  <si>
+    <t>When was the push activity send</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>What is the status of the push activity, I.E. was it Delivered, Part of control cell,…</t>
+  </si>
+  <si>
+    <t>Which marketing asset was sent my marketing activity</t>
+  </si>
+  <si>
+    <t>FK -&gt;Marketing Asset.Marketing Asset ID</t>
+  </si>
+  <si>
+    <t>Campaign ID</t>
+  </si>
+  <si>
+    <t>Which campaign was this activity associated with.</t>
+  </si>
+  <si>
+    <t>FK -&gt; Campaigns.Campaign_ID</t>
+  </si>
+  <si>
+    <t>Targeted Person ID</t>
+  </si>
+  <si>
+    <t>Identifies the person the marketing activity targeted.</t>
+  </si>
+  <si>
+    <t>Targeted Company ID</t>
+  </si>
+  <si>
+    <t>Identified the company that was targeted with the communication.</t>
+  </si>
+  <si>
+    <t>Identified the audience that caused the individual or company to be targeted. This is a foreign key to linking to the audience table.</t>
+  </si>
+  <si>
+    <t>This will be one of the ways that a marketing activity is associated with an person or a company ultimately then an outcome.</t>
+  </si>
+  <si>
+    <t>Used in the audience analysis as a selection of the group of individuals or companies to review for outcome and descriptive charicteristics.</t>
+  </si>
+  <si>
+    <t>System ID</t>
+  </si>
+  <si>
     <t>Which System facilitated this Activity</t>
   </si>
   <si>
-    <t>Reach Individuals</t>
-  </si>
-  <si>
-    <t>The estimated or actual number of individuals that would have had an opportunity to interact with this activity</t>
-  </si>
-  <si>
-    <t>Combine with the audience size to estimate the likelyhood that anyone in the audience was impacted by this activity.</t>
-  </si>
-  <si>
-    <t>potential Metric for future dashboards that are not currently in scope</t>
-  </si>
-  <si>
-    <t>Reach Companies</t>
-  </si>
-  <si>
-    <t>The estimated or actual number of companies that would have had the opportunity to interact with this activity. * Company Granularity to be determined</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Identifies if this record is actual part of the control for this campaign, As such wasn't sent the communications * Might be better handled in a different way.</t>
-  </si>
-  <si>
-    <t>Needed to support automating the control cell measurement which is a guardrail for our attribution model. Also Identifies those that for modelling purposes have been excluded so shouldn't have any revenue attributed due to this activity</t>
-  </si>
-  <si>
-    <t>Needed to showcase at a campaign level the control cell vs not for control cell uplift visualisation.</t>
-  </si>
-  <si>
-    <t>Boolean</t>
-  </si>
-  <si>
-    <t>When was the push activity send</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>What is the status of the push activity, I.E. was it Delivered, Part of control cell,…</t>
-  </si>
-  <si>
-    <t>Marketing Asset</t>
-  </si>
-  <si>
-    <t>Which asset was sent my marketing activity</t>
-  </si>
-  <si>
-    <t>Campaign</t>
-  </si>
-  <si>
-    <t>Which campaign was this activity associated with.</t>
-  </si>
-  <si>
-    <t>Person Targeted</t>
-  </si>
-  <si>
-    <t>Identifies the person the marketing activity targeted.</t>
-  </si>
-  <si>
-    <t>Company Targeted</t>
-  </si>
-  <si>
-    <t>Identified the company that was targeted with the communication.</t>
-  </si>
-  <si>
-    <t>Identified the audience that caused the individual or company to be targeted. This is a foreign key to linking to the audience table.</t>
-  </si>
-  <si>
-    <t>This will be one of the ways that a marketing activity is associated with an person or a company ultimately then an outcome.</t>
-  </si>
-  <si>
-    <t>Used in the audience analysis as a selection of the group of individuals or companies to review for outcome and descriptive charicteristics.</t>
-  </si>
-  <si>
-    <t>System ID</t>
+    <t>Name of the tool</t>
   </si>
   <si>
     <t>Owner</t>
   </si>
   <si>
+    <t>The BT team member that is responsible for this tool</t>
+  </si>
+  <si>
     <t>Yearly Cost</t>
   </si>
   <si>
     <t>* We may want a more compex tracking method later. This should be the cost that is not campaign specific. I.E. General License and platform maintainance costs.</t>
   </si>
   <si>
+    <t>Currency Pounds</t>
+  </si>
+  <si>
     <t>Person_ID</t>
   </si>
   <si>
@@ -1718,27 +1736,9 @@
     <t>Persona</t>
   </si>
   <si>
-    <t>Source Table</t>
-  </si>
-  <si>
-    <t>Identifies the GCP table that this Row is sourced from</t>
-  </si>
-  <si>
     <t>GCP Table Reference</t>
   </si>
   <si>
-    <t>Source ID Field</t>
-  </si>
-  <si>
-    <t>Identifies the PK field of that table.</t>
-  </si>
-  <si>
-    <t>Source ID</t>
-  </si>
-  <si>
-    <t>The Source Table PK Value.</t>
-  </si>
-  <si>
     <t>FK -&gt; Source_Table. Source_ID_Field</t>
   </si>
   <si>
@@ -1767,9 +1767,6 @@
   </si>
   <si>
     <t>Parent_Company_ID</t>
-  </si>
-  <si>
-    <t>FK -&gt; Company.Parent_Company_ID</t>
   </si>
   <si>
     <t>Company Market Channel</t>
@@ -1907,9 +1904,6 @@
     <t>Reference to the company that these products and the changes are associated with.</t>
   </si>
   <si>
-    <t>Product ID</t>
-  </si>
-  <si>
     <t>Sythentic ID that represents the Unified Product ID.</t>
   </si>
   <si>
@@ -1968,6 +1962,18 @@
   </si>
   <si>
     <t>Month Number within BT Financial Year.</t>
+  </si>
+  <si>
+    <t>is_weekend</t>
+  </si>
+  <si>
+    <t>is_holiday</t>
+  </si>
+  <si>
+    <t>Tool_id</t>
+  </si>
+  <si>
+    <t>Sythentic ID given to head tool</t>
   </si>
   <si>
     <t>Interaction</t>
@@ -6388,15 +6394,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D396AB2F-F9BE-4F78-8BC5-51EC98BD60B1}" name="Table1" displayName="Table1" ref="A1:J164" totalsRowShown="0">
-  <autoFilter ref="A1:J164" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Person Company Role"/>
-        <filter val="(NonBlanks)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D396AB2F-F9BE-4F78-8BC5-51EC98BD60B1}" name="Table1" displayName="Table1" ref="A1:J173" totalsRowShown="0">
+  <autoFilter ref="A1:J173" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{FA10E4DE-EA14-4D6D-B2DE-B36300D4BF76}" name="Object" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{32E1B4A0-4AC4-478E-B858-9CDAC148562B}" name="Name"/>
@@ -6776,21 +6775,6 @@
       <mention mentionpersonId="{2D30A5D6-A763-4ABB-81AE-1F40D026C227}" mentionId="{09FFD19E-344E-45A8-85D7-6A39558E8131}" startIndex="0" length="13"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="B60" dT="2025-03-06T16:38:19.89" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{53BF789D-732F-480E-97B9-73E27DB0995E}">
-    <text xml:space="preserve">@David Irvine 
-May need to be product group of the Asset like Broadbrand , BT net etc) not Marketing Asset (like bulletin board, pamphlet etc)
-</text>
-    <mentions>
-      <mention mentionpersonId="{2D30A5D6-A763-4ABB-81AE-1F40D026C227}" mentionId="{9B74DC43-1EEC-4964-993A-1E484285F1E1}" startIndex="0" length="13"/>
-    </mentions>
-  </threadedComment>
-  <threadedComment ref="B60" dT="2025-03-07T22:24:19.95" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{4D3A114C-CBF1-47E2-B039-07A79D6B6656}" parentId="{53BF789D-732F-480E-97B9-73E27DB0995E}">
-    <text>We are identifying here the product that the marketing asset is aimed at promoting or is containing information about.
-The "Outcome" Product will also be tracked. We need both as they may match or differ.</text>
-  </threadedComment>
-  <threadedComment ref="B60" dT="2025-03-07T22:29:28.28" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{35DBA43B-71E3-45C9-B42F-B90422D01B7F}" parentId="{53BF789D-732F-480E-97B9-73E27DB0995E}">
-    <text>@srini Reports from Base movement reference Product Tower and product Type. These might be equivilent / additional, We need to review, understand the product hierarchy and ensure we are aligned.</text>
-  </threadedComment>
   <threadedComment ref="B61" dT="2025-03-06T16:38:33.85" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{8497C7DA-1239-4373-88D7-CCD3FD1374B1}">
     <text xml:space="preserve">@David Irvine 
 May need to be product like Broadbrand , BT net etc) not Marketing Asset (like bulletin board, pamphlet etc)
@@ -6802,7 +6786,7 @@
   <threadedComment ref="B61" dT="2025-03-07T22:24:32.38" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{3477900C-1235-4AD9-B6B9-B36EBE216470}" parentId="{8497C7DA-1239-4373-88D7-CCD3FD1374B1}">
     <text>See comment on product family</text>
   </threadedComment>
-  <threadedComment ref="C98" dT="2025-03-06T16:36:49.39" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
+  <threadedComment ref="C104" dT="2025-03-06T16:36:49.39" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
     <text xml:space="preserve">@David Irvine 
 example please . is it a available field in existing Marketo Activities?
 </text>
@@ -6810,7 +6794,7 @@
       <mention mentionpersonId="{2D30A5D6-A763-4ABB-81AE-1F40D026C227}" mentionId="{40C38E33-B939-49D4-8B2E-6D818BD6F889}" startIndex="0" length="13"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="C101" dT="2025-03-06T16:37:15.29" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}">
+  <threadedComment ref="C107" dT="2025-03-06T16:37:15.29" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}">
     <text xml:space="preserve">@David Irvine 
 hope its Marketing Asset - bulletin etc
 </text>
@@ -6818,10 +6802,10 @@
       <mention mentionpersonId="{2D30A5D6-A763-4ABB-81AE-1F40D026C227}" mentionId="{A3E4CE78-E2D0-4F35-8130-361426FEAED0}" startIndex="0" length="13"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="C101" dT="2025-03-07T22:07:31.32" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{5B19FF75-413F-42F1-981E-51C52DF1C444}" parentId="{0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}">
+  <threadedComment ref="C107" dT="2025-03-07T22:07:31.32" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{5B19FF75-413F-42F1-981E-51C52DF1C444}" parentId="{0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}">
     <text>Updated</text>
   </threadedComment>
-  <threadedComment ref="C105" dT="2025-03-06T16:37:38.16" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{743A8CEB-662A-4266-9865-AE4208BB8853}">
+  <threadedComment ref="C111" dT="2025-03-06T16:37:38.16" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{743A8CEB-662A-4266-9865-AE4208BB8853}">
     <text xml:space="preserve">@David Irvine 
 need some example please . Audience will be part of contact(person) or company (customer)
 </text>
@@ -6829,7 +6813,7 @@
       <mention mentionpersonId="{2D30A5D6-A763-4ABB-81AE-1F40D026C227}" mentionId="{98A2319B-9179-4D17-8B08-096AE9402B5D}" startIndex="0" length="13"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="C105" dT="2025-03-07T22:08:12.74" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{7ECB8EFC-8B65-4BC1-894D-08FDEBC4BB3E}" parentId="{743A8CEB-662A-4266-9865-AE4208BB8853}">
+  <threadedComment ref="C111" dT="2025-03-07T22:08:12.74" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{7ECB8EFC-8B65-4BC1-894D-08FDEBC4BB3E}" parentId="{743A8CEB-662A-4266-9865-AE4208BB8853}">
     <text>See the audience table and description given lower in this table and in the higher level object definitions.</text>
   </threadedComment>
 </ThreadedComments>
@@ -6846,7 +6830,9 @@
     <col min="4" max="4" width="49.5703125" style="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.140625" style="16" customWidth="1"/>
     <col min="6" max="6" width="158.42578125" style="16" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="28" customWidth="1"/>
     <col min="12" max="12" width="31.85546875" customWidth="1"/>
     <col min="13" max="13" width="22.28515625" customWidth="1"/>
@@ -6880,280 +6866,307 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="90">
       <c r="A2" s="34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2">
         <f>COUNTIF(Attributes!A:A,objects!A2)</f>
         <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>30</v>
+      </c>
       <c r="L2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="75">
       <c r="A3" s="35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <f>COUNTIF(Attributes!A:A,objects!A3)</f>
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="75">
       <c r="A4" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <f>COUNTIF(Attributes!A:A,objects!A4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
+      <c r="J4">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:13" ht="60">
       <c r="A5" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5">
         <f>COUNTIF(Attributes!A:A,objects!A5)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
+      <c r="J5">
+        <v>300</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="60">
       <c r="A6" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <f>COUNTIF(Attributes!A:A,objects!A6)</f>
         <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="75">
       <c r="A7" s="34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="34"/>
       <c r="C7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7">
         <f>COUNTIF(Attributes!A:A,objects!A7)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7">
         <v>15</v>
       </c>
+      <c r="J7">
+        <v>10000</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="60">
       <c r="A8" s="34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" s="34"/>
       <c r="C8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8">
         <f>COUNTIF(Attributes!A:A,objects!A8)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8">
         <v>16</v>
       </c>
+      <c r="J8">
+        <v>10000</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="105">
       <c r="A9" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <f>COUNTIF(Attributes!A:A,objects!A9)</f>
         <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I9">
         <v>17</v>
       </c>
+      <c r="J9">
+        <v>500000</v>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="30">
       <c r="A10" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <f>COUNTIF(Attributes!A:A,objects!A10)</f>
         <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I10">
         <v>18</v>
@@ -7161,89 +7174,95 @@
     </row>
     <row r="11" spans="1:13" ht="75">
       <c r="A11" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11">
         <f>COUNTIF(Attributes!A:A,objects!A11)</f>
         <v>5</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I11">
         <v>7</v>
       </c>
+      <c r="J11">
+        <v>5000</v>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="120">
       <c r="A12" s="34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G12">
         <f>COUNTIF(Attributes!A:A,objects!A12)</f>
         <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12">
         <v>6</v>
       </c>
+      <c r="J12">
+        <v>3000</v>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="60">
       <c r="A13" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13">
         <f>COUNTIF(Attributes!A:A,objects!A13)</f>
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="I13">
         <v>8</v>
@@ -7254,7 +7273,7 @@
         <v>80</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>81</v>
@@ -7273,10 +7292,13 @@
         <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14">
         <v>9</v>
+      </c>
+      <c r="J14">
+        <v>7000</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="105">
@@ -7284,7 +7306,7 @@
         <v>85</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>86</v>
@@ -7303,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -7311,13 +7333,13 @@
     </row>
     <row r="16" spans="1:13" ht="60">
       <c r="A16" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>82</v>
@@ -7326,14 +7348,14 @@
         <v>83</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G16">
         <f>COUNTIF(Attributes!A:A,objects!A16)</f>
         <v>12</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="I16">
         <v>11</v>
@@ -7341,13 +7363,13 @@
     </row>
     <row r="17" spans="1:9" ht="45">
       <c r="A17" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>82</v>
@@ -7356,14 +7378,14 @@
         <v>83</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17">
         <f>COUNTIF(Attributes!A:A,objects!A17)</f>
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="I17">
         <v>12</v>
@@ -7371,29 +7393,29 @@
     </row>
     <row r="18" spans="1:9" ht="60">
       <c r="A18" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G18">
         <f>COUNTIF(Attributes!A:A,objects!A18)</f>
         <v>4</v>
       </c>
       <c r="H18" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="I18">
         <v>14</v>
@@ -7401,29 +7423,29 @@
     </row>
     <row r="19" spans="1:9" ht="75">
       <c r="A19" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G19">
         <f>COUNTIF(Attributes!A:A,objects!A19)</f>
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="I19">
         <v>13</v>
@@ -7431,25 +7453,25 @@
     </row>
     <row r="20" spans="1:9" ht="45">
       <c r="A20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -7457,25 +7479,25 @@
     </row>
     <row r="21" spans="1:9" ht="45">
       <c r="A21" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -7488,7 +7510,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:J173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -7505,7 +7527,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -7514,766 +7536,769 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C2" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="F6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="F8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="107.25" customHeight="1">
+      <c r="A9" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="F9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="F10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" t="s">
         <v>125</v>
       </c>
-      <c r="F2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" hidden="1">
-      <c r="A3" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="F3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" hidden="1">
-      <c r="A4" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" hidden="1">
-      <c r="A5" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="F5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" hidden="1">
-      <c r="A6" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="F6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" hidden="1">
-      <c r="A7" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="F7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" hidden="1">
-      <c r="A8" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="F8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="107.25" hidden="1" customHeight="1">
-      <c r="A9" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="F9" t="s">
-        <v>135</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" hidden="1">
-      <c r="A10" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="F10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" hidden="1">
-      <c r="A11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" t="s">
-        <v>152</v>
-      </c>
-      <c r="F11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" hidden="1">
-      <c r="A12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" t="s">
-        <v>124</v>
-      </c>
       <c r="C12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F12" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" hidden="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" t="s">
         <v>156</v>
       </c>
-      <c r="C13" t="s">
-        <v>157</v>
-      </c>
-      <c r="F13" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" hidden="1">
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G14" s="16">
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
         <v>162</v>
       </c>
-      <c r="F15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" hidden="1">
-      <c r="A16" t="s">
-        <v>161</v>
-      </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G16" s="16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" t="s">
+        <v>169</v>
+      </c>
+      <c r="F17" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F18" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="45">
+      <c r="A20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" t="s">
+        <v>181</v>
+      </c>
+      <c r="F21" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" t="s">
+        <v>183</v>
+      </c>
+      <c r="C22" t="s">
+        <v>184</v>
+      </c>
+      <c r="F22" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" hidden="1">
-      <c r="A17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B17" t="s">
-        <v>167</v>
-      </c>
-      <c r="C17" t="s">
-        <v>168</v>
-      </c>
-      <c r="F17" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" hidden="1">
-      <c r="A18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="G22" s="16" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" t="s">
+        <v>187</v>
+      </c>
+      <c r="F23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" t="s">
+        <v>189</v>
+      </c>
+      <c r="F24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" t="s">
+        <v>191</v>
+      </c>
+      <c r="F25" t="s">
         <v>170</v>
       </c>
-      <c r="C18" t="s">
-        <v>171</v>
-      </c>
-      <c r="F18" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" hidden="1">
-      <c r="A19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C19" t="s">
-        <v>173</v>
-      </c>
-      <c r="F19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="45" hidden="1">
-      <c r="A20" t="s">
-        <v>161</v>
-      </c>
-      <c r="B20" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="F20" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" hidden="1">
-      <c r="A21" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" t="s">
-        <v>179</v>
-      </c>
-      <c r="C21" t="s">
-        <v>180</v>
-      </c>
-      <c r="F21" t="s">
-        <v>135</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" hidden="1">
-      <c r="A22" t="s">
-        <v>161</v>
-      </c>
-      <c r="B22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F22" t="s">
-        <v>165</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" hidden="1">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" t="s">
-        <v>186</v>
-      </c>
-      <c r="F23" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" t="s">
-        <v>187</v>
-      </c>
-      <c r="C24" t="s">
-        <v>188</v>
-      </c>
-      <c r="F24" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" hidden="1">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" t="s">
-        <v>189</v>
-      </c>
-      <c r="C25" t="s">
-        <v>190</v>
-      </c>
-      <c r="F25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" hidden="1">
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F26" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" hidden="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C27" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F27" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" hidden="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E28" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" hidden="1">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F29" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" hidden="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D30" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E30" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" hidden="1">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C31" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" hidden="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C32" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" hidden="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C33" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D33" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E33" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="60" hidden="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="60">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C34" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D34" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E34" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" hidden="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C35" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" hidden="1">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" hidden="1">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" t="s">
         <v>225</v>
       </c>
-      <c r="C37" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" hidden="1">
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F38" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="135" hidden="1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="135">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C39" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" hidden="1">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" hidden="1">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D41" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F41" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" hidden="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
         <v>0</v>
       </c>
       <c r="C42" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E42" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F42" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="45" hidden="1">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="45">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B43" t="s">
+        <v>240</v>
+      </c>
+      <c r="C43" t="s">
+        <v>241</v>
+      </c>
+      <c r="E43" t="s">
         <v>239</v>
       </c>
-      <c r="C43" t="s">
-        <v>240</v>
-      </c>
-      <c r="E43" t="s">
-        <v>238</v>
-      </c>
       <c r="F43" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G43" s="16" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="75">
+      <c r="A44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" t="s">
+        <v>244</v>
+      </c>
+      <c r="C44" t="s">
+        <v>245</v>
+      </c>
+      <c r="F44" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="75" hidden="1">
-      <c r="A44" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" t="s">
-        <v>243</v>
-      </c>
-      <c r="C44" t="s">
-        <v>244</v>
-      </c>
-      <c r="F44" t="s">
-        <v>241</v>
-      </c>
       <c r="G44" s="16" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="45" hidden="1">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="45">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C45" t="s">
+        <v>248</v>
+      </c>
+      <c r="F45" t="s">
+        <v>242</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" t="s">
+        <v>250</v>
+      </c>
+      <c r="C46" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" t="s">
         <v>247</v>
       </c>
-      <c r="F45" t="s">
-        <v>241</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" hidden="1">
-      <c r="A46" t="s">
-        <v>51</v>
-      </c>
-      <c r="B46" t="s">
-        <v>249</v>
-      </c>
-      <c r="C46" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" hidden="1">
-      <c r="A47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B47" t="s">
-        <v>246</v>
-      </c>
       <c r="C47" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" hidden="1">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C48" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="27" hidden="1">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="27">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C49" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F49" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" hidden="1">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C50" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" hidden="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>259</v>
+        <v>128</v>
       </c>
       <c r="C51" t="s">
         <v>260</v>
       </c>
+      <c r="F51" t="s">
+        <v>130</v>
+      </c>
       <c r="J51" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
         <v>262</v>
@@ -8281,13 +8306,16 @@
       <c r="C52" t="s">
         <v>263</v>
       </c>
+      <c r="F52" t="s">
+        <v>145</v>
+      </c>
       <c r="J52" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1">
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" t="s">
         <v>264</v>
@@ -8295,10 +8323,13 @@
       <c r="C53" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" hidden="1">
+      <c r="F53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
         <v>266</v>
@@ -8310,9 +8341,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B55" t="s">
         <v>269</v>
@@ -8321,20 +8352,20 @@
         <v>270</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1">
-      <c r="A56" s="4" t="s">
-        <v>32</v>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>33</v>
       </c>
       <c r="B56" t="s">
         <v>271</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1">
+    <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
         <v>273</v>
@@ -8343,114 +8374,108 @@
         <v>274</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1">
+    <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
+        <v>275</v>
+      </c>
+      <c r="C58" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" t="s">
         <v>0</v>
       </c>
-      <c r="C58" t="s">
-        <v>275</v>
-      </c>
-      <c r="D58" t="s">
-        <v>213</v>
-      </c>
-      <c r="E58" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" hidden="1">
-      <c r="A59" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>277</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
+        <v>214</v>
+      </c>
+      <c r="E59" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="60" hidden="1">
+    <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>226</v>
-      </c>
-      <c r="C60" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="C60" t="s">
         <v>280</v>
       </c>
-      <c r="E60" s="6" t="s">
+    </row>
+    <row r="61" spans="1:10" ht="57.75">
+      <c r="A61" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" t="s">
         <v>281</v>
       </c>
-      <c r="J60" t="s">
+      <c r="C61" s="6" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" ht="60" hidden="1">
-      <c r="A61" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B61" t="s">
+      <c r="D61" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="E61" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="F61" t="s">
+        <v>229</v>
+      </c>
+      <c r="J61" t="s">
         <v>285</v>
       </c>
-      <c r="E61" s="6" t="s">
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B62" t="s">
         <v>286</v>
       </c>
-      <c r="J61" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" hidden="1">
-      <c r="A62" t="s">
-        <v>80</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="C62" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" hidden="1">
-      <c r="A63" t="s">
-        <v>80</v>
-      </c>
-      <c r="B63" t="s">
-        <v>0</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="J63" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" hidden="1">
-      <c r="A64" t="s">
-        <v>80</v>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>226</v>
-      </c>
-      <c r="C64" t="s">
         <v>290</v>
       </c>
-      <c r="F64" t="s">
+      <c r="C64" s="1" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" hidden="1">
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
         <v>80</v>
       </c>
@@ -8460,1189 +8485,1340 @@
       <c r="C65" t="s">
         <v>293</v>
       </c>
-      <c r="F65" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" hidden="1">
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
         <v>80</v>
       </c>
       <c r="B66" t="s">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="C66" t="s">
         <v>294</v>
       </c>
-      <c r="F66" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" hidden="1">
+      <c r="J66" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
         <v>80</v>
       </c>
       <c r="B67" t="s">
+        <v>227</v>
+      </c>
+      <c r="C67" t="s">
         <v>295</v>
       </c>
-      <c r="C67" t="s">
+      <c r="F67" t="s">
         <v>296</v>
       </c>
-      <c r="F67" t="s">
-        <v>291</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="45" hidden="1">
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
         <v>80</v>
       </c>
       <c r="B68" t="s">
+        <v>297</v>
+      </c>
+      <c r="C68" t="s">
         <v>298</v>
       </c>
-      <c r="C68" t="s">
-        <v>299</v>
-      </c>
       <c r="F68" t="s">
-        <v>291</v>
-      </c>
-      <c r="G68" s="16" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" hidden="1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
         <v>80</v>
       </c>
       <c r="B69" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C69" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" hidden="1">
+        <v>300</v>
+      </c>
+      <c r="F69" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
         <v>80</v>
       </c>
       <c r="B70" t="s">
+        <v>301</v>
+      </c>
+      <c r="C70" t="s">
+        <v>302</v>
+      </c>
+      <c r="F70" t="s">
+        <v>296</v>
+      </c>
+      <c r="G70" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="C70" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" hidden="1">
+    </row>
+    <row r="71" spans="1:10" ht="45">
       <c r="A71" t="s">
         <v>80</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" t="s">
+        <v>304</v>
+      </c>
+      <c r="C71" t="s">
         <v>305</v>
       </c>
-      <c r="C71"/>
-    </row>
-    <row r="72" spans="1:10" hidden="1">
+      <c r="F71" t="s">
+        <v>296</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
         <v>80</v>
       </c>
-      <c r="B72" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C72"/>
-    </row>
-    <row r="73" spans="1:10" hidden="1">
+      <c r="B72" t="s">
+        <v>307</v>
+      </c>
+      <c r="C72" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C73"/>
-    </row>
-    <row r="74" spans="1:10" hidden="1">
+      <c r="B73" t="s">
+        <v>309</v>
+      </c>
+      <c r="C73" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
         <v>80</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C74"/>
     </row>
-    <row r="75" spans="1:10" hidden="1">
-      <c r="A75" s="4" t="s">
+    <row r="75" spans="1:10">
+      <c r="A75" t="s">
         <v>80</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C75"/>
     </row>
-    <row r="76" spans="1:10" hidden="1">
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
         <v>80</v>
       </c>
-      <c r="B76" t="s">
-        <v>68</v>
-      </c>
-      <c r="C76" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" hidden="1">
-      <c r="A77" s="4" t="s">
+      <c r="B76" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C76"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="F77" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" hidden="1">
-      <c r="A78" t="s">
+        <v>314</v>
+      </c>
+      <c r="C77"/>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B78" t="s">
-        <v>313</v>
-      </c>
-      <c r="C78" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" hidden="1">
+      <c r="B78" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C78"/>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>315</v>
-      </c>
-      <c r="C79" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C79" t="s">
         <v>316</v>
       </c>
       <c r="F79" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" hidden="1">
-      <c r="A80" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="4" t="s">
         <v>318</v>
       </c>
       <c r="F80" t="s">
-        <v>319</v>
-      </c>
-      <c r="J80" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" hidden="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" t="s">
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>319</v>
+      </c>
+      <c r="C81" t="s">
         <v>320</v>
       </c>
-      <c r="C81" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" hidden="1">
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" t="s">
         <v>80</v>
       </c>
       <c r="B82" t="s">
+        <v>321</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C82" t="s">
+      <c r="F82" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" t="s">
+        <v>80</v>
+      </c>
+      <c r="B83" t="s">
         <v>323</v>
       </c>
-      <c r="F82" t="s">
+      <c r="C83" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" hidden="1">
-      <c r="A83" s="4" t="s">
+      <c r="F83" t="s">
+        <v>325</v>
+      </c>
+      <c r="J83" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" t="s">
         <v>80</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="C83" s="4" t="s">
+      <c r="B84" t="s">
         <v>326</v>
       </c>
-      <c r="J83" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" hidden="1">
-      <c r="A84" s="4" t="s">
+      <c r="C84" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" t="s">
         <v>80</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C84" s="4" t="s">
+      <c r="B85" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" hidden="1">
-      <c r="A85" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B85" s="4" t="s">
+      <c r="C85" t="s">
         <v>329</v>
       </c>
-      <c r="C85" s="4"/>
-    </row>
-    <row r="86" spans="1:10" hidden="1">
+      <c r="F85" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" hidden="1">
+        <v>332</v>
+      </c>
+      <c r="J86" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" hidden="1">
-      <c r="A88" t="s">
-        <v>46</v>
-      </c>
-      <c r="B88" t="s">
-        <v>287</v>
-      </c>
-      <c r="C88" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1">
-      <c r="A89" t="s">
-        <v>46</v>
-      </c>
-      <c r="B89" t="s">
+    <row r="88" spans="1:10">
+      <c r="A88" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C88" s="4"/>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" t="s">
+        <v>47</v>
+      </c>
+      <c r="B91" t="s">
+        <v>292</v>
+      </c>
+      <c r="C91" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" t="s">
+        <v>47</v>
+      </c>
+      <c r="B92" t="s">
         <v>0</v>
       </c>
-      <c r="C89" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" hidden="1">
-      <c r="A90" t="s">
-        <v>46</v>
-      </c>
-      <c r="B90" t="s">
-        <v>191</v>
-      </c>
-      <c r="C90" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" hidden="1">
-      <c r="A91" t="s">
-        <v>46</v>
-      </c>
-      <c r="B91" t="s">
-        <v>193</v>
-      </c>
-      <c r="C91" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" hidden="1">
-      <c r="A92" t="s">
-        <v>46</v>
-      </c>
-      <c r="B92" t="s">
-        <v>338</v>
-      </c>
       <c r="C92" t="s">
-        <v>339</v>
-      </c>
-      <c r="D92" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" hidden="1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="C93" t="s">
-        <v>341</v>
-      </c>
-      <c r="D93" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" hidden="1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>342</v>
+        <v>194</v>
       </c>
       <c r="C94" t="s">
         <v>343</v>
       </c>
-      <c r="D94" t="s">
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" t="s">
+        <v>47</v>
+      </c>
+      <c r="B95" t="s">
         <v>344</v>
       </c>
-      <c r="E94" t="s">
+      <c r="C95" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" hidden="1">
-      <c r="A95" t="s">
-        <v>46</v>
-      </c>
-      <c r="B95" t="s">
+      <c r="D95" t="s">
         <v>346</v>
       </c>
-      <c r="C95" t="s">
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" t="s">
+        <v>47</v>
+      </c>
+      <c r="B96" t="s">
+        <v>286</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>47</v>
+      </c>
+      <c r="B97" t="s">
+        <v>288</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>47</v>
+      </c>
+      <c r="B98" t="s">
+        <v>290</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>47</v>
+      </c>
+      <c r="B99" t="s">
         <v>347</v>
       </c>
-      <c r="D95" t="s">
+      <c r="C99" t="s">
+        <v>348</v>
+      </c>
+      <c r="D99" t="s">
+        <v>349</v>
+      </c>
+      <c r="E99" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>47</v>
+      </c>
+      <c r="B100" t="s">
+        <v>351</v>
+      </c>
+      <c r="C100" t="s">
+        <v>352</v>
+      </c>
+      <c r="D100" t="s">
+        <v>349</v>
+      </c>
+      <c r="E100" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>47</v>
+      </c>
+      <c r="B101" t="s">
+        <v>271</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>42</v>
+      </c>
+      <c r="B102" t="s">
+        <v>292</v>
+      </c>
+      <c r="C102" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>42</v>
+      </c>
+      <c r="B103" t="s">
+        <v>0</v>
+      </c>
+      <c r="C103" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="105">
+      <c r="A104" t="s">
+        <v>42</v>
+      </c>
+      <c r="B104" t="s">
+        <v>354</v>
+      </c>
+      <c r="C104" t="s">
+        <v>355</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="F104" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>42</v>
+      </c>
+      <c r="B105" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>42</v>
+      </c>
+      <c r="B106" t="s">
+        <v>360</v>
+      </c>
+      <c r="C106" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>42</v>
+      </c>
+      <c r="B107" t="s">
+        <v>271</v>
+      </c>
+      <c r="C107" t="s">
+        <v>362</v>
+      </c>
+      <c r="F107" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>42</v>
+      </c>
+      <c r="B108" t="s">
+        <v>364</v>
+      </c>
+      <c r="C108" t="s">
+        <v>365</v>
+      </c>
+      <c r="F108" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>42</v>
+      </c>
+      <c r="B109" t="s">
+        <v>367</v>
+      </c>
+      <c r="C109" t="s">
+        <v>368</v>
+      </c>
+      <c r="F109" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>42</v>
+      </c>
+      <c r="B110" t="s">
+        <v>369</v>
+      </c>
+      <c r="C110" t="s">
+        <v>370</v>
+      </c>
+      <c r="F110" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="60">
+      <c r="A111" t="s">
+        <v>42</v>
+      </c>
+      <c r="B111" t="s">
         <v>344</v>
       </c>
-      <c r="E95" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" hidden="1">
-      <c r="A96" t="s">
-        <v>41</v>
-      </c>
-      <c r="B96" t="s">
+      <c r="C111" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>42</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C112" t="s">
+        <v>375</v>
+      </c>
+      <c r="D112" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" t="s">
+        <v>42</v>
+      </c>
+      <c r="B113" t="s">
+        <v>286</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C96" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" hidden="1">
-      <c r="A97" t="s">
-        <v>41</v>
-      </c>
-      <c r="B97" t="s">
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" t="s">
+        <v>42</v>
+      </c>
+      <c r="B114" t="s">
+        <v>288</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" t="s">
+        <v>42</v>
+      </c>
+      <c r="B115" t="s">
+        <v>290</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" t="s">
+        <v>28</v>
+      </c>
+      <c r="B116" t="s">
         <v>0</v>
       </c>
-      <c r="C97" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="105" hidden="1">
-      <c r="A98" t="s">
-        <v>41</v>
-      </c>
-      <c r="B98" t="s">
-        <v>348</v>
-      </c>
-      <c r="C98" t="s">
-        <v>349</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="F98" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" hidden="1">
-      <c r="A99" t="s">
-        <v>41</v>
-      </c>
-      <c r="B99" t="s">
-        <v>169</v>
-      </c>
-      <c r="C99" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" hidden="1">
-      <c r="A100" t="s">
-        <v>41</v>
-      </c>
-      <c r="B100" t="s">
-        <v>354</v>
-      </c>
-      <c r="C100" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" hidden="1">
-      <c r="A101" t="s">
-        <v>41</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C101" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" hidden="1">
-      <c r="A102" t="s">
-        <v>41</v>
-      </c>
-      <c r="B102" t="s">
-        <v>358</v>
-      </c>
-      <c r="C102" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" hidden="1">
-      <c r="A103" t="s">
-        <v>41</v>
-      </c>
-      <c r="B103" t="s">
-        <v>360</v>
-      </c>
-      <c r="C103" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" hidden="1">
-      <c r="A104" t="s">
-        <v>41</v>
-      </c>
-      <c r="B104" t="s">
-        <v>362</v>
-      </c>
-      <c r="C104" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="60" hidden="1">
-      <c r="A105" t="s">
-        <v>41</v>
-      </c>
-      <c r="B105" t="s">
-        <v>338</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" hidden="1">
-      <c r="A106" t="s">
-        <v>41</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C106" t="s">
-        <v>341</v>
-      </c>
-      <c r="D106" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" hidden="1">
-      <c r="C107"/>
-    </row>
-    <row r="108" spans="1:6" hidden="1">
-      <c r="C108"/>
-    </row>
-    <row r="109" spans="1:6" hidden="1">
-      <c r="A109" t="s">
-        <v>27</v>
-      </c>
-      <c r="B109" t="s">
-        <v>0</v>
-      </c>
-      <c r="C109"/>
-    </row>
-    <row r="110" spans="1:6" hidden="1">
-      <c r="A110" t="s">
-        <v>27</v>
-      </c>
-      <c r="B110" t="s">
-        <v>368</v>
-      </c>
-      <c r="C110"/>
-    </row>
-    <row r="111" spans="1:6" hidden="1">
-      <c r="A111" t="s">
-        <v>27</v>
-      </c>
-      <c r="B111" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" hidden="1">
-      <c r="A112" t="s">
-        <v>63</v>
-      </c>
-      <c r="B112" t="s">
-        <v>371</v>
-      </c>
-      <c r="C112" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" hidden="1">
-      <c r="A113" t="s">
-        <v>63</v>
-      </c>
-      <c r="B113" t="s">
-        <v>373</v>
-      </c>
-      <c r="C113"/>
-    </row>
-    <row r="114" spans="1:10" hidden="1">
-      <c r="A114" t="s">
-        <v>63</v>
-      </c>
-      <c r="B114" t="s">
-        <v>374</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="C116" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" hidden="1">
-      <c r="A115" t="s">
-        <v>63</v>
-      </c>
-      <c r="B115" t="s">
+      <c r="F116" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" t="s">
+        <v>28</v>
+      </c>
+      <c r="B117" t="s">
         <v>377</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C117" t="s">
         <v>378</v>
       </c>
-      <c r="F115" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" hidden="1">
-      <c r="A116" t="s">
-        <v>63</v>
-      </c>
-      <c r="B116" t="s">
-        <v>379</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="F116" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" hidden="1">
-      <c r="B117" t="s">
-        <v>382</v>
-      </c>
-      <c r="C117" t="s">
-        <v>383</v>
+      <c r="F117" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="118" spans="1:10">
       <c r="A118" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="B118" t="s">
-        <v>142</v>
-      </c>
-      <c r="C118"/>
+        <v>379</v>
+      </c>
+      <c r="C118" t="s">
+        <v>380</v>
+      </c>
       <c r="F118" t="s">
-        <v>144</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:10">
       <c r="A119" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B119" t="s">
-        <v>139</v>
-      </c>
-      <c r="C119"/>
-      <c r="F119" t="s">
-        <v>141</v>
+        <v>382</v>
+      </c>
+      <c r="C119" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:10">
       <c r="A120" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B120" t="s">
-        <v>191</v>
-      </c>
-      <c r="C120" t="s">
         <v>384</v>
       </c>
-      <c r="F120" t="s">
-        <v>169</v>
-      </c>
-      <c r="J120" t="s">
-        <v>282</v>
-      </c>
+      <c r="C120"/>
     </row>
     <row r="121" spans="1:10">
       <c r="A121" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B121" t="s">
-        <v>193</v>
-      </c>
-      <c r="C121" t="s">
+        <v>286</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F121" t="s">
         <v>385</v>
-      </c>
-      <c r="F121" t="s">
-        <v>169</v>
-      </c>
-      <c r="J121" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:10">
       <c r="A122" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B122" t="s">
+        <v>288</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F122" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" t="s">
+        <v>64</v>
+      </c>
+      <c r="B123" t="s">
+        <v>290</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F123" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="B124" t="s">
         <v>387</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C124" t="s">
         <v>388</v>
       </c>
-      <c r="F122" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" hidden="1">
-      <c r="A123" t="s">
-        <v>68</v>
-      </c>
-      <c r="B123" t="s">
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" t="s">
+        <v>74</v>
+      </c>
+      <c r="B125" t="s">
+        <v>143</v>
+      </c>
+      <c r="C125"/>
+      <c r="F125" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" t="s">
+        <v>74</v>
+      </c>
+      <c r="B126" t="s">
+        <v>140</v>
+      </c>
+      <c r="C126"/>
+      <c r="F126" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" t="s">
+        <v>74</v>
+      </c>
+      <c r="B127" t="s">
+        <v>192</v>
+      </c>
+      <c r="C127" t="s">
         <v>389</v>
       </c>
-      <c r="C123"/>
-      <c r="F123" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" hidden="1">
-      <c r="A124" t="s">
-        <v>68</v>
-      </c>
-      <c r="B124" t="s">
+      <c r="F127" t="s">
+        <v>170</v>
+      </c>
+      <c r="J127" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128" t="s">
+        <v>74</v>
+      </c>
+      <c r="B128" t="s">
+        <v>194</v>
+      </c>
+      <c r="C128" t="s">
         <v>390</v>
       </c>
-      <c r="C124"/>
-      <c r="F124" t="s">
+      <c r="F128" t="s">
+        <v>170</v>
+      </c>
+      <c r="J128" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1">
-      <c r="A125" t="s">
-        <v>68</v>
-      </c>
-      <c r="B125" t="s">
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
+        <v>74</v>
+      </c>
+      <c r="B129" t="s">
         <v>392</v>
       </c>
-      <c r="C125"/>
-    </row>
-    <row r="126" spans="1:10" hidden="1">
-      <c r="A126" t="s">
-        <v>68</v>
-      </c>
-      <c r="B126" t="s">
+      <c r="C129" t="s">
         <v>393</v>
       </c>
-      <c r="C126" t="s">
+      <c r="F129" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>69</v>
+      </c>
+      <c r="B130" t="s">
         <v>394</v>
       </c>
-      <c r="G126" s="16" t="s">
+      <c r="C130"/>
+      <c r="F130" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
+        <v>69</v>
+      </c>
+      <c r="B131" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" hidden="1">
-      <c r="A127" t="s">
-        <v>68</v>
-      </c>
-      <c r="B127" t="s">
+      <c r="C131"/>
+      <c r="F131" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
+        <v>69</v>
+      </c>
+      <c r="B132" t="s">
         <v>396</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C132"/>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>69</v>
+      </c>
+      <c r="B133" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" hidden="1">
-      <c r="A128" t="s">
-        <v>68</v>
-      </c>
-      <c r="B128" s="4" t="s">
+      <c r="C133" t="s">
         <v>398</v>
       </c>
-      <c r="C128"/>
-    </row>
-    <row r="129" spans="1:7" hidden="1">
-      <c r="A129" t="s">
-        <v>68</v>
-      </c>
-      <c r="B129" t="s">
+      <c r="G133" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="C129"/>
-    </row>
-    <row r="130" spans="1:7" hidden="1">
-      <c r="A130" t="s">
-        <v>68</v>
-      </c>
-      <c r="B130" t="s">
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
+        <v>69</v>
+      </c>
+      <c r="B134" t="s">
         <v>400</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C134" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1">
-      <c r="B131" t="s">
-        <v>382</v>
-      </c>
-      <c r="C131" t="s">
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
+        <v>69</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" hidden="1">
-      <c r="A132" t="s">
-        <v>36</v>
-      </c>
-      <c r="B132" t="s">
+      <c r="C135"/>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
+        <v>69</v>
+      </c>
+      <c r="B136" t="s">
+        <v>403</v>
+      </c>
+      <c r="C136"/>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>69</v>
+      </c>
+      <c r="B137" t="s">
+        <v>404</v>
+      </c>
+      <c r="C137" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="B138" t="s">
+        <v>387</v>
+      </c>
+      <c r="C138" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>37</v>
+      </c>
+      <c r="B139" t="s">
+        <v>344</v>
+      </c>
+      <c r="C139"/>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
+        <v>37</v>
+      </c>
+      <c r="B140" t="s">
+        <v>0</v>
+      </c>
+      <c r="C140" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>37</v>
+      </c>
+      <c r="B141" t="s">
+        <v>247</v>
+      </c>
+      <c r="C141" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
+        <v>37</v>
+      </c>
+      <c r="B142" t="s">
+        <v>409</v>
+      </c>
+      <c r="C142" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
+        <v>37</v>
+      </c>
+      <c r="B143" t="s">
+        <v>411</v>
+      </c>
+      <c r="C143" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" s="4" customFormat="1">
+      <c r="A144" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="G144" s="6"/>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>37</v>
+      </c>
+      <c r="B145" t="s">
+        <v>416</v>
+      </c>
+      <c r="C145" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>37</v>
+      </c>
+      <c r="B146" t="s">
+        <v>418</v>
+      </c>
+      <c r="C146" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="60">
+      <c r="A155" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="G155" s="16" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>107</v>
+      </c>
+      <c r="B159" t="s">
+        <v>281</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D159" t="s">
+        <v>441</v>
+      </c>
+      <c r="E159" t="s">
+        <v>442</v>
+      </c>
+      <c r="F159" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>107</v>
+      </c>
+      <c r="B160" t="s">
+        <v>443</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D160" t="s">
+        <v>445</v>
+      </c>
+      <c r="F160" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>107</v>
+      </c>
+      <c r="B161" t="s">
+        <v>0</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="F161" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>107</v>
+      </c>
+      <c r="B162" t="s">
+        <v>448</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="F162" t="s">
+        <v>136</v>
+      </c>
+      <c r="G162" s="16" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>107</v>
+      </c>
+      <c r="B163" t="s">
+        <v>286</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C132"/>
-    </row>
-    <row r="133" spans="1:7" hidden="1">
-      <c r="A133" t="s">
-        <v>36</v>
-      </c>
-      <c r="B133" t="s">
-        <v>0</v>
-      </c>
-      <c r="C133" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" hidden="1">
-      <c r="A134" t="s">
-        <v>36</v>
-      </c>
-      <c r="B134" t="s">
-        <v>246</v>
-      </c>
-      <c r="C134" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" hidden="1">
-      <c r="A135" t="s">
-        <v>36</v>
-      </c>
-      <c r="B135" t="s">
-        <v>405</v>
-      </c>
-      <c r="C135" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" hidden="1">
-      <c r="A136" t="s">
-        <v>36</v>
-      </c>
-      <c r="B136" t="s">
-        <v>407</v>
-      </c>
-      <c r="C136" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" s="4" customFormat="1" hidden="1">
-      <c r="A137" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E137" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="G137" s="6"/>
-    </row>
-    <row r="138" spans="1:7" hidden="1">
-      <c r="A138" t="s">
-        <v>36</v>
-      </c>
-      <c r="B138" t="s">
-        <v>412</v>
-      </c>
-      <c r="C138" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" hidden="1">
-      <c r="A139" t="s">
-        <v>36</v>
-      </c>
-      <c r="B139" t="s">
-        <v>414</v>
-      </c>
-      <c r="C139" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" hidden="1">
-      <c r="A140" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" hidden="1">
-      <c r="A141" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" hidden="1">
-      <c r="A142" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" hidden="1">
-      <c r="A143" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" hidden="1">
-      <c r="A144" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" hidden="1">
-      <c r="A145" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" hidden="1">
-      <c r="A146" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" hidden="1">
-      <c r="A147" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="60" hidden="1">
-      <c r="A148" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="G148" s="16" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" hidden="1">
-      <c r="A149" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" hidden="1">
-      <c r="A150" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" hidden="1">
-      <c r="A151" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" hidden="1">
-      <c r="A152" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B152" t="s">
-        <v>436</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="D152" t="s">
-        <v>438</v>
-      </c>
-      <c r="E152" t="s">
-        <v>439</v>
-      </c>
-      <c r="F152" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" hidden="1">
-      <c r="A153" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B153" t="s">
-        <v>440</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="D153" t="s">
-        <v>442</v>
-      </c>
-      <c r="F153" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" hidden="1">
-      <c r="A154" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B154" t="s">
-        <v>0</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="F154" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" hidden="1">
-      <c r="A155" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B155" t="s">
-        <v>445</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="F155" t="s">
-        <v>135</v>
-      </c>
-      <c r="G155" s="16" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" hidden="1">
-      <c r="A156" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B156" t="s">
-        <v>374</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="F156" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" hidden="1">
-      <c r="A157" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B157" t="s">
-        <v>377</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="F157" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" hidden="1">
-      <c r="A158" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B158" t="s">
-        <v>379</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="F158" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" hidden="1">
-      <c r="A159" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B159" t="s">
-        <v>448</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" hidden="1">
-      <c r="A160" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B160" t="s">
-        <v>169</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" hidden="1">
-      <c r="A161" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B161" t="s">
+      <c r="F163" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>107</v>
+      </c>
+      <c r="B164" t="s">
+        <v>288</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F164" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>107</v>
+      </c>
+      <c r="B165" t="s">
+        <v>290</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F165" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>112</v>
+      </c>
+      <c r="B166" t="s">
         <v>451</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="C166" s="1" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1">
-      <c r="A162" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B162" t="s">
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>112</v>
+      </c>
+      <c r="B167" t="s">
+        <v>170</v>
+      </c>
+      <c r="C167" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="C162" s="1" t="s">
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>112</v>
+      </c>
+      <c r="B168" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" hidden="1">
-      <c r="A163" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B163" t="s">
+      <c r="C168" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="C163" s="1" t="s">
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>112</v>
+      </c>
+      <c r="B169" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" s="3"/>
+      <c r="C169" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>112</v>
+      </c>
+      <c r="B170" t="s">
+        <v>458</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>112</v>
+      </c>
+      <c r="B171" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>112</v>
+      </c>
+      <c r="B172" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>28</v>
+      </c>
+      <c r="B173" t="s">
+        <v>462</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="F173" t="s">
+        <v>127</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J106">
-    <sortCondition ref="A2:A106"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J112">
+    <sortCondition ref="A2:A112"/>
   </sortState>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1" xr:uid="{EAF3A632-FFC2-461F-8E3C-46D4F5CA1EA8}"/>
@@ -9686,55 +9862,55 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="G1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="K1" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="M1" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="N1" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -9745,10 +9921,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="E2" s="31">
         <v>1</v>
@@ -9760,7 +9936,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="I2" s="3">
         <v>10</v>
@@ -9784,10 +9960,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="E3" s="31">
         <v>1</v>
@@ -9799,7 +9975,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="I3" s="3">
         <v>200</v>
@@ -9823,10 +9999,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="E4" s="31">
         <v>2</v>
@@ -9836,7 +10012,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="I4" s="3">
         <v>15</v>
@@ -9860,10 +10036,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="E5" s="31">
         <v>3</v>
@@ -9873,7 +10049,7 @@
         <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -9900,7 +10076,7 @@
         <v>80</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="E6" s="31">
         <v>4</v>
@@ -9912,7 +10088,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="I6" s="3">
         <v>0</v>
@@ -9939,7 +10115,7 @@
         <v>80</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="31">
@@ -9949,7 +10125,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="I7" s="3">
         <v>256</v>
@@ -9976,7 +10152,7 @@
         <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="E8" s="31">
         <v>6</v>
@@ -9986,7 +10162,7 @@
         <v>7</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="I8" s="3">
         <v>24</v>
@@ -10013,7 +10189,7 @@
         <v>80</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="31">
@@ -10023,7 +10199,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="I9" s="3">
         <v>51</v>
@@ -10062,78 +10238,78 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="10" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="11" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="D4" s="17"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="11" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="11" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="11" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="D7" s="17"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="10" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -10141,47 +10317,47 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D9" s="17"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="11" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="D10" s="17"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="11" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="D11" s="17"/>
     </row>
     <row r="12" spans="1:4" ht="30">
       <c r="A12" s="11" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D12" s="17"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="10" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -10189,724 +10365,724 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="11" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="D14" s="17"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="11" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="D15" s="17"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="11" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="11" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="D17" s="17"/>
     </row>
     <row r="18" spans="1:6">
       <c r="E18" s="13" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="45">
       <c r="A19" s="12" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30">
       <c r="A20" s="12" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="60">
       <c r="A21" s="12" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30">
       <c r="A22" s="12" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="135">
       <c r="A23" s="12" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="270">
       <c r="A24" s="12" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="75">
       <c r="A25" s="12" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="120">
       <c r="A26" s="12" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="75">
       <c r="A27" s="12" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="75">
       <c r="A28" s="12" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="75">
       <c r="A29" s="12" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="75">
       <c r="A30" s="12" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="75">
       <c r="A31" s="12" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="45">
       <c r="A32" s="12" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="C32" s="19"/>
       <c r="E32" s="14" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30">
       <c r="A33" s="12" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30">
       <c r="A34" s="12" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="12" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="12" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="B38" s="16" t="s">
         <v>588</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>581</v>
-      </c>
       <c r="C38" s="16" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="12" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="45">
       <c r="A40" s="12" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="60">
       <c r="A41" s="12" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="60">
       <c r="A42" s="12" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="45">
       <c r="A43" s="12" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="30">
       <c r="A44" s="12" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="105">
       <c r="A45" s="12" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="45">
       <c r="A46" s="12" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="30">
       <c r="A47" s="12" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="30">
       <c r="A48" s="12" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="12" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="12" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="60">
       <c r="A51" s="12" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="60">
       <c r="A52" s="12" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="12" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="165">
       <c r="A54" s="12" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="30">
       <c r="A55" s="12" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="12" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="60">
       <c r="A57" s="12" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="60">
       <c r="A58" s="12" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="45">
       <c r="A59" s="12" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="45">
       <c r="A60" s="12" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="45">
       <c r="A61" s="12" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="45">
       <c r="A62" s="12" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -10927,234 +11103,234 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F1" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="B2" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="C2" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="D2" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="C3" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="D3" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="C4" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="D4" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="C5" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="D5" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="F5" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="C6" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="D6" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="C7" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D7" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="C8" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D8" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="C9" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D9" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="C10" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D10" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="C11" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D11" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" t="s">
+        <v>708</v>
+      </c>
+      <c r="C12" t="s">
         <v>701</v>
       </c>
-      <c r="C12" t="s">
-        <v>694</v>
-      </c>
       <c r="D12" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" t="s">
+        <v>709</v>
+      </c>
+      <c r="C13" t="s">
+        <v>701</v>
+      </c>
+      <c r="D13" t="s">
         <v>702</v>
-      </c>
-      <c r="C13" t="s">
-        <v>694</v>
-      </c>
-      <c r="D13" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="C14" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D14" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="C15" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D15" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="C16" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D16" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="C17" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D17" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="C18" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="D18" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="C19" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="D19" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="C20" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="D20" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -11187,10 +11363,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="28" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -11201,353 +11377,353 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="29" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="B2" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="C2" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="D2" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="29" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="B3" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="C3" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="D3" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="H3" s="25"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="29" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="B4" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="C4" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="D4" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="E4" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="F4" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="G4" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="H4" s="25"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="29" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="B5" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="H5" s="25"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="29" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="B6" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="C6" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="D6" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="H6" s="25"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="29" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="B7" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="C7" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="D7" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="E7" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="H7" s="25"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="29" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="B8" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="C8" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="D8" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="H8" s="25"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="29" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="B9" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="C9" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="H9" s="25"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="29" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="B10" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="C10" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="D10" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="H10" s="25"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="29" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="B11" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C11" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="D11" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="H11" s="25"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="29" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B12" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C12" t="s">
+        <v>735</v>
+      </c>
+      <c r="D12" t="s">
+        <v>736</v>
+      </c>
+      <c r="E12" t="s">
+        <v>720</v>
+      </c>
+      <c r="F12" t="s">
+        <v>727</v>
+      </c>
+      <c r="G12" t="s">
         <v>728</v>
-      </c>
-      <c r="D12" t="s">
-        <v>729</v>
-      </c>
-      <c r="E12" t="s">
-        <v>713</v>
-      </c>
-      <c r="F12" t="s">
-        <v>720</v>
-      </c>
-      <c r="G12" t="s">
-        <v>721</v>
       </c>
       <c r="H12" s="25"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="29" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="B13" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C13" t="s">
+        <v>735</v>
+      </c>
+      <c r="D13" t="s">
+        <v>736</v>
+      </c>
+      <c r="E13" t="s">
+        <v>720</v>
+      </c>
+      <c r="F13" t="s">
+        <v>727</v>
+      </c>
+      <c r="G13" t="s">
         <v>728</v>
-      </c>
-      <c r="D13" t="s">
-        <v>729</v>
-      </c>
-      <c r="E13" t="s">
-        <v>713</v>
-      </c>
-      <c r="F13" t="s">
-        <v>720</v>
-      </c>
-      <c r="G13" t="s">
-        <v>721</v>
       </c>
       <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="29" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="B14" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C14" t="s">
+        <v>735</v>
+      </c>
+      <c r="D14" t="s">
+        <v>734</v>
+      </c>
+      <c r="E14" t="s">
+        <v>737</v>
+      </c>
+      <c r="F14" t="s">
+        <v>720</v>
+      </c>
+      <c r="G14" t="s">
         <v>728</v>
       </c>
-      <c r="D14" t="s">
+      <c r="H14" s="25" t="s">
         <v>727</v>
-      </c>
-      <c r="E14" t="s">
-        <v>730</v>
-      </c>
-      <c r="F14" t="s">
-        <v>713</v>
-      </c>
-      <c r="G14" t="s">
-        <v>721</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="29" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="B15" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C15" t="s">
+        <v>735</v>
+      </c>
+      <c r="D15" t="s">
+        <v>734</v>
+      </c>
+      <c r="E15" t="s">
+        <v>720</v>
+      </c>
+      <c r="F15" t="s">
+        <v>738</v>
+      </c>
+      <c r="G15" t="s">
         <v>728</v>
-      </c>
-      <c r="D15" t="s">
-        <v>727</v>
-      </c>
-      <c r="E15" t="s">
-        <v>713</v>
-      </c>
-      <c r="F15" t="s">
-        <v>731</v>
-      </c>
-      <c r="G15" t="s">
-        <v>721</v>
       </c>
       <c r="H15" s="25"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="29" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="B16" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C16" t="s">
+        <v>735</v>
+      </c>
+      <c r="D16" t="s">
+        <v>734</v>
+      </c>
+      <c r="E16" t="s">
+        <v>720</v>
+      </c>
+      <c r="F16" t="s">
+        <v>738</v>
+      </c>
+      <c r="G16" t="s">
         <v>728</v>
-      </c>
-      <c r="D16" t="s">
-        <v>727</v>
-      </c>
-      <c r="E16" t="s">
-        <v>713</v>
-      </c>
-      <c r="F16" t="s">
-        <v>731</v>
-      </c>
-      <c r="G16" t="s">
-        <v>721</v>
       </c>
       <c r="H16" s="25"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="29" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="B17" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C17" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="E17" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="H17" s="25"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="29" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="B18" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="C18" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="H18" s="25"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="29" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="B19" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="C19" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="D19" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="29" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="B20" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C20" t="s">
+        <v>735</v>
+      </c>
+      <c r="D20" t="s">
+        <v>734</v>
+      </c>
+      <c r="E20" t="s">
+        <v>737</v>
+      </c>
+      <c r="F20" t="s">
+        <v>720</v>
+      </c>
+      <c r="G20" t="s">
         <v>728</v>
       </c>
-      <c r="D20" t="s">
+      <c r="H20" s="25" t="s">
         <v>727</v>
-      </c>
-      <c r="E20" t="s">
-        <v>730</v>
-      </c>
-      <c r="F20" t="s">
-        <v>713</v>
-      </c>
-      <c r="G20" t="s">
-        <v>721</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="30" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="26"/>

--- a/data/input/Low Level Field Detail Design(6).xlsx
+++ b/data/input/Low Level Field Detail Design(6).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgroupcloud.sharepoint.com/teams/CampaignManagementTransformation/Shared Documents/ROI and Attribution/Data Engineering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBCDC2F9-3417-498A-AD9F-9C1048427BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86C46C64-67AF-466A-917F-2A8852E2A9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
   </bookViews>
   <sheets>
     <sheet name="objects" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Interaction Types" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Attributes!$A$1:$J$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Attributes!$A$1:$J$167</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Channels!$A$1:$F$20</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -54,8 +54,6 @@
     <author>tc={B1C76761-6506-4B3F-A378-69D1147B5870}</author>
     <author>tc={8497C7DA-1239-4373-88D7-CCD3FD1374B1}</author>
     <author>tc={B341755A-7D9C-4B12-B3E8-F721DABD8A3A}</author>
-    <author>tc={0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}</author>
-    <author>tc={743A8CEB-662A-4266-9865-AE4208BB8853}</author>
   </authors>
   <commentList>
     <comment ref="B20" authorId="0" shapeId="0" xr:uid="{57FA6171-D98F-4CBE-BFC6-0F80D28C0683}">
@@ -121,7 +119,7 @@
     See comment on product family</t>
       </text>
     </comment>
-    <comment ref="C104" authorId="6" shapeId="0" xr:uid="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
+    <comment ref="C93" authorId="6" shapeId="0" xr:uid="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -131,34 +129,12 @@
 </t>
       </text>
     </comment>
-    <comment ref="C107" authorId="7" shapeId="0" xr:uid="{0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    @David Irvine 
-hope its Marketing Asset - bulletin etc
-Reply:
-    Updated</t>
-      </text>
-    </comment>
-    <comment ref="C111" authorId="8" shapeId="0" xr:uid="{743A8CEB-662A-4266-9865-AE4208BB8853}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    @David Irvine 
-need some example please . Audience will be part of contact(person) or company (customer)
-Reply:
-    See the audience table and description given lower in this table and in the higher level object definitions.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="749">
   <si>
     <t>Name</t>
   </si>
@@ -231,7 +207,7 @@
     <t>Channels</t>
   </si>
   <si>
-    <t>Derived or MRD</t>
+    <t>MRD</t>
   </si>
   <si>
     <t>A method of Delivering Content/assets to customers. E.G. Email.</t>
@@ -301,43 +277,29 @@
 And audience respresents the complete criteria a communicatino wouldn’t go to some intersection of two audiences, This example would be a third audience.</t>
   </si>
   <si>
-    <t>Push Activity</t>
-  </si>
-  <si>
-    <t>Outbound, proactive, targeted distribution of marketing assets (e.g., emails, calls, direct mail).</t>
+    <t>Marketing Activity</t>
+  </si>
+  <si>
+    <t>Outbound, proactive, targeted distribution of marketing assets (e.g., emails, calls, direct mail).
+Or
+Organic, content-driven strategies that attract and engage audiences on their own terms (e.g., social posts, billboards, website content).</t>
   </si>
   <si>
     <t>This Identifies the actions that BT Carries out and is ultimately the most granular element of Marketing activity that BT can optimise.</t>
   </si>
   <si>
-    <t>This defines the Specific audience for campaigns and activities where the audience is known. For calculation of conversion or engagement rates, This would be used as the baseline count.</t>
+    <t>Again this is a baseline for the marketing activity that has been carried out by BT.</t>
   </si>
   <si>
     <t>Each Row represents the Sending of a single assets to a single contact point which may be an individual or company.
 This is based on the experiance of the reciepient, So technical retries due to failure wouldn’t result in multiple rows, But if the User recieved two duplicate messages at the same time this would be 2 seperate rows.
-This covers everyone who was selected in the audience to receive the communication, Including the Control Cell audience.</t>
-  </si>
-  <si>
-    <t>Pull Activity</t>
-  </si>
-  <si>
-    <t>Organic, content-driven strategies that attract and engage audiences on their own terms (e.g., social posts, billboards, website content).</t>
-  </si>
-  <si>
-    <t>This tracks the BT marketing activities that are either 1 to many communications or where the audience is not defined. It provides a timeframe and link to assets and to Interactions.</t>
-  </si>
-  <si>
-    <t>Again this is a baseline for the marketing activity that has been carried out by BT.</t>
-  </si>
-  <si>
-    <t>Each Row represents a BT action to any number of people. Each action should have a Time or a timeframe where it would be consistantly showing the same asset.
+This covers everyone who was selected in the audience to receive the communication, Including the Control Cell audience.
+OR
+Each Row represents a BT action to any number of people. Each action should have a Time or a timeframe where it would be consistantly showing the same asset.
 Given the audience is Unknown one row here might have multiple engagements from Multiple Individuals or Companies.</t>
   </si>
   <si>
     <t>Interactions</t>
-  </si>
-  <si>
-    <t>Can be a derived entity from Activity</t>
   </si>
   <si>
     <t>Tracked activities by individuals that show they are engaging with an Asset.</t>
@@ -412,9 +374,6 @@
   </si>
   <si>
     <t>Person Company Role</t>
-  </si>
-  <si>
-    <t>Source System(JOB TITLE)</t>
   </si>
   <si>
     <t>Represents the relationship a person has with a company. I.E. decision maker, influences.
@@ -597,7 +556,7 @@
     <t>Requirement</t>
   </si>
   <si>
-    <t>Link ID</t>
+    <t>link_id</t>
   </si>
   <si>
     <t>Unique Identifier for this particular link</t>
@@ -606,7 +565,7 @@
     <t>PK</t>
   </si>
   <si>
-    <t>Activity ID</t>
+    <t>activity_id</t>
   </si>
   <si>
     <t>Identifies the specific marketing activity being linked</t>
@@ -615,7 +574,7 @@
     <t>FK -&gt; Activity.Activity_ID</t>
   </si>
   <si>
-    <t>Interaction ID</t>
+    <t>interaction_id</t>
   </si>
   <si>
     <t>Identifies the specific interaction that is being linked</t>
@@ -624,7 +583,7 @@
     <t>FK -&gt; Interaction.Interaction_ID</t>
   </si>
   <si>
-    <t>Outcome Type</t>
+    <t>outcome_type</t>
   </si>
   <si>
     <t>Identifies which outcome table is being linked</t>
@@ -633,7 +592,7 @@
     <t>Picklist</t>
   </si>
   <si>
-    <t>Outcome ID</t>
+    <t>outcome_id</t>
   </si>
   <si>
     <t>Identifies the specific outcome within that table that is linked.</t>
@@ -642,7 +601,7 @@
     <t>FK -&gt; Outcome_Type.Outcome_ID</t>
   </si>
   <si>
-    <t>Company ID</t>
+    <t>company_id</t>
   </si>
   <si>
     <t>Identifies the company that carried out the interaction and is related to the outcome.</t>
@@ -651,7 +610,7 @@
     <t>FK -&gt; Company.Company_ID</t>
   </si>
   <si>
-    <t>Person ID</t>
+    <t>person_id</t>
   </si>
   <si>
     <t>Identifies the Person related to the activity or interaction.</t>
@@ -660,7 +619,7 @@
     <t>FK -&gt; Person.Person_ID</t>
   </si>
   <si>
-    <t>Relation Type</t>
+    <t>relation_type</t>
   </si>
   <si>
     <t>Classify how the Activity was related to the outcome. Its possible there were multiple methods to associate the activity with the outcome. This identifies the most confident of linkage types.</t>
@@ -777,7 +736,7 @@
     </r>
   </si>
   <si>
-    <t>Time Lag</t>
+    <t>time_lag</t>
   </si>
   <si>
     <t>Time Between the Activity and the outcome * modelling may prefer to calculate from source fields.</t>
@@ -786,7 +745,7 @@
     <t>Time Difference</t>
   </si>
   <si>
-    <t>Model Output ID</t>
+    <t>model_output_id</t>
   </si>
   <si>
     <t>Unique Identifier for the model output given for this link and model.</t>
@@ -801,13 +760,13 @@
     <t>ID - FK</t>
   </si>
   <si>
-    <t>Model ID</t>
+    <t>model_id</t>
   </si>
   <si>
     <t>Which Model has provided this result</t>
   </si>
   <si>
-    <t>Attribution Weight</t>
+    <t>attribution_weight</t>
   </si>
   <si>
     <t>What is the proportion of the outcome that was caused by the activity as calculated by the model.</t>
@@ -822,7 +781,7 @@
     <t>Unique Identifier for the model</t>
   </si>
   <si>
-    <t>Model Name</t>
+    <t>model_name</t>
   </si>
   <si>
     <t>Name given the the model</t>
@@ -834,7 +793,7 @@
     <t>V01.0_Rules_Based_with_Guardrails</t>
   </si>
   <si>
-    <t>Model Start Date</t>
+    <t>model_start_date</t>
   </si>
   <si>
     <t>When was the model usable from</t>
@@ -843,19 +802,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>Model End Date</t>
+    <t>model_end_date</t>
   </si>
   <si>
     <t>When does the model cease to be useable.</t>
   </si>
   <si>
-    <t>Model Status</t>
+    <t>model_status</t>
   </si>
   <si>
     <t>is the model validated and usable, or retired</t>
   </si>
   <si>
-    <t>Model Type</t>
+    <t>model_type</t>
   </si>
   <si>
     <t>Classifies the models that are produced by the modelling team by which techniques they use</t>
@@ -870,7 +829,7 @@
     <t>Rules based, learned, TBC from Modelling Team</t>
   </si>
   <si>
-    <t>Outcome Used</t>
+    <t>outcome_used</t>
   </si>
   <si>
     <t xml:space="preserve">Which outcome is this model Attributing for </t>
@@ -879,7 +838,7 @@
     <t>Raised Orders, Completed Orders, Customer Value Change, Churn, leads, Lead Conversion</t>
   </si>
   <si>
-    <t>Model Owner</t>
+    <t>model_owner</t>
   </si>
   <si>
     <t>Current Owner of the model implimentation</t>
@@ -888,37 +847,37 @@
     <t>Petros</t>
   </si>
   <si>
-    <t>Campaign_ID</t>
+    <t>campaign_id</t>
   </si>
   <si>
     <t>Primary Identified for a campaign, This could either be the Monday code or a GCP generated ID, using the Monday code as a proxy identifier.</t>
   </si>
   <si>
-    <t>Campaign_Name</t>
+    <t>campaign_name</t>
   </si>
   <si>
     <t>The Unique business understandable short name of the campaign.</t>
   </si>
   <si>
-    <t>Created Date</t>
+    <t>created_date</t>
   </si>
   <si>
     <t>Date the Campaign was created (in Monday.com)</t>
   </si>
   <si>
-    <t>Start Date</t>
+    <t>start_date</t>
   </si>
   <si>
     <t>Date the campaign First went live and it was possible for a person to interact with the campaigns content.</t>
   </si>
   <si>
-    <t>End Date</t>
+    <t>end_date</t>
   </si>
   <si>
     <t>Date the campaign finished, the content is no longer being shared and new interactions are either impossible or unlikely.</t>
   </si>
   <si>
-    <t>Budget Timeframe</t>
+    <t>budget_timeframe</t>
   </si>
   <si>
     <t>The Quarter? Budget that was allocated to the development and support of this campaign. TBC this may need to be a Multi Line/ separate object depending on data source.</t>
@@ -930,7 +889,7 @@
     <t>Support Views look at Spend vs outcome for appropriate ROI analysis.</t>
   </si>
   <si>
-    <t>Targeted Audience ID</t>
+    <t>targeted_audience_id</t>
   </si>
   <si>
     <t>** Might not be directly relevant might primarially be joined via the Activity</t>
@@ -939,7 +898,7 @@
     <t>FK -&gt; Audience.Audience_ID</t>
   </si>
   <si>
-    <t>Parent Campaign ID</t>
+    <t>parent_campaign_id</t>
   </si>
   <si>
     <t>Identifies a parent campaign that might encompass multiple child campaigns.</t>
@@ -954,19 +913,19 @@
     <t>FK -&gt;Campaigns.Campaign_ID</t>
   </si>
   <si>
-    <t>Costs Anticipated</t>
+    <t>costs_anticipated</t>
   </si>
   <si>
     <t>Planned Cost of the campaign, How much of the budget has been provisionally allocated.</t>
   </si>
   <si>
-    <t>Costs Actuals</t>
+    <t>costs_actuals</t>
   </si>
   <si>
     <t>The actual tracked cost for this campaign. TBC if this is just external cost of if there is also an internal effort considered here.</t>
   </si>
   <si>
-    <t>Outcome Targets</t>
+    <t>outcome_targets</t>
   </si>
   <si>
     <t>Likely Multiple Fields, E.G. Expected uplift in order amounts. TBC with Monday.com setup what is available.</t>
@@ -978,7 +937,7 @@
     <t>Visual to show actuals vs Targets Able to show which campaigns are performing below or above expectations.</t>
   </si>
   <si>
-    <t>Brand</t>
+    <t>brand</t>
   </si>
   <si>
     <t>Which Brand is the Campaign Representing</t>
@@ -996,7 +955,7 @@
 EE Consumer</t>
   </si>
   <si>
-    <t>Business Unit</t>
+    <t>business_unit</t>
   </si>
   <si>
     <t>Which Business Unit is the campaign Targeting</t>
@@ -1005,16 +964,16 @@
     <t>SMB, CPS, Global</t>
   </si>
   <si>
-    <t>DMO Owner</t>
+    <t>dmo_owner</t>
   </si>
   <si>
     <t>Or another table that identifies the roles associated with the campaign.</t>
   </si>
   <si>
-    <t>??? Owner</t>
-  </si>
-  <si>
-    <t>Product Family</t>
+    <t>???_owner</t>
+  </si>
+  <si>
+    <t>product_family</t>
   </si>
   <si>
     <t>Identifies the Product the Campaign Is Targeting</t>
@@ -1023,7 +982,7 @@
     <t>FK -&gt; Product.Product_ID</t>
   </si>
   <si>
-    <t>Objective</t>
+    <t>objective</t>
   </si>
   <si>
     <t>What part of the customer lifecycle is being targeted</t>
@@ -1040,13 +999,13 @@
 Out of Contract</t>
   </si>
   <si>
-    <t>Partner</t>
+    <t>partner</t>
   </si>
   <si>
     <t>Company that is partnering, supporting, or running the campaign. E.G. a Joint Event with a Vendor.</t>
   </si>
   <si>
-    <t>Channel_ID</t>
+    <t>channel_id</t>
   </si>
   <si>
     <t>GCP Generated</t>
@@ -1055,13 +1014,16 @@
     <t>PK to be referenced by other objects.</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>Name Representing the channel</t>
   </si>
   <si>
     <t>Used for grouping and comparison within dashboards.</t>
   </si>
   <si>
-    <t>Group</t>
+    <t>group</t>
   </si>
   <si>
     <t>The Broad category of communication styles this channel is part of.</t>
@@ -1137,7 +1099,7 @@
     </r>
   </si>
   <si>
-    <t>Identifiable method</t>
+    <t>identifiable_method</t>
   </si>
   <si>
     <t>Describes how  this channels activity can be linked to Orders.</t>
@@ -1254,7 +1216,7 @@
     </r>
   </si>
   <si>
-    <t>Type</t>
+    <t>type</t>
   </si>
   <si>
     <t>Another way we could group channels is by the different high level delivery mechanisms involved.</t>
@@ -1327,19 +1289,19 @@
     </r>
   </si>
   <si>
-    <t>Interaction_ID</t>
-  </si>
-  <si>
     <t>Unique Identifier for the Interaction</t>
   </si>
   <si>
     <t>What was the type of intereaction. E.G. Open, Click, Visit, Call,…</t>
   </si>
   <si>
+    <t>date</t>
+  </si>
+  <si>
     <t>When did this interaction happen.</t>
   </si>
   <si>
-    <t>Duration</t>
+    <t>duration</t>
   </si>
   <si>
     <t>How long did the interaction last.</t>
@@ -1352,7 +1314,7 @@
 https://cloud.google.com/bigquery/docs/reference/standard-sql/interval_functions</t>
   </si>
   <si>
-    <t>Follow from interaction</t>
+    <t>follow_from_interaction</t>
   </si>
   <si>
     <t>If interaction came from a separate interaction. I.E. click on link -&gt; View Webpage -&gt; Submit Form</t>
@@ -1364,19 +1326,19 @@
     <t>Optional Needs One of person or company</t>
   </si>
   <si>
-    <t>Interacted Person ID</t>
+    <t>interacted_person_id</t>
   </si>
   <si>
     <t>Identifies the person that carried out the interaction.</t>
   </si>
   <si>
-    <t>Interacted Company ID</t>
+    <t>interacted_company_id</t>
   </si>
   <si>
     <t>Identifies the company that carried out the interaction.</t>
   </si>
   <si>
-    <t>Identification Method</t>
+    <t>identification_method</t>
   </si>
   <si>
     <t>What method was used to identify the individual or company for this interaction.</t>
@@ -1385,25 +1347,25 @@
     <t>Known From outbound Communication, Self Identification, Cookie match, IP Company Match, None</t>
   </si>
   <si>
-    <t>Data Source</t>
+    <t>data_source</t>
   </si>
   <si>
     <t>Which system tracked this interaction</t>
   </si>
   <si>
-    <t>Marketing Asset ID</t>
+    <t>marketing_asset_id</t>
   </si>
   <si>
     <t>Primary key for each unique Marketing Asset</t>
   </si>
   <si>
-    <t>Uses Dynamic Content</t>
+    <t>uses_dynamic_content</t>
   </si>
   <si>
     <t>identifies if the content contains dynamic personalisation specific to the audience.</t>
   </si>
   <si>
-    <t>Pega Flag</t>
+    <t>pega_flag</t>
   </si>
   <si>
     <t>Does the asset use pega recommendations as part of the content.</t>
@@ -1415,13 +1377,13 @@
     <t>For identifying specific assets within views.</t>
   </si>
   <si>
-    <t>Varient</t>
+    <t>varient</t>
   </si>
   <si>
     <t>* Should this differentiate the asset or be on the activity, Or actual a sub Object.</t>
   </si>
   <si>
-    <t>Product ID</t>
+    <t>product_id</t>
   </si>
   <si>
     <t>Links to the product or product family that this asset is promoting.</t>
@@ -1436,25 +1398,25 @@
     <t>Optional</t>
   </si>
   <si>
-    <t>Source Table</t>
+    <t>source_table</t>
   </si>
   <si>
     <t>Identifies the GCP table that this Row is sourced from</t>
   </si>
   <si>
-    <t>Source ID Field</t>
+    <t>source_id_field</t>
   </si>
   <si>
     <t>Identifies the PK field of that table.</t>
   </si>
   <si>
-    <t>Source ID</t>
+    <t>source_id</t>
   </si>
   <si>
     <t>The Source Table PK Value.</t>
   </si>
   <si>
-    <t>ID</t>
+    <t>order_id</t>
   </si>
   <si>
     <t>Unique Identifier for this order.</t>
@@ -1469,19 +1431,19 @@
     <t>String Enum</t>
   </si>
   <si>
-    <t>Product Group</t>
+    <t>product_group</t>
   </si>
   <si>
     <t>Which product group the product being sold in the order belongs to.</t>
   </si>
   <si>
-    <t>Product</t>
+    <t>product</t>
   </si>
   <si>
     <t>Which particular product was being sold in the order. *It might be actual we relate the order to a more complex product table depending on how the source data is structured</t>
   </si>
   <si>
-    <t>Action Type</t>
+    <t>action_type</t>
   </si>
   <si>
     <t xml:space="preserve">In what part of the customer lifecycle is this order, what is its context based on current  company status. </t>
@@ -1490,7 +1452,7 @@
     <t>"No Action", "Cease", "Modify", "Provide", "Mixed"</t>
   </si>
   <si>
-    <t>Transaction Channel</t>
+    <t>transaction_channel</t>
   </si>
   <si>
     <t xml:space="preserve">How did the customer make the order
@@ -1502,55 +1464,55 @@
 Physically - Order was processed and agreed F2F?</t>
   </si>
   <si>
-    <t>Date Raised</t>
+    <t>date_raised</t>
   </si>
   <si>
     <t>Date the order was agreed by the client, They have commited to buy at agreed price</t>
   </si>
   <si>
-    <t>Transaction Date</t>
+    <t>transaction_date</t>
   </si>
   <si>
     <t>When was the order actually transacted</t>
   </si>
   <si>
-    <t>Sales Order Value</t>
-  </si>
-  <si>
-    <t>Sales Order Value Gross Margin</t>
-  </si>
-  <si>
-    <t>Initial Contract Value</t>
-  </si>
-  <si>
-    <t>Initial Contract Value Gross margin</t>
-  </si>
-  <si>
-    <t>Average Revenue per Unit</t>
+    <t>sales_order_value</t>
+  </si>
+  <si>
+    <t>sales_order_value_gross_margin</t>
+  </si>
+  <si>
+    <t>initial_contract_value</t>
+  </si>
+  <si>
+    <t>initial_contract_value_gross_margin</t>
+  </si>
+  <si>
+    <t>average_revenue_per_unit</t>
   </si>
   <si>
     <t>Company the order is for * might their be cases where the paying company is meaningfully distinct from the using company</t>
   </si>
   <si>
-    <t>Contact_ID</t>
+    <t>contact_id</t>
   </si>
   <si>
     <t>The Key Contact Associated with Making the order, It might be we need a full relationship table that dictates the roles for the order, Dependant on available data.</t>
   </si>
   <si>
-    <t>Date Completed</t>
+    <t>date_completed</t>
   </si>
   <si>
     <t>When is the order delivery completed and revenue is confirmed.</t>
   </si>
   <si>
-    <t>Causal_Interaction_ID</t>
+    <t>causal_interaction_id</t>
   </si>
   <si>
     <t>The Iteraction that lead to the sale. E.G. the call. Foreign Key to the Interaction table.</t>
   </si>
   <si>
-    <t>Related Opportunity_ID</t>
+    <t>related_opportunity_id</t>
   </si>
   <si>
     <t>Which Opportunity preceeded and drove this order</t>
@@ -1559,13 +1521,13 @@
     <t>FK -&gt; Opportunity.Opportunity_ID</t>
   </si>
   <si>
-    <t>Contract Term</t>
+    <t>contract_term</t>
   </si>
   <si>
     <t>Agreed length of the contract.</t>
   </si>
   <si>
-    <t>Previous Order_ID</t>
+    <t>previous_order_id</t>
   </si>
   <si>
     <t>Link to another order where this order was a renewal of a previous order.</t>
@@ -1574,151 +1536,133 @@
     <t>FK -&gt; Orders.Order_ID</t>
   </si>
   <si>
-    <t>Ceased Date</t>
+    <t>ceased_date</t>
   </si>
   <si>
     <t>Date when the subscription expires or date when subscription is cancled. For non subscription products this would be blank</t>
   </si>
   <si>
-    <t>Product price Type</t>
+    <t>product_price_type</t>
   </si>
   <si>
     <t>Identifies if it’s a one off or recurring revenue sales. I.E&gt; Subscription.</t>
   </si>
   <si>
-    <t>Product Quantity</t>
-  </si>
-  <si>
-    <t>Cessetion Reason</t>
+    <t>product_quantity</t>
+  </si>
+  <si>
+    <t>cessetion_reason</t>
   </si>
   <si>
     <t>Cessation reason of the Order Item. Stopped after use</t>
   </si>
   <si>
-    <t>Cancel Reason</t>
+    <t>cancel_reason</t>
   </si>
   <si>
     <t>Reason for canceling, Stopped without using or applying, I bought then decided not to. I requested an adjustment then decided I didn't want the change.</t>
   </si>
   <si>
+    <t>audience_id</t>
+  </si>
+  <si>
+    <t>The Expected audience for this Activity</t>
+  </si>
+  <si>
+    <t>Used to limit which people / companies are likely to have been impacted by this activity</t>
+  </si>
+  <si>
+    <t>Which campaign was this activity associated with.</t>
+  </si>
+  <si>
+    <t>FK -&gt; Campaigns.Campaign_ID</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>Identifies if this record is actual part of the control for this campaign, As such wasn't sent the communications * Might be better handled in a different way.</t>
+  </si>
+  <si>
+    <t>Needed to support automating the control cell measurement which is a guardrail for our attribution model. Also Identifies those that for modelling purposes have been excluded so shouldn't have any revenue attributed due to this activity</t>
+  </si>
+  <si>
+    <t>Needed to showcase at a campaign level the control cell vs not for control cell uplift visualisation.</t>
+  </si>
+  <si>
+    <t>Boolean</t>
+  </si>
+  <si>
+    <t>When the asset stopped being shared through this mechanism and interactions are either impossible or unlikely.</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
     <t>Unique Identifier for the activity</t>
   </si>
   <si>
+    <t>Identifies the marketing asset that this marketing activity shares</t>
+  </si>
+  <si>
     <t>Optional Name of the activity, might not be needed may come from asset + Campaign.</t>
   </si>
   <si>
+    <t>reach_companies</t>
+  </si>
+  <si>
+    <t>The estimated or actual number of companies that would have had the opportunity to interact with this activity. * Company Granularity to be determined</t>
+  </si>
+  <si>
+    <t>Combine with the audience size to estimate the likelyhood that anyone in the audience was impacted by this activity.</t>
+  </si>
+  <si>
+    <t>potential Metric for future dashboards that are not currently in scope</t>
+  </si>
+  <si>
+    <t>reach_individuals</t>
+  </si>
+  <si>
+    <t>The estimated or actual number of individuals that would have had an opportunity to interact with this activity</t>
+  </si>
+  <si>
     <t>When the asset started to be shared through this mechanism and interactions are possible.</t>
   </si>
   <si>
-    <t>When the asset stopped being shared through this mechanism and interactions are either impossible or unlikely.</t>
-  </si>
-  <si>
-    <t>Audience ID</t>
-  </si>
-  <si>
-    <t>The Expected audience for this Activity</t>
-  </si>
-  <si>
-    <t>Used to limit which people / companies are likely to have been impacted by this activity</t>
-  </si>
-  <si>
-    <t>Reach Individuals</t>
-  </si>
-  <si>
-    <t>The estimated or actual number of individuals that would have had an opportunity to interact with this activity</t>
-  </si>
-  <si>
-    <t>Combine with the audience size to estimate the likelyhood that anyone in the audience was impacted by this activity.</t>
-  </si>
-  <si>
-    <t>potential Metric for future dashboards that are not currently in scope</t>
-  </si>
-  <si>
-    <t>Reach Companies</t>
-  </si>
-  <si>
-    <t>The estimated or actual number of companies that would have had the opportunity to interact with this activity. * Company Granularity to be determined</t>
-  </si>
-  <si>
-    <t>Identifies the marketing asset that this marketing activity shares</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Identifies if this record is actual part of the control for this campaign, As such wasn't sent the communications * Might be better handled in a different way.</t>
-  </si>
-  <si>
-    <t>Needed to support automating the control cell measurement which is a guardrail for our attribution model. Also Identifies those that for modelling purposes have been excluded so shouldn't have any revenue attributed due to this activity</t>
-  </si>
-  <si>
-    <t>Needed to showcase at a campaign level the control cell vs not for control cell uplift visualisation.</t>
-  </si>
-  <si>
-    <t>Boolean</t>
-  </si>
-  <si>
-    <t>When was the push activity send</t>
-  </si>
-  <si>
-    <t>Status</t>
+    <t>status</t>
   </si>
   <si>
     <t>What is the status of the push activity, I.E. was it Delivered, Part of control cell,…</t>
   </si>
   <si>
-    <t>Which marketing asset was sent my marketing activity</t>
-  </si>
-  <si>
-    <t>FK -&gt;Marketing Asset.Marketing Asset ID</t>
-  </si>
-  <si>
-    <t>Campaign ID</t>
-  </si>
-  <si>
-    <t>Which campaign was this activity associated with.</t>
-  </si>
-  <si>
-    <t>FK -&gt; Campaigns.Campaign_ID</t>
-  </si>
-  <si>
-    <t>Targeted Person ID</t>
+    <t>system_id</t>
+  </si>
+  <si>
+    <t>Which System facilitated this Activity</t>
+  </si>
+  <si>
+    <t>targeted_company_id</t>
+  </si>
+  <si>
+    <t>Identified the company that was targeted with the communication.</t>
+  </si>
+  <si>
+    <t>targeted_person_id</t>
   </si>
   <si>
     <t>Identifies the person the marketing activity targeted.</t>
   </si>
   <si>
-    <t>Targeted Company ID</t>
-  </si>
-  <si>
-    <t>Identified the company that was targeted with the communication.</t>
-  </si>
-  <si>
-    <t>Identified the audience that caused the individual or company to be targeted. This is a foreign key to linking to the audience table.</t>
-  </si>
-  <si>
-    <t>This will be one of the ways that a marketing activity is associated with an person or a company ultimately then an outcome.</t>
-  </si>
-  <si>
-    <t>Used in the audience analysis as a selection of the group of individuals or companies to review for outcome and descriptive charicteristics.</t>
-  </si>
-  <si>
-    <t>System ID</t>
-  </si>
-  <si>
-    <t>Which System facilitated this Activity</t>
-  </si>
-  <si>
     <t>Name of the tool</t>
   </si>
   <si>
-    <t>Owner</t>
+    <t>owner</t>
   </si>
   <si>
     <t>The BT team member that is responsible for this tool</t>
   </si>
   <si>
-    <t>Yearly Cost</t>
+    <t>yearly_cost</t>
   </si>
   <si>
     <t>* We may want a more compex tracking method later. This should be the cost that is not campaign specific. I.E. General License and platform maintainance costs.</t>
@@ -1727,13 +1671,10 @@
     <t>Currency Pounds</t>
   </si>
   <si>
-    <t>Person_ID</t>
-  </si>
-  <si>
     <t>Sythentic ID given to this individiual</t>
   </si>
   <si>
-    <t>Persona</t>
+    <t>persona</t>
   </si>
   <si>
     <t>GCP Table Reference</t>
@@ -1757,22 +1698,19 @@
     <t xml:space="preserve">Optional </t>
   </si>
   <si>
-    <t>Role Type</t>
+    <t>role_type</t>
   </si>
   <si>
     <t>Identifies the Role the person had at the company,</t>
   </si>
   <si>
-    <t>Company_ID</t>
-  </si>
-  <si>
-    <t>Parent_Company_ID</t>
-  </si>
-  <si>
-    <t>Company Market Channel</t>
-  </si>
-  <si>
-    <t>Company Business Type</t>
+    <t>parent_company_id</t>
+  </si>
+  <si>
+    <t>company_market_channel</t>
+  </si>
+  <si>
+    <t>company_business_type</t>
   </si>
   <si>
     <t>Billing Account, CUG, WK</t>
@@ -1781,19 +1719,19 @@
     <t>CUG, Billing Account, SAC, World Key</t>
   </si>
   <si>
-    <t>Owner_ID</t>
+    <t>owner_id</t>
   </si>
   <si>
     <t>Who is the sales person assigned to manage this company as an account.</t>
   </si>
   <si>
-    <t>Vertical</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>Location</t>
+    <t>vertical</t>
+  </si>
+  <si>
+    <t>industry</t>
+  </si>
+  <si>
+    <t>location</t>
   </si>
   <si>
     <t>This is a proxy field for some set of fields that identify company locations, can be aligned to source data structure.</t>
@@ -1808,19 +1746,19 @@
     <t>How is this audience identified</t>
   </si>
   <si>
-    <t>Audience Criteria Description</t>
+    <t>audience_criteria_description</t>
   </si>
   <si>
     <t>An description of the requirements for the audience to fulfil</t>
   </si>
   <si>
-    <t>Audience Criteria Technical</t>
+    <t>audience_criteria_technical</t>
   </si>
   <si>
     <t>The technical implimentation of these audience requirements.</t>
   </si>
   <si>
-    <t>Propensity model used</t>
+    <t>propensity_model_used</t>
   </si>
   <si>
     <t>Identifies the propensity model that is used as part of the audience selection criteria. This would be a FK to another table.</t>
@@ -1829,13 +1767,13 @@
     <t>Dimensions for filter and comparison, Gives the end user the ability to understand the effectiveness of the propensity models.</t>
   </si>
   <si>
-    <t>Size individuals</t>
+    <t>size_individuals</t>
   </si>
   <si>
     <t>The Estimated or actual count of individuals that form this audience.</t>
   </si>
   <si>
-    <t>Size Companies</t>
+    <t>size_companies</t>
   </si>
   <si>
     <t>The Estimated or actual count of Companies that form this audience. *Company Granularity to be determined</t>
@@ -1853,31 +1791,31 @@
     <t>Identifies the specific product family that this change refers to.</t>
   </si>
   <si>
-    <t>Sales Order Value Change</t>
+    <t>sales_order_value_change</t>
   </si>
   <si>
     <t>The Difference in Sales Order Value, Before to after the change date</t>
   </si>
   <si>
-    <t>Sales Order Value Gross Margin Change</t>
+    <t>sales_order_value_gross_margin_change</t>
   </si>
   <si>
     <t>The difference in SOV GM from before the change to after the change date</t>
   </si>
   <si>
-    <t>Initial Contract Value Change</t>
+    <t>initial_contract_value_change</t>
   </si>
   <si>
     <t>The difference in ICV from before to after the change date.</t>
   </si>
   <si>
-    <t>Initial Contract Value Gross margin Change</t>
+    <t>initial_contract_value_gross_margin_change</t>
   </si>
   <si>
     <t>The Difference in ICV GM from before to after the change date.</t>
   </si>
   <si>
-    <t>Change Type</t>
+    <t>change_type</t>
   </si>
   <si>
     <t>Denotes what the type of change was, whether its at the start or end of a customer journey or in the midding.</t>
@@ -1889,13 +1827,13 @@
 Lapsing</t>
   </si>
   <si>
-    <t>Prev Order ID</t>
+    <t>prev_order_id</t>
   </si>
   <si>
     <t>Reference to the Order that contains the old values for this product. This may be empty if no previous order found.</t>
   </si>
   <si>
-    <t>New Order ID</t>
+    <t>new_order_id</t>
   </si>
   <si>
     <t>Reference to the Order that contains the new values for this product. This may be empty if previous order is lapsing without renewal.</t>
@@ -1913,7 +1851,7 @@
     <t>For other Tables to Join To</t>
   </si>
   <si>
-    <t>Product Parent ID</t>
+    <t>product_parent_id</t>
   </si>
   <si>
     <t>Reference to Products Parent i.e Which Family or group this product is in.</t>
@@ -1928,7 +1866,7 @@
     <t>Short Human Understandable Name of the product.</t>
   </si>
   <si>
-    <t>Level</t>
+    <t>level</t>
   </si>
   <si>
     <t>The Level of the hierachy that this product is in.</t>
@@ -1937,7 +1875,7 @@
     <t>Tier 0, Tier 1, Tier 2 OR Product, Product Family, Product Group</t>
   </si>
   <si>
-    <t>DateKey</t>
+    <t>datekey</t>
   </si>
   <si>
     <t>This is the Date Primary Key</t>
@@ -1946,19 +1884,19 @@
     <t>Actual Date being represented</t>
   </si>
   <si>
-    <t>Financial Year</t>
+    <t>financial_year</t>
   </si>
   <si>
     <t>Which financial Year this date falls within</t>
   </si>
   <si>
-    <t>Financial Quarter</t>
+    <t>financial_quarter</t>
   </si>
   <si>
     <t>Which Financial Quarter this date falls into.</t>
   </si>
   <si>
-    <t>Financial Month Number</t>
+    <t>financial_month_number</t>
   </si>
   <si>
     <t>Month Number within BT Financial Year.</t>
@@ -1970,18 +1908,46 @@
     <t>is_holiday</t>
   </si>
   <si>
-    <t>Tool_id</t>
+    <t>tool_id</t>
   </si>
   <si>
     <t>Sythentic ID given to head tool</t>
   </si>
   <si>
+    <t>communication_mode</t>
+  </si>
+  <si>
+    <t>Identifies if this is a push or pull communication.</t>
+  </si>
+  <si>
+    <t>Helps understanding which attributes we would expect in the related marketing activities.</t>
+  </si>
+  <si>
+    <t>Push
+Pull</t>
+  </si>
+  <si>
+    <t>Activity ID</t>
+  </si>
+  <si>
+    <t>Outcome ID</t>
+  </si>
+  <si>
+    <t>Outcome Type</t>
+  </si>
+  <si>
+    <t>Link ID</t>
+  </si>
+  <si>
     <t>Interaction</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
+    <t>Relation Type</t>
+  </si>
+  <si>
     <t>Time Lag (Days)</t>
   </si>
   <si>
@@ -1992,6 +1958,21 @@
   </si>
   <si>
     <t>Attributed Amount</t>
+  </si>
+  <si>
+    <t>Sales Order Value</t>
+  </si>
+  <si>
+    <t>Sales Order Value Gross Margin</t>
+  </si>
+  <si>
+    <t>Initial Contract Value</t>
+  </si>
+  <si>
+    <t>Initial Contract Value Gross margin</t>
+  </si>
+  <si>
+    <t>Average Revenue per Unit</t>
   </si>
   <si>
     <t>Opportunty Created</t>
@@ -5767,6 +5748,18 @@
       </rPr>
       <t>. Many dashboards mention “Audience Groupings” that can include company size.</t>
     </r>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Identifiable method</t>
+  </si>
+  <si>
+    <t>Type</t>
   </si>
   <si>
     <t>Comment</t>
@@ -6394,8 +6387,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D396AB2F-F9BE-4F78-8BC5-51EC98BD60B1}" name="Table1" displayName="Table1" ref="A1:J173" totalsRowShown="0">
-  <autoFilter ref="A1:J173" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D396AB2F-F9BE-4F78-8BC5-51EC98BD60B1}" name="Table1" displayName="Table1" ref="A1:J167" totalsRowShown="0">
+  <autoFilter ref="A1:J167" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Orders"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J165">
+    <sortCondition ref="A1:A165"/>
+  </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{FA10E4DE-EA14-4D6D-B2DE-B36300D4BF76}" name="Object" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{32E1B4A0-4AC4-478E-B858-9CDAC148562B}" name="Name"/>
@@ -6786,7 +6788,7 @@
   <threadedComment ref="B61" dT="2025-03-07T22:24:32.38" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{3477900C-1235-4AD9-B6B9-B36EBE216470}" parentId="{8497C7DA-1239-4373-88D7-CCD3FD1374B1}">
     <text>See comment on product family</text>
   </threadedComment>
-  <threadedComment ref="C104" dT="2025-03-06T16:36:49.39" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
+  <threadedComment ref="C93" dT="2025-03-06T16:36:49.39" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
     <text xml:space="preserve">@David Irvine 
 example please . is it a available field in existing Marketo Activities?
 </text>
@@ -6794,34 +6796,12 @@
       <mention mentionpersonId="{2D30A5D6-A763-4ABB-81AE-1F40D026C227}" mentionId="{40C38E33-B939-49D4-8B2E-6D818BD6F889}" startIndex="0" length="13"/>
     </mentions>
   </threadedComment>
-  <threadedComment ref="C107" dT="2025-03-06T16:37:15.29" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}">
-    <text xml:space="preserve">@David Irvine 
-hope its Marketing Asset - bulletin etc
-</text>
-    <mentions>
-      <mention mentionpersonId="{2D30A5D6-A763-4ABB-81AE-1F40D026C227}" mentionId="{A3E4CE78-E2D0-4F35-8130-361426FEAED0}" startIndex="0" length="13"/>
-    </mentions>
-  </threadedComment>
-  <threadedComment ref="C107" dT="2025-03-07T22:07:31.32" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{5B19FF75-413F-42F1-981E-51C52DF1C444}" parentId="{0AF79B6B-4424-47BE-A6D1-44B67BFA5C1D}">
-    <text>Updated</text>
-  </threadedComment>
-  <threadedComment ref="C111" dT="2025-03-06T16:37:38.16" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{743A8CEB-662A-4266-9865-AE4208BB8853}">
-    <text xml:space="preserve">@David Irvine 
-need some example please . Audience will be part of contact(person) or company (customer)
-</text>
-    <mentions>
-      <mention mentionpersonId="{2D30A5D6-A763-4ABB-81AE-1F40D026C227}" mentionId="{98A2319B-9179-4D17-8B08-096AE9402B5D}" startIndex="0" length="13"/>
-    </mentions>
-  </threadedComment>
-  <threadedComment ref="C111" dT="2025-03-07T22:08:12.74" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{7ECB8EFC-8B65-4BC1-894D-08FDEBC4BB3E}" parentId="{743A8CEB-662A-4266-9865-AE4208BB8853}">
-    <text>See the audience table and description given lower in this table and in the higher level object definitions.</text>
-  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF98BEB6-65EB-437D-B437-4DFA85EC4A08}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
@@ -6936,7 +6916,7 @@
       </c>
       <c r="G3">
         <f>COUNTIF(Attributes!A:A,objects!A3)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" t="s">
         <v>27</v>
@@ -7047,11 +7027,13 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="75">
+    <row r="7" spans="1:13" ht="101.25">
       <c r="A7" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>43</v>
       </c>
@@ -7066,7 +7048,7 @@
       </c>
       <c r="G7">
         <f>COUNTIF(Attributes!A:A,objects!A7)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -7078,11 +7060,13 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="60">
+    <row r="8" spans="1:13" ht="105">
       <c r="A8" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="C8" s="1" t="s">
         <v>48</v>
       </c>
@@ -7097,23 +7081,23 @@
       </c>
       <c r="G8">
         <f>COUNTIF(Attributes!A:A,objects!A8)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
       </c>
       <c r="I8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="105">
-      <c r="A9" s="34" t="s">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30">
+      <c r="A9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -7130,376 +7114,343 @@
       </c>
       <c r="G9">
         <f>COUNTIF(Attributes!A:A,objects!A9)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I9">
-        <v>17</v>
-      </c>
-      <c r="J9">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="30">
-      <c r="A10" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="75">
+      <c r="A10" s="34" t="s">
         <v>58</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="G10">
         <f>COUNTIF(Attributes!A:A,objects!A10)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I10">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="75">
+        <v>7</v>
+      </c>
+      <c r="J10">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="120">
       <c r="A11" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="G11">
         <f>COUNTIF(Attributes!A:A,objects!A11)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="120">
-      <c r="A12" s="34" t="s">
-        <v>69</v>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="60">
+      <c r="A12" s="37" t="s">
+        <v>68</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="G12">
         <f>COUNTIF(Attributes!A:A,objects!A12)</f>
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12">
         <v>8</v>
       </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12">
-        <v>6</v>
-      </c>
-      <c r="J12">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="60">
-      <c r="A13" s="37" t="s">
+    </row>
+    <row r="13" spans="1:13" ht="45">
+      <c r="A13" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="D13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G13">
         <f>COUNTIF(Attributes!A:A,objects!A13)</f>
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="45">
+        <v>9</v>
+      </c>
+      <c r="J13">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="105">
       <c r="A14" s="34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G14">
         <f>COUNTIF(Attributes!A:A,objects!A14)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="I14">
-        <v>9</v>
-      </c>
-      <c r="J14">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="105">
-      <c r="A15" s="34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="60">
+      <c r="A15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="G15">
         <f>COUNTIF(Attributes!A:A,objects!A15)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="45">
+      <c r="A16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="I15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="60">
-      <c r="A16" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="G16">
         <f>COUNTIF(Attributes!A:A,objects!A16)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16">
         <v>12</v>
       </c>
-      <c r="H16" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="45">
-      <c r="A17" s="7" t="s">
+    </row>
+    <row r="17" spans="1:9" ht="60">
+      <c r="A17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="F17" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="G17">
         <f>COUNTIF(Attributes!A:A,objects!A17)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="60">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="75">
       <c r="A18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="D18" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="G18">
         <f>COUNTIF(Attributes!A:A,objects!A18)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I18">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="45">
+      <c r="A19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="75">
-      <c r="A19" s="3" t="s">
+      <c r="C19" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="E19" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="F19" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G19">
-        <f>COUNTIF(Attributes!A:A,objects!A19)</f>
+      <c r="H19" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19">
         <v>0</v>
-      </c>
-      <c r="H19" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19">
-        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="45">
       <c r="A20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="E20" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="F20" s="16" t="s">
         <v>109</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>111</v>
       </c>
       <c r="H20" t="s">
         <v>27</v>
       </c>
       <c r="I20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="45">
-      <c r="A21" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="H21" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21">
         <v>0</v>
       </c>
     </row>
@@ -7510,7 +7461,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
-  <dimension ref="A1:J173"/>
+  <dimension ref="A1:J167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -7527,7 +7478,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -7536,1454 +7487,1460 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" hidden="1">
+      <c r="A2" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="C2" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F2" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="24" t="s">
+    </row>
+    <row r="3" spans="1:10" hidden="1">
+      <c r="A3" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="H1" t="s">
+      <c r="C3" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="I1" t="s">
+      <c r="F3" t="s">
         <v>123</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="4" spans="1:10" hidden="1">
+      <c r="A4" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="36" t="s">
+      <c r="C4" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="F4" t="s">
         <v>126</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="5" spans="1:10" hidden="1">
+      <c r="A5" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="36" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="36" t="s">
+      <c r="C5" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="F5" t="s">
         <v>129</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="6" spans="1:10" hidden="1">
+      <c r="A6" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="36" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="36" t="s">
+      <c r="C6" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="F6" t="s">
         <v>132</v>
       </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="7" spans="1:10" hidden="1">
+      <c r="A7" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="36" t="s">
+      <c r="C7" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="F7" t="s">
         <v>135</v>
       </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="8" spans="1:10" hidden="1">
+      <c r="A8" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="36" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="36" t="s">
+      <c r="C8" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="F8" t="s">
         <v>138</v>
       </c>
-      <c r="F6" t="s">
+    </row>
+    <row r="9" spans="1:10" ht="107.25" hidden="1" customHeight="1">
+      <c r="A9" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="36" t="s">
+      <c r="C9" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="F9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="10" spans="1:10" hidden="1">
+      <c r="A10" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="36" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="36" t="s">
+      <c r="C10" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="F10" t="s">
         <v>144</v>
       </c>
-      <c r="F8" t="s">
+    </row>
+    <row r="11" spans="1:10" hidden="1">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="107.25" customHeight="1">
-      <c r="A9" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="36" t="s">
+      <c r="C11" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="F11" t="s">
         <v>147</v>
       </c>
-      <c r="F9" t="s">
-        <v>136</v>
-      </c>
-      <c r="G9" s="16" t="s">
+    </row>
+    <row r="12" spans="1:10" hidden="1">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="36" t="s">
+      <c r="F12" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="36" t="s">
+    </row>
+    <row r="13" spans="1:10" hidden="1">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
         <v>150</v>
       </c>
-      <c r="F10" t="s">
+      <c r="C13" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="F13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" hidden="1">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
         <v>152</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C14" t="s">
         <v>153</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F14" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F13" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" t="s">
-        <v>161</v>
       </c>
       <c r="G14" s="16">
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" hidden="1">
       <c r="A15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" hidden="1">
+      <c r="A16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F16" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" hidden="1">
+      <c r="A17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" t="s">
         <v>162</v>
       </c>
-      <c r="B15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="F17" t="s">
         <v>163</v>
       </c>
-      <c r="F15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="18" spans="1:7" hidden="1">
+      <c r="A18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" t="s">
         <v>164</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C18" t="s">
         <v>165</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" hidden="1">
+      <c r="A19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" t="s">
         <v>166</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="C19" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="F19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="43.5" hidden="1">
+      <c r="A20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B20" t="s">
         <v>168</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C20" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F17" t="s">
+      <c r="D20" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="E20" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F18" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B19" t="s">
+    </row>
+    <row r="21" spans="1:7" hidden="1">
+      <c r="A21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B21" t="s">
         <v>173</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C21" t="s">
         <v>174</v>
       </c>
-      <c r="F19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="45">
-      <c r="A20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="F21" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="C20" s="5" t="s">
+    </row>
+    <row r="22" spans="1:7" hidden="1">
+      <c r="A22" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" t="s">
         <v>176</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="C22" t="s">
         <v>177</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="F22" t="s">
+        <v>159</v>
+      </c>
+      <c r="G22" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="F20" t="s">
-        <v>136</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>162</v>
-      </c>
-      <c r="B21" t="s">
-        <v>180</v>
-      </c>
-      <c r="C21" t="s">
-        <v>181</v>
-      </c>
-      <c r="F21" t="s">
-        <v>136</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>162</v>
-      </c>
-      <c r="B22" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" t="s">
-        <v>184</v>
-      </c>
-      <c r="F22" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+    </row>
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C23" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F23" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" t="s">
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C24" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F24" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C25" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F25" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C26" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F26" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C27" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F27" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C28" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D28" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E28" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" t="s">
         <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C29" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F29" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" t="s">
         <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C30" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D30" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E30" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F30" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C31" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C32" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C33" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D33" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="E33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="60">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="57.75" hidden="1">
       <c r="A34" t="s">
         <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C34" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D34" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E34" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C37" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F38" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="135">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="130.5" hidden="1">
       <c r="A39" t="s">
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C39" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C40" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C41" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D41" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F41" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="C42" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E42" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F42" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="45">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="43.5" hidden="1">
       <c r="A43" t="s">
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C43" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E43" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F43" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="75">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="72.75" hidden="1">
       <c r="A44" t="s">
         <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C44" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="F44" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="45">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="43.5" hidden="1">
       <c r="A45" t="s">
         <v>21</v>
       </c>
       <c r="B45" t="s">
+        <v>241</v>
+      </c>
+      <c r="C45" t="s">
+        <v>242</v>
+      </c>
+      <c r="F45" t="s">
+        <v>236</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" hidden="1">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" hidden="1">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s">
+        <v>241</v>
+      </c>
+      <c r="C47" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" hidden="1">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>246</v>
+      </c>
+      <c r="C48" t="s">
         <v>247</v>
       </c>
-      <c r="C45" t="s">
+    </row>
+    <row r="49" spans="1:10" ht="24.75" hidden="1">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
         <v>248</v>
       </c>
-      <c r="F45" t="s">
-        <v>242</v>
-      </c>
-      <c r="G45" s="16" t="s">
+      <c r="C49" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="F49" t="s">
         <v>250</v>
       </c>
-      <c r="C46" t="s">
+      <c r="G49" s="38" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
-      <c r="A47" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" t="s">
-        <v>247</v>
-      </c>
-      <c r="C47" t="s">
+    <row r="50" spans="1:10" hidden="1">
+      <c r="A50" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" t="s">
-        <v>52</v>
-      </c>
-      <c r="B48" t="s">
-        <v>170</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="C50" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="27">
-      <c r="A49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49" t="s">
+    <row r="51" spans="1:10" hidden="1">
+      <c r="A51" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" t="s">
         <v>254</v>
       </c>
-      <c r="C49" t="s">
+      <c r="F51" t="s">
+        <v>123</v>
+      </c>
+      <c r="J51" t="s">
         <v>255</v>
       </c>
-      <c r="F49" t="s">
+    </row>
+    <row r="52" spans="1:10" hidden="1">
+      <c r="A52" t="s">
+        <v>47</v>
+      </c>
+      <c r="B52" t="s">
         <v>256</v>
       </c>
-      <c r="G49" s="38" t="s">
+      <c r="C52" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="F52" t="s">
+        <v>138</v>
+      </c>
+      <c r="J52" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" hidden="1">
+      <c r="A53" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" t="s">
         <v>258</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C53" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" t="s">
-        <v>128</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="F53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" hidden="1">
+      <c r="A54" t="s">
+        <v>47</v>
+      </c>
+      <c r="B54" t="s">
         <v>260</v>
       </c>
-      <c r="F51" t="s">
-        <v>130</v>
-      </c>
-      <c r="J51" t="s">
+      <c r="C54" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" t="s">
-        <v>52</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="G54" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="C52" t="s">
+    </row>
+    <row r="55" spans="1:10" hidden="1">
+      <c r="A55" t="s">
+        <v>47</v>
+      </c>
+      <c r="B55" t="s">
         <v>263</v>
       </c>
-      <c r="F52" t="s">
-        <v>145</v>
-      </c>
-      <c r="J52" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="C55" t="s">
         <v>264</v>
       </c>
-      <c r="C53" t="s">
-        <v>265</v>
-      </c>
-      <c r="F53" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" t="s">
-        <v>52</v>
-      </c>
-      <c r="B54" t="s">
-        <v>266</v>
-      </c>
-      <c r="C54" t="s">
-        <v>267</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" t="s">
-        <v>269</v>
-      </c>
-      <c r="C55" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+    </row>
+    <row r="56" spans="1:10" hidden="1">
       <c r="A56" t="s">
         <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" hidden="1">
       <c r="A57" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C57" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" hidden="1">
       <c r="A58" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C58" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" hidden="1">
       <c r="A59" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="C59" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D59" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="E59" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" hidden="1">
       <c r="A60" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C60" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="57.75">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="57.75" hidden="1">
       <c r="A61" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="F61" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="J61" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" hidden="1">
       <c r="A62" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" hidden="1">
       <c r="A63" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" hidden="1">
       <c r="A64" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B65" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C65" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="C66" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J66" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C67" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F67" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C68" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="F68" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C69" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="F69" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C70" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F70" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="45">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="43.5">
       <c r="A71" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C71" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F71" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C72" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C73" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C74"/>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C75"/>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C76"/>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C77"/>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C78"/>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B79" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C79" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F79" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F80" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B81" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C81" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B82" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F82" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B83" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C83" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F83" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="J83" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B84" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C84" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B85" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C85" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F85" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="J86" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C88" s="4"/>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B90" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" hidden="1">
+      <c r="A91" t="s">
+        <v>42</v>
+      </c>
+      <c r="B91" t="s">
+        <v>334</v>
+      </c>
+      <c r="C91" t="s">
+        <v>335</v>
+      </c>
+      <c r="D91" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" hidden="1">
+      <c r="A92" t="s">
+        <v>42</v>
+      </c>
+      <c r="B92" t="s">
+        <v>179</v>
+      </c>
+      <c r="C92" t="s">
+        <v>337</v>
+      </c>
+      <c r="F92" t="s">
         <v>338</v>
       </c>
-      <c r="C90" s="4" t="s">
+    </row>
+    <row r="93" spans="1:10" ht="29.25" hidden="1">
+      <c r="A93" t="s">
+        <v>42</v>
+      </c>
+      <c r="B93" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="91" spans="1:10">
-      <c r="A91" t="s">
-        <v>47</v>
-      </c>
-      <c r="B91" t="s">
-        <v>292</v>
-      </c>
-      <c r="C91" t="s">
+      <c r="C93" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="92" spans="1:10">
-      <c r="A92" t="s">
-        <v>47</v>
-      </c>
-      <c r="B92" t="s">
-        <v>0</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="D93" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="A93" t="s">
-        <v>47</v>
-      </c>
-      <c r="B93" t="s">
-        <v>192</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="E93" s="6" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="94" spans="1:10">
+      <c r="F93" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" hidden="1">
       <c r="A94" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C94" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" hidden="1">
       <c r="A95" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C95" t="s">
-        <v>345</v>
-      </c>
-      <c r="D95" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" hidden="1">
       <c r="A96" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" hidden="1">
       <c r="A97" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>288</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+        <v>231</v>
+      </c>
+      <c r="C97" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" hidden="1">
       <c r="A98" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B98" t="s">
-        <v>290</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+        <v>349</v>
+      </c>
+      <c r="C98" t="s">
+        <v>350</v>
+      </c>
+      <c r="D98" t="s">
+        <v>351</v>
+      </c>
+      <c r="E98" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" hidden="1">
       <c r="A99" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C99" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="D99" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E99" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" hidden="1">
       <c r="A100" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>351</v>
-      </c>
-      <c r="C100" t="s">
-        <v>352</v>
-      </c>
-      <c r="D100" t="s">
-        <v>349</v>
-      </c>
-      <c r="E100" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+        <v>284</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" hidden="1">
       <c r="A101" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B101" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" hidden="1">
       <c r="A102" t="s">
         <v>42</v>
       </c>
       <c r="B102" t="s">
-        <v>292</v>
-      </c>
-      <c r="C102" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+        <v>280</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" hidden="1">
       <c r="A103" t="s">
         <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="C103" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="105">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" hidden="1">
       <c r="A104" t="s">
         <v>42</v>
       </c>
       <c r="B104" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C104" t="s">
-        <v>355</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="E104" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="F104" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+    </row>
+    <row r="105" spans="1:6" hidden="1">
       <c r="A105" t="s">
         <v>42</v>
       </c>
       <c r="B105" t="s">
-        <v>170</v>
+        <v>358</v>
       </c>
       <c r="C105" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="106" spans="1:6">
+      <c r="D105" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" hidden="1">
       <c r="A106" t="s">
         <v>42</v>
       </c>
@@ -8993,832 +8950,754 @@
       <c r="C106" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="107" spans="1:6">
+      <c r="F106" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" hidden="1">
       <c r="A107" t="s">
         <v>42</v>
       </c>
       <c r="B107" t="s">
-        <v>271</v>
+        <v>362</v>
       </c>
       <c r="C107" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F107" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" hidden="1">
       <c r="A108" t="s">
+        <v>28</v>
+      </c>
+      <c r="B108" t="s">
+        <v>231</v>
+      </c>
+      <c r="C108" t="s">
+        <v>364</v>
+      </c>
+      <c r="F108" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" hidden="1">
+      <c r="A109" t="s">
+        <v>28</v>
+      </c>
+      <c r="B109" t="s">
+        <v>365</v>
+      </c>
+      <c r="C109" t="s">
+        <v>366</v>
+      </c>
+      <c r="F109" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" hidden="1">
+      <c r="A110" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" t="s">
+        <v>367</v>
+      </c>
+      <c r="C110" t="s">
+        <v>368</v>
+      </c>
+      <c r="F110" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" hidden="1">
+      <c r="A111" t="s">
+        <v>58</v>
+      </c>
+      <c r="B111" t="s">
+        <v>136</v>
+      </c>
+      <c r="C111" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" hidden="1">
+      <c r="A112" t="s">
+        <v>58</v>
+      </c>
+      <c r="B112" t="s">
+        <v>371</v>
+      </c>
+      <c r="C112"/>
+    </row>
+    <row r="113" spans="1:10" hidden="1">
+      <c r="A113" t="s">
+        <v>58</v>
+      </c>
+      <c r="B113" t="s">
+        <v>280</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F113" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" hidden="1">
+      <c r="A114" t="s">
+        <v>58</v>
+      </c>
+      <c r="B114" t="s">
+        <v>282</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F114" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" hidden="1">
+      <c r="A115" t="s">
+        <v>58</v>
+      </c>
+      <c r="B115" t="s">
+        <v>284</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F115" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" hidden="1">
+      <c r="B116" t="s">
+        <v>374</v>
+      </c>
+      <c r="C116" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" hidden="1">
+      <c r="A117" t="s">
+        <v>68</v>
+      </c>
+      <c r="B117" t="s">
+        <v>136</v>
+      </c>
+      <c r="C117"/>
+      <c r="F117" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" hidden="1">
+      <c r="A118" t="s">
+        <v>68</v>
+      </c>
+      <c r="B118" t="s">
+        <v>133</v>
+      </c>
+      <c r="C118"/>
+      <c r="F118" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" hidden="1">
+      <c r="A119" t="s">
+        <v>68</v>
+      </c>
+      <c r="B119" t="s">
+        <v>185</v>
+      </c>
+      <c r="C119" t="s">
+        <v>376</v>
+      </c>
+      <c r="F119" t="s">
+        <v>163</v>
+      </c>
+      <c r="J119" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" hidden="1">
+      <c r="A120" t="s">
+        <v>68</v>
+      </c>
+      <c r="B120" t="s">
+        <v>187</v>
+      </c>
+      <c r="C120" t="s">
+        <v>377</v>
+      </c>
+      <c r="F120" t="s">
+        <v>163</v>
+      </c>
+      <c r="J120" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" hidden="1">
+      <c r="A121" t="s">
+        <v>68</v>
+      </c>
+      <c r="B121" t="s">
+        <v>379</v>
+      </c>
+      <c r="C121" t="s">
+        <v>380</v>
+      </c>
+      <c r="F121" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" hidden="1">
+      <c r="A122" t="s">
+        <v>63</v>
+      </c>
+      <c r="B122" t="s">
+        <v>133</v>
+      </c>
+      <c r="C122"/>
+      <c r="F122" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" hidden="1">
+      <c r="A123" t="s">
+        <v>63</v>
+      </c>
+      <c r="B123" t="s">
+        <v>381</v>
+      </c>
+      <c r="C123"/>
+      <c r="F123" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" hidden="1">
+      <c r="A124" t="s">
+        <v>63</v>
+      </c>
+      <c r="B124" t="s">
+        <v>382</v>
+      </c>
+      <c r="C124"/>
+    </row>
+    <row r="125" spans="1:10" hidden="1">
+      <c r="A125" t="s">
+        <v>63</v>
+      </c>
+      <c r="B125" t="s">
+        <v>383</v>
+      </c>
+      <c r="C125" t="s">
+        <v>384</v>
+      </c>
+      <c r="G125" s="16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" hidden="1">
+      <c r="A126" t="s">
+        <v>63</v>
+      </c>
+      <c r="B126" t="s">
+        <v>386</v>
+      </c>
+      <c r="C126" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" hidden="1">
+      <c r="A127" t="s">
+        <v>63</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C127"/>
+    </row>
+    <row r="128" spans="1:10" hidden="1">
+      <c r="A128" t="s">
+        <v>63</v>
+      </c>
+      <c r="B128" t="s">
+        <v>389</v>
+      </c>
+      <c r="C128"/>
+    </row>
+    <row r="129" spans="1:7" hidden="1">
+      <c r="A129" t="s">
+        <v>63</v>
+      </c>
+      <c r="B129" t="s">
+        <v>390</v>
+      </c>
+      <c r="C129" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" hidden="1">
+      <c r="B130" t="s">
+        <v>374</v>
+      </c>
+      <c r="C130" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" hidden="1">
+      <c r="A131" t="s">
+        <v>37</v>
+      </c>
+      <c r="B131" t="s">
+        <v>334</v>
+      </c>
+      <c r="C131"/>
+    </row>
+    <row r="132" spans="1:7" hidden="1">
+      <c r="A132" t="s">
+        <v>37</v>
+      </c>
+      <c r="B132" t="s">
+        <v>231</v>
+      </c>
+      <c r="C132" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" hidden="1">
+      <c r="A133" t="s">
+        <v>37</v>
+      </c>
+      <c r="B133" t="s">
+        <v>241</v>
+      </c>
+      <c r="C133" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" hidden="1">
+      <c r="A134" t="s">
+        <v>37</v>
+      </c>
+      <c r="B134" t="s">
+        <v>395</v>
+      </c>
+      <c r="C134" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" hidden="1">
+      <c r="A135" t="s">
+        <v>37</v>
+      </c>
+      <c r="B135" t="s">
+        <v>397</v>
+      </c>
+      <c r="C135" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" s="4" customFormat="1" hidden="1">
+      <c r="A136" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="G136" s="6"/>
+    </row>
+    <row r="137" spans="1:7" hidden="1">
+      <c r="A137" t="s">
+        <v>37</v>
+      </c>
+      <c r="B137" t="s">
+        <v>402</v>
+      </c>
+      <c r="C137" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" hidden="1">
+      <c r="A138" t="s">
+        <v>37</v>
+      </c>
+      <c r="B138" t="s">
+        <v>404</v>
+      </c>
+      <c r="C138" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" hidden="1">
+      <c r="A139" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" hidden="1">
+      <c r="A140" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" hidden="1">
+      <c r="A141" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" hidden="1">
+      <c r="A142" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" hidden="1">
+      <c r="A143" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" hidden="1">
+      <c r="A144" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" hidden="1">
+      <c r="A145" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" hidden="1">
+      <c r="A146" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="57.75" hidden="1">
+      <c r="A147" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="G147" s="16" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" hidden="1">
+      <c r="A148" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" hidden="1">
+      <c r="A149" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" hidden="1">
+      <c r="A150" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" hidden="1">
+      <c r="A151" t="s">
+        <v>100</v>
+      </c>
+      <c r="B151" t="s">
+        <v>275</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D151" t="s">
+        <v>427</v>
+      </c>
+      <c r="E151" t="s">
+        <v>428</v>
+      </c>
+      <c r="F151" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" hidden="1">
+      <c r="A152" t="s">
+        <v>100</v>
+      </c>
+      <c r="B152" t="s">
+        <v>429</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D152" t="s">
+        <v>431</v>
+      </c>
+      <c r="F152" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" hidden="1">
+      <c r="A153" t="s">
+        <v>100</v>
+      </c>
+      <c r="B153" t="s">
+        <v>231</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F153" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" hidden="1">
+      <c r="A154" t="s">
+        <v>100</v>
+      </c>
+      <c r="B154" t="s">
+        <v>434</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="F154" t="s">
+        <v>129</v>
+      </c>
+      <c r="G154" s="16" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" hidden="1">
+      <c r="A155" t="s">
+        <v>100</v>
+      </c>
+      <c r="B155" t="s">
+        <v>280</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F155" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" hidden="1">
+      <c r="A156" t="s">
+        <v>100</v>
+      </c>
+      <c r="B156" t="s">
+        <v>282</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F156" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" hidden="1">
+      <c r="A157" t="s">
+        <v>100</v>
+      </c>
+      <c r="B157" t="s">
+        <v>284</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F157" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" hidden="1">
+      <c r="A158" t="s">
+        <v>105</v>
+      </c>
+      <c r="B158" t="s">
+        <v>437</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" hidden="1">
+      <c r="A159" t="s">
+        <v>105</v>
+      </c>
+      <c r="B159" t="s">
+        <v>246</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" hidden="1">
+      <c r="A160" t="s">
+        <v>105</v>
+      </c>
+      <c r="B160" t="s">
+        <v>440</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" hidden="1">
+      <c r="A161" t="s">
+        <v>105</v>
+      </c>
+      <c r="B161" t="s">
+        <v>442</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" hidden="1">
+      <c r="A162" t="s">
+        <v>105</v>
+      </c>
+      <c r="B162" t="s">
+        <v>444</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" hidden="1">
+      <c r="A163" t="s">
+        <v>105</v>
+      </c>
+      <c r="B163" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" hidden="1">
+      <c r="A164" t="s">
+        <v>105</v>
+      </c>
+      <c r="B164" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" hidden="1">
+      <c r="A165" t="s">
+        <v>28</v>
+      </c>
+      <c r="B165" t="s">
+        <v>448</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="F165" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" hidden="1">
+      <c r="A166" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B108" t="s">
-        <v>364</v>
-      </c>
-      <c r="C108" t="s">
-        <v>365</v>
-      </c>
-      <c r="F108" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109" t="s">
-        <v>42</v>
-      </c>
-      <c r="B109" t="s">
-        <v>367</v>
-      </c>
-      <c r="C109" t="s">
-        <v>368</v>
-      </c>
-      <c r="F109" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110" t="s">
-        <v>42</v>
-      </c>
-      <c r="B110" t="s">
-        <v>369</v>
-      </c>
-      <c r="C110" t="s">
-        <v>370</v>
-      </c>
-      <c r="F110" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="60">
-      <c r="A111" t="s">
-        <v>42</v>
-      </c>
-      <c r="B111" t="s">
-        <v>344</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112" t="s">
-        <v>42</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="C112" t="s">
-        <v>375</v>
-      </c>
-      <c r="D112" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
-      <c r="A113" t="s">
-        <v>42</v>
-      </c>
-      <c r="B113" t="s">
-        <v>286</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
-      <c r="A114" t="s">
-        <v>42</v>
-      </c>
-      <c r="B114" t="s">
-        <v>288</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10">
-      <c r="A115" t="s">
-        <v>42</v>
-      </c>
-      <c r="B115" t="s">
-        <v>290</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
-      <c r="A116" t="s">
-        <v>28</v>
-      </c>
-      <c r="B116" t="s">
-        <v>0</v>
-      </c>
-      <c r="C116" t="s">
-        <v>376</v>
-      </c>
-      <c r="F116" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10">
-      <c r="A117" t="s">
-        <v>28</v>
-      </c>
-      <c r="B117" t="s">
-        <v>377</v>
-      </c>
-      <c r="C117" t="s">
-        <v>378</v>
-      </c>
-      <c r="F117" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
-      <c r="A118" t="s">
-        <v>28</v>
-      </c>
-      <c r="B118" t="s">
-        <v>379</v>
-      </c>
-      <c r="C118" t="s">
-        <v>380</v>
-      </c>
-      <c r="F118" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
-      <c r="A119" t="s">
-        <v>64</v>
-      </c>
-      <c r="B119" t="s">
-        <v>382</v>
-      </c>
-      <c r="C119" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10">
-      <c r="A120" t="s">
-        <v>64</v>
-      </c>
-      <c r="B120" t="s">
-        <v>384</v>
-      </c>
-      <c r="C120"/>
-    </row>
-    <row r="121" spans="1:10">
-      <c r="A121" t="s">
-        <v>64</v>
-      </c>
-      <c r="B121" t="s">
-        <v>286</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F121" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
-      <c r="A122" t="s">
-        <v>64</v>
-      </c>
-      <c r="B122" t="s">
-        <v>288</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="F122" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
-      <c r="A123" t="s">
-        <v>64</v>
-      </c>
-      <c r="B123" t="s">
-        <v>290</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F123" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
-      <c r="B124" t="s">
-        <v>387</v>
-      </c>
-      <c r="C124" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
-      <c r="A125" t="s">
-        <v>74</v>
-      </c>
-      <c r="B125" t="s">
-        <v>143</v>
-      </c>
-      <c r="C125"/>
-      <c r="F125" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10">
-      <c r="A126" t="s">
-        <v>74</v>
-      </c>
-      <c r="B126" t="s">
-        <v>140</v>
-      </c>
-      <c r="C126"/>
-      <c r="F126" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10">
-      <c r="A127" t="s">
-        <v>74</v>
-      </c>
-      <c r="B127" t="s">
-        <v>192</v>
-      </c>
-      <c r="C127" t="s">
-        <v>389</v>
-      </c>
-      <c r="F127" t="s">
-        <v>170</v>
-      </c>
-      <c r="J127" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10">
-      <c r="A128" t="s">
-        <v>74</v>
-      </c>
-      <c r="B128" t="s">
-        <v>194</v>
-      </c>
-      <c r="C128" t="s">
-        <v>390</v>
-      </c>
-      <c r="F128" t="s">
-        <v>170</v>
-      </c>
-      <c r="J128" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="A129" t="s">
-        <v>74</v>
-      </c>
-      <c r="B129" t="s">
-        <v>392</v>
-      </c>
-      <c r="C129" t="s">
-        <v>393</v>
-      </c>
-      <c r="F129" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130" t="s">
-        <v>69</v>
-      </c>
-      <c r="B130" t="s">
-        <v>394</v>
-      </c>
-      <c r="C130"/>
-      <c r="F130" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131" t="s">
-        <v>69</v>
-      </c>
-      <c r="B131" t="s">
-        <v>395</v>
-      </c>
-      <c r="C131"/>
-      <c r="F131" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132" t="s">
-        <v>69</v>
-      </c>
-      <c r="B132" t="s">
-        <v>396</v>
-      </c>
-      <c r="C132"/>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133" t="s">
-        <v>69</v>
-      </c>
-      <c r="B133" t="s">
-        <v>397</v>
-      </c>
-      <c r="C133" t="s">
-        <v>398</v>
-      </c>
-      <c r="G133" s="16" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134" t="s">
-        <v>69</v>
-      </c>
-      <c r="B134" t="s">
-        <v>400</v>
-      </c>
-      <c r="C134" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="A135" t="s">
-        <v>69</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="C135"/>
-    </row>
-    <row r="136" spans="1:7">
-      <c r="A136" t="s">
-        <v>69</v>
-      </c>
-      <c r="B136" t="s">
-        <v>403</v>
-      </c>
-      <c r="C136"/>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="A137" t="s">
-        <v>69</v>
-      </c>
-      <c r="B137" t="s">
-        <v>404</v>
-      </c>
-      <c r="C137" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="B138" t="s">
-        <v>387</v>
-      </c>
-      <c r="C138" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139" t="s">
-        <v>37</v>
-      </c>
-      <c r="B139" t="s">
-        <v>344</v>
-      </c>
-      <c r="C139"/>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="A140" t="s">
-        <v>37</v>
-      </c>
-      <c r="B140" t="s">
-        <v>0</v>
-      </c>
-      <c r="C140" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="A141" t="s">
-        <v>37</v>
-      </c>
-      <c r="B141" t="s">
-        <v>247</v>
-      </c>
-      <c r="C141" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="A142" t="s">
-        <v>37</v>
-      </c>
-      <c r="B142" t="s">
-        <v>409</v>
-      </c>
-      <c r="C142" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
-      <c r="A143" t="s">
-        <v>37</v>
-      </c>
-      <c r="B143" t="s">
-        <v>411</v>
-      </c>
-      <c r="C143" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" s="4" customFormat="1">
-      <c r="A144" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="G144" s="6"/>
-    </row>
-    <row r="145" spans="1:7">
-      <c r="A145" t="s">
-        <v>37</v>
-      </c>
-      <c r="B145" t="s">
-        <v>416</v>
-      </c>
-      <c r="C145" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
-      <c r="A146" t="s">
-        <v>37</v>
-      </c>
-      <c r="B146" t="s">
-        <v>418</v>
-      </c>
-      <c r="C146" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
-      <c r="A147" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="A148" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="A150" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="A151" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="A154" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="60">
-      <c r="A155" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="G155" s="16" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="A156" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="A158" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
-      <c r="A159" t="s">
-        <v>107</v>
-      </c>
-      <c r="B159" t="s">
-        <v>281</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D159" t="s">
-        <v>441</v>
-      </c>
-      <c r="E159" t="s">
-        <v>442</v>
-      </c>
-      <c r="F159" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
-      <c r="A160" t="s">
-        <v>107</v>
-      </c>
-      <c r="B160" t="s">
-        <v>443</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="D160" t="s">
-        <v>445</v>
-      </c>
-      <c r="F160" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
-      <c r="A161" t="s">
-        <v>107</v>
-      </c>
-      <c r="B161" t="s">
-        <v>0</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="F161" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
-      <c r="A162" t="s">
-        <v>107</v>
-      </c>
-      <c r="B162" t="s">
-        <v>448</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="F162" t="s">
-        <v>136</v>
-      </c>
-      <c r="G162" s="16" t="s">
+      <c r="B166" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="29.25" hidden="1">
+      <c r="A167" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B167" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="163" spans="1:7">
-      <c r="A163" t="s">
-        <v>107</v>
-      </c>
-      <c r="B163" t="s">
-        <v>286</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F163" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
-      <c r="A164" t="s">
-        <v>107</v>
-      </c>
-      <c r="B164" t="s">
-        <v>288</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="F164" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
-      <c r="A165" t="s">
-        <v>107</v>
-      </c>
-      <c r="B165" t="s">
-        <v>290</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F165" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
-      <c r="A166" t="s">
-        <v>112</v>
-      </c>
-      <c r="B166" t="s">
+      <c r="C167" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="E167" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167" t="s">
-        <v>112</v>
-      </c>
-      <c r="B167" t="s">
-        <v>170</v>
-      </c>
-      <c r="C167" s="1" t="s">
+      <c r="G167" s="16" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
-      <c r="A168" t="s">
-        <v>112</v>
-      </c>
-      <c r="B168" t="s">
-        <v>454</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" t="s">
-        <v>112</v>
-      </c>
-      <c r="B169" t="s">
-        <v>456</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="A170" t="s">
-        <v>112</v>
-      </c>
-      <c r="B170" t="s">
-        <v>458</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="A171" t="s">
-        <v>112</v>
-      </c>
-      <c r="B171" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="A172" t="s">
-        <v>112</v>
-      </c>
-      <c r="B172" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
-      <c r="A173" t="s">
-        <v>28</v>
-      </c>
-      <c r="B173" t="s">
-        <v>462</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="F173" t="s">
-        <v>127</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J112">
-    <sortCondition ref="A2:A112"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J107">
+    <sortCondition ref="A2:A107"/>
   </sortState>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1" xr:uid="{EAF3A632-FFC2-461F-8E3C-46D4F5CA1EA8}"/>
@@ -9862,55 +9741,55 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="3" t="s">
-        <v>128</v>
+        <v>454</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>137</v>
+        <v>455</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>134</v>
+        <v>456</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>125</v>
+        <v>457</v>
       </c>
       <c r="E1" s="31" t="s">
+        <v>458</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>459</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="K1" t="s">
+        <v>462</v>
+      </c>
+      <c r="M1" t="s">
+        <v>463</v>
+      </c>
+      <c r="N1" t="s">
         <v>464</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="P1" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="G1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="K1" t="s">
+      <c r="R1" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="M1" t="s">
+      <c r="S1" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="N1" t="s">
+      <c r="T1" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -10073,7 +9952,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>480</v>
@@ -10112,7 +9991,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>481</v>
@@ -10149,7 +10028,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>482</v>
@@ -10186,7 +10065,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>483</v>
@@ -10699,7 +10578,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="12" t="s">
-        <v>134</v>
+        <v>456</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>588</v>
@@ -11103,234 +10982,234 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>292</v>
+        <v>689</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>240</v>
+        <v>690</v>
       </c>
       <c r="D1" t="s">
-        <v>244</v>
+        <v>691</v>
       </c>
       <c r="E1" t="s">
-        <v>247</v>
+        <v>692</v>
       </c>
       <c r="F1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="B2" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D2" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C3" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D3" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
+        <v>699</v>
+      </c>
+      <c r="C4" t="s">
         <v>695</v>
       </c>
-      <c r="C4" t="s">
-        <v>691</v>
-      </c>
       <c r="D4" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C5" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D5" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="F5" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C6" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D6" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C7" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D7" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C8" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D8" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
+        <v>709</v>
+      </c>
+      <c r="C9" t="s">
         <v>705</v>
       </c>
-      <c r="C9" t="s">
-        <v>701</v>
-      </c>
       <c r="D9" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C10" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D10" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C11" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D11" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C12" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D12" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C13" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D13" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C14" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D14" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C15" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D15" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C16" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D16" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C17" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D17" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C18" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D18" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C19" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D19" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C20" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D20" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -11363,10 +11242,10 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="28" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C1" s="40"/>
       <c r="D1" s="40"/>
@@ -11377,353 +11256,353 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="29" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C2" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D2" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="29" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B3" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C3" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D3" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H3" s="25"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="29" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B4" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C4" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D4" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="E4" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F4" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="G4" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="H4" s="25"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="29" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B5" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="H5" s="25"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="29" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B6" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C6" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D6" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="H6" s="25"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="29" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B7" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C7" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D7" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="E7" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="H7" s="25"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="29" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B8" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C8" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D8" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="H8" s="25"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="29" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B9" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C9" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H9" s="25"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="29" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B10" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C10" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D10" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="H10" s="25"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="29" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B11" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C11" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="D11" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="H11" s="25"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="29" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B12" t="s">
+        <v>736</v>
+      </c>
+      <c r="C12" t="s">
+        <v>739</v>
+      </c>
+      <c r="D12" t="s">
+        <v>740</v>
+      </c>
+      <c r="E12" t="s">
+        <v>724</v>
+      </c>
+      <c r="F12" t="s">
+        <v>731</v>
+      </c>
+      <c r="G12" t="s">
         <v>732</v>
-      </c>
-      <c r="C12" t="s">
-        <v>735</v>
-      </c>
-      <c r="D12" t="s">
-        <v>736</v>
-      </c>
-      <c r="E12" t="s">
-        <v>720</v>
-      </c>
-      <c r="F12" t="s">
-        <v>727</v>
-      </c>
-      <c r="G12" t="s">
-        <v>728</v>
       </c>
       <c r="H12" s="25"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="29" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B13" t="s">
+        <v>736</v>
+      </c>
+      <c r="C13" t="s">
+        <v>739</v>
+      </c>
+      <c r="D13" t="s">
+        <v>740</v>
+      </c>
+      <c r="E13" t="s">
+        <v>724</v>
+      </c>
+      <c r="F13" t="s">
+        <v>731</v>
+      </c>
+      <c r="G13" t="s">
         <v>732</v>
-      </c>
-      <c r="C13" t="s">
-        <v>735</v>
-      </c>
-      <c r="D13" t="s">
-        <v>736</v>
-      </c>
-      <c r="E13" t="s">
-        <v>720</v>
-      </c>
-      <c r="F13" t="s">
-        <v>727</v>
-      </c>
-      <c r="G13" t="s">
-        <v>728</v>
       </c>
       <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="29" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B14" t="s">
+        <v>736</v>
+      </c>
+      <c r="C14" t="s">
+        <v>739</v>
+      </c>
+      <c r="D14" t="s">
+        <v>738</v>
+      </c>
+      <c r="E14" t="s">
+        <v>741</v>
+      </c>
+      <c r="F14" t="s">
+        <v>724</v>
+      </c>
+      <c r="G14" t="s">
         <v>732</v>
       </c>
-      <c r="C14" t="s">
-        <v>735</v>
-      </c>
-      <c r="D14" t="s">
-        <v>734</v>
-      </c>
-      <c r="E14" t="s">
-        <v>737</v>
-      </c>
-      <c r="F14" t="s">
-        <v>720</v>
-      </c>
-      <c r="G14" t="s">
-        <v>728</v>
-      </c>
       <c r="H14" s="25" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="29" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B15" t="s">
+        <v>736</v>
+      </c>
+      <c r="C15" t="s">
+        <v>739</v>
+      </c>
+      <c r="D15" t="s">
+        <v>738</v>
+      </c>
+      <c r="E15" t="s">
+        <v>724</v>
+      </c>
+      <c r="F15" t="s">
+        <v>742</v>
+      </c>
+      <c r="G15" t="s">
         <v>732</v>
-      </c>
-      <c r="C15" t="s">
-        <v>735</v>
-      </c>
-      <c r="D15" t="s">
-        <v>734</v>
-      </c>
-      <c r="E15" t="s">
-        <v>720</v>
-      </c>
-      <c r="F15" t="s">
-        <v>738</v>
-      </c>
-      <c r="G15" t="s">
-        <v>728</v>
       </c>
       <c r="H15" s="25"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="29" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B16" t="s">
+        <v>736</v>
+      </c>
+      <c r="C16" t="s">
+        <v>739</v>
+      </c>
+      <c r="D16" t="s">
+        <v>738</v>
+      </c>
+      <c r="E16" t="s">
+        <v>724</v>
+      </c>
+      <c r="F16" t="s">
+        <v>742</v>
+      </c>
+      <c r="G16" t="s">
         <v>732</v>
-      </c>
-      <c r="C16" t="s">
-        <v>735</v>
-      </c>
-      <c r="D16" t="s">
-        <v>734</v>
-      </c>
-      <c r="E16" t="s">
-        <v>720</v>
-      </c>
-      <c r="F16" t="s">
-        <v>738</v>
-      </c>
-      <c r="G16" t="s">
-        <v>728</v>
       </c>
       <c r="H16" s="25"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="29" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="B17" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C17" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="E17" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="H17" s="25"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="29" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B18" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C18" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H18" s="25"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="29" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B19" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C19" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D19" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="29" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="B20" t="s">
+        <v>736</v>
+      </c>
+      <c r="C20" t="s">
+        <v>739</v>
+      </c>
+      <c r="D20" t="s">
+        <v>738</v>
+      </c>
+      <c r="E20" t="s">
+        <v>741</v>
+      </c>
+      <c r="F20" t="s">
+        <v>724</v>
+      </c>
+      <c r="G20" t="s">
         <v>732</v>
       </c>
-      <c r="C20" t="s">
-        <v>735</v>
-      </c>
-      <c r="D20" t="s">
-        <v>734</v>
-      </c>
-      <c r="E20" t="s">
-        <v>737</v>
-      </c>
-      <c r="F20" t="s">
-        <v>720</v>
-      </c>
-      <c r="G20" t="s">
-        <v>728</v>
-      </c>
       <c r="H20" s="25" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="30" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="26"/>
@@ -11741,21 +11620,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D1F78A46A5B61544A3F5E5F9D558353B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd5889db134979e54dcf054cdc4727ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a7019f60-298e-442e-b6f6-687001478962" xmlns:ns3="244a3a2d-c3b8-4eaa-9334-4c3b8cbc7cc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fdf5543a8e45e11fa247a01810ff6e7b" ns2:_="" ns3:_="">
     <xsd:import namespace="a7019f60-298e-442e-b6f6-687001478962"/>
@@ -11956,14 +11820,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51BB428E-D1CA-47E8-B784-F33B49A13D8D}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
 </file>
--- a/data/input/Low Level Field Detail Design(6).xlsx
+++ b/data/input/Low Level Field Detail Design(6).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgroupcloud.sharepoint.com/teams/CampaignManagementTransformation/Shared Documents/ROI and Attribution/Data Engineering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86C46C64-67AF-466A-917F-2A8852E2A9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB48945F-A91D-44AD-9ABB-43DC99024615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Interaction Types" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Attributes!$A$1:$J$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Attributes!$A$1:$J$164</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Channels!$A$1:$F$20</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -119,7 +119,7 @@
     See comment on product family</t>
       </text>
     </comment>
-    <comment ref="C93" authorId="6" shapeId="0" xr:uid="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
+    <comment ref="C91" authorId="6" shapeId="0" xr:uid="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="744">
   <si>
     <t>Name</t>
   </si>
@@ -973,7 +973,7 @@
     <t>???_owner</t>
   </si>
   <si>
-    <t>product_family</t>
+    <t>product_id</t>
   </si>
   <si>
     <t>Identifies the Product the Campaign Is Targeting</t>
@@ -1383,9 +1383,6 @@
     <t>* Should this differentiate the asset or be on the activity, Or actual a sub Object.</t>
   </si>
   <si>
-    <t>product_id</t>
-  </si>
-  <si>
     <t>Links to the product or product family that this asset is promoting.</t>
   </si>
   <si>
@@ -1425,28 +1422,19 @@
     <t>Unique Friendly name of the order, May be a concatenation of product, Time and company.</t>
   </si>
   <si>
-    <t>Which Product Family the product being sold in the order belongs to.</t>
+    <t>Which particular product was being sold in the order. *It might be actual we relate the order to a more complex product table depending on how the source data is structured</t>
+  </si>
+  <si>
+    <t>FK -&gt; Product.product_id</t>
+  </si>
+  <si>
+    <t>action_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In what part of the customer lifecycle is this order, what is its context based on current  company status. </t>
   </si>
   <si>
     <t>String Enum</t>
-  </si>
-  <si>
-    <t>product_group</t>
-  </si>
-  <si>
-    <t>Which product group the product being sold in the order belongs to.</t>
-  </si>
-  <si>
-    <t>product</t>
-  </si>
-  <si>
-    <t>Which particular product was being sold in the order. *It might be actual we relate the order to a more complex product table depending on how the source data is structured</t>
-  </si>
-  <si>
-    <t>action_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In what part of the customer lifecycle is this order, what is its context based on current  company status. </t>
   </si>
   <si>
     <t>"No Action", "Cease", "Modify", "Provide", "Mixed"</t>
@@ -1786,9 +1774,6 @@
   </si>
   <si>
     <t>Identifes the specific product that this change referers to.</t>
-  </si>
-  <si>
-    <t>Identifies the specific product family that this change refers to.</t>
   </si>
   <si>
     <t>sales_order_value_change</t>
@@ -6387,16 +6372,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D396AB2F-F9BE-4F78-8BC5-51EC98BD60B1}" name="Table1" displayName="Table1" ref="A1:J167" totalsRowShown="0">
-  <autoFilter ref="A1:J167" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
-    <filterColumn colId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D396AB2F-F9BE-4F78-8BC5-51EC98BD60B1}" name="Table1" displayName="Table1" ref="A1:J164" totalsRowShown="0">
+  <autoFilter ref="A1:J164" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Orders"/>
+        <filter val="product"/>
+        <filter val="product_family"/>
+        <filter val="product_id"/>
+        <filter val="product_parent_id"/>
+        <filter val="product_price_type"/>
+        <filter val="product_quantity"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J165">
-    <sortCondition ref="A1:A165"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J162">
+    <sortCondition ref="A1:A162"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{FA10E4DE-EA14-4D6D-B2DE-B36300D4BF76}" name="Object" dataDxfId="2"/>
@@ -6788,7 +6778,7 @@
   <threadedComment ref="B61" dT="2025-03-07T22:24:32.38" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{3477900C-1235-4AD9-B6B9-B36EBE216470}" parentId="{8497C7DA-1239-4373-88D7-CCD3FD1374B1}">
     <text>See comment on product family</text>
   </threadedComment>
-  <threadedComment ref="C93" dT="2025-03-06T16:36:49.39" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
+  <threadedComment ref="C91" dT="2025-03-06T16:36:49.39" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
     <text xml:space="preserve">@David Irvine 
 example please . is it a available field in existing Marketo Activities?
 </text>
@@ -7027,7 +7017,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="101.25">
+    <row r="7" spans="1:13" ht="105">
       <c r="A7" s="34" t="s">
         <v>42</v>
       </c>
@@ -7240,7 +7230,7 @@
       </c>
       <c r="G13">
         <f>COUNTIF(Attributes!A:A,objects!A13)</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -7303,7 +7293,7 @@
       </c>
       <c r="G15">
         <f>COUNTIF(Attributes!A:A,objects!A15)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H15" t="s">
         <v>81</v>
@@ -7461,7 +7451,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:J164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -7769,7 +7759,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="43.5" hidden="1">
+    <row r="20" spans="1:7" ht="45" hidden="1">
       <c r="A20" t="s">
         <v>155</v>
       </c>
@@ -7986,7 +7976,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="57.75" hidden="1">
+    <row r="34" spans="1:7" ht="60" hidden="1">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -8042,7 +8032,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -8056,7 +8046,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="130.5" hidden="1">
+    <row r="39" spans="1:7" ht="135" hidden="1">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -8115,7 +8105,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="43.5" hidden="1">
+    <row r="43" spans="1:7" ht="45" hidden="1">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -8135,7 +8125,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="72.75" hidden="1">
+    <row r="44" spans="1:7" ht="75" hidden="1">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -8152,7 +8142,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="43.5" hidden="1">
+    <row r="45" spans="1:7" ht="45" hidden="1">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -8202,7 +8192,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="24.75" hidden="1">
+    <row r="49" spans="1:10" ht="27" hidden="1">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -8364,27 +8354,27 @@
         <v>274</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="57.75" hidden="1">
+    <row r="61" spans="1:10" ht="60">
       <c r="A61" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B61" t="s">
+        <v>220</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="D61" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="E61" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="F61" t="s">
         <v>222</v>
       </c>
       <c r="J61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="62" spans="1:10" hidden="1">
@@ -8392,10 +8382,10 @@
         <v>33</v>
       </c>
       <c r="B62" t="s">
+        <v>279</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -8405,10 +8395,10 @@
         <v>33</v>
       </c>
       <c r="B63" t="s">
+        <v>281</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -8418,26 +8408,26 @@
         <v>33</v>
       </c>
       <c r="B64" t="s">
+        <v>283</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" hidden="1">
       <c r="A65" t="s">
         <v>73</v>
       </c>
       <c r="B65" t="s">
+        <v>285</v>
+      </c>
+      <c r="C65" t="s">
         <v>286</v>
       </c>
-      <c r="C65" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
+    </row>
+    <row r="66" spans="1:10" hidden="1">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -8445,10 +8435,10 @@
         <v>231</v>
       </c>
       <c r="C66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J66" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -8459,170 +8449,167 @@
         <v>220</v>
       </c>
       <c r="C67" t="s">
+        <v>288</v>
+      </c>
+      <c r="F67" t="s">
         <v>289</v>
       </c>
-      <c r="F67" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
+    </row>
+    <row r="68" spans="1:10" hidden="1">
       <c r="A68" t="s">
         <v>73</v>
       </c>
       <c r="B68" t="s">
+        <v>290</v>
+      </c>
+      <c r="C68" t="s">
         <v>291</v>
       </c>
-      <c r="C68" t="s">
+      <c r="F68" t="s">
         <v>292</v>
       </c>
-      <c r="F68" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+      <c r="G68" s="16" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="45" hidden="1">
       <c r="A69" t="s">
         <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C69" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F69" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+        <v>292</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" hidden="1">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C70" t="s">
-        <v>296</v>
-      </c>
-      <c r="F70" t="s">
-        <v>290</v>
-      </c>
-      <c r="G70" s="16" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="43.5">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" hidden="1">
       <c r="A71" t="s">
         <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C71" t="s">
-        <v>299</v>
-      </c>
-      <c r="F71" t="s">
-        <v>290</v>
-      </c>
-      <c r="G71" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" hidden="1">
       <c r="A72" t="s">
         <v>73</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="C72" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+      <c r="C72"/>
+    </row>
+    <row r="73" spans="1:10" hidden="1">
       <c r="A73" t="s">
         <v>73</v>
       </c>
-      <c r="B73" t="s">
-        <v>303</v>
-      </c>
-      <c r="C73" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
+      <c r="B73" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C73"/>
+    </row>
+    <row r="74" spans="1:10" hidden="1">
       <c r="A74" t="s">
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C74"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" hidden="1">
       <c r="A75" t="s">
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C75"/>
     </row>
-    <row r="76" spans="1:10">
-      <c r="A76" t="s">
+    <row r="76" spans="1:10" hidden="1">
+      <c r="A76" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C76"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" hidden="1">
       <c r="A77" t="s">
         <v>73</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="C77"/>
-    </row>
-    <row r="78" spans="1:10">
+      <c r="B77" t="s">
+        <v>133</v>
+      </c>
+      <c r="C77" t="s">
+        <v>306</v>
+      </c>
+      <c r="F77" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" hidden="1">
       <c r="A78" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="C78"/>
-    </row>
-    <row r="79" spans="1:10">
+        <v>307</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="F78" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" hidden="1">
       <c r="A79" t="s">
         <v>73</v>
       </c>
       <c r="B79" t="s">
-        <v>133</v>
+        <v>309</v>
       </c>
       <c r="C79" t="s">
         <v>310</v>
       </c>
-      <c r="F79" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
-      <c r="A80" s="4" t="s">
+    </row>
+    <row r="80" spans="1:10" hidden="1">
+      <c r="A80" t="s">
         <v>73</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" t="s">
         <v>311</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>312</v>
       </c>
       <c r="F80" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" hidden="1">
       <c r="A81" t="s">
         <v>73</v>
       </c>
@@ -8632,60 +8619,60 @@
       <c r="C81" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="82" spans="1:10">
+      <c r="F81" t="s">
+        <v>315</v>
+      </c>
+      <c r="J81" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" hidden="1">
       <c r="A82" t="s">
         <v>73</v>
       </c>
       <c r="B82" t="s">
-        <v>315</v>
-      </c>
-      <c r="C82" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="F82" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
+      <c r="C82" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" hidden="1">
       <c r="A83" t="s">
         <v>73</v>
       </c>
       <c r="B83" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C83" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F83" t="s">
-        <v>319</v>
-      </c>
-      <c r="J83" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="A84" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" hidden="1">
+      <c r="A84" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B84" t="s">
-        <v>320</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="B84" s="4" t="s">
         <v>321</v>
       </c>
+      <c r="C84" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="J84" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" t="s">
+      <c r="A85" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B85" t="s">
-        <v>322</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="B85" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F85" t="s">
+      <c r="C85" s="4" t="s">
         <v>324</v>
       </c>
     </row>
@@ -8696,67 +8683,76 @@
       <c r="B86" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="J86" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+      <c r="C86" s="4"/>
+    </row>
+    <row r="87" spans="1:10" hidden="1">
       <c r="A87" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B87" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+    </row>
+    <row r="88" spans="1:10" hidden="1">
       <c r="A88" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B88" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="C88" s="4"/>
-    </row>
-    <row r="89" spans="1:10">
-      <c r="A89" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B89" s="4" t="s">
+    </row>
+    <row r="89" spans="1:10" hidden="1">
+      <c r="A89" t="s">
+        <v>42</v>
+      </c>
+      <c r="B89" t="s">
         <v>330</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="90" spans="1:10">
-      <c r="A90" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B90" s="4" t="s">
+      <c r="D89" t="s">
         <v>332</v>
       </c>
-      <c r="C90" s="4" t="s">
+    </row>
+    <row r="90" spans="1:10" hidden="1">
+      <c r="A90" t="s">
+        <v>42</v>
+      </c>
+      <c r="B90" t="s">
+        <v>179</v>
+      </c>
+      <c r="C90" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" hidden="1">
+      <c r="F90" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="45" hidden="1">
       <c r="A91" t="s">
         <v>42</v>
       </c>
       <c r="B91" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C91" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D91" t="s">
-        <v>336</v>
+        <v>337</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="F91" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="92" spans="1:10" hidden="1">
@@ -8764,33 +8760,21 @@
         <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C92" t="s">
-        <v>337</v>
-      </c>
-      <c r="F92" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="29.25" hidden="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" hidden="1">
       <c r="A93" t="s">
         <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C93" t="s">
-        <v>340</v>
-      </c>
-      <c r="D93" t="s">
-        <v>341</v>
-      </c>
-      <c r="E93" s="6" t="s">
         <v>342</v>
-      </c>
-      <c r="F93" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="94" spans="1:10" hidden="1">
@@ -8798,10 +8782,10 @@
         <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
-      </c>
-      <c r="C94" t="s">
-        <v>344</v>
+        <v>265</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:10" hidden="1">
@@ -8809,10 +8793,10 @@
         <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>345</v>
+        <v>231</v>
       </c>
       <c r="C95" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="96" spans="1:10" hidden="1">
@@ -8820,10 +8804,16 @@
         <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>265</v>
-      </c>
-      <c r="C96" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C96" t="s">
+        <v>346</v>
+      </c>
+      <c r="D96" t="s">
         <v>347</v>
+      </c>
+      <c r="E96" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="97" spans="1:6" hidden="1">
@@ -8831,9 +8821,15 @@
         <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>231</v>
+        <v>349</v>
       </c>
       <c r="C97" t="s">
+        <v>350</v>
+      </c>
+      <c r="D97" t="s">
+        <v>347</v>
+      </c>
+      <c r="E97" t="s">
         <v>348</v>
       </c>
     </row>
@@ -8842,16 +8838,10 @@
         <v>42</v>
       </c>
       <c r="B98" t="s">
-        <v>349</v>
-      </c>
-      <c r="C98" t="s">
-        <v>350</v>
-      </c>
-      <c r="D98" t="s">
-        <v>351</v>
-      </c>
-      <c r="E98" t="s">
-        <v>352</v>
+        <v>283</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:6" hidden="1">
@@ -8859,16 +8849,10 @@
         <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>353</v>
-      </c>
-      <c r="C99" t="s">
-        <v>354</v>
-      </c>
-      <c r="D99" t="s">
-        <v>351</v>
-      </c>
-      <c r="E99" t="s">
-        <v>352</v>
+        <v>281</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="100" spans="1:6" hidden="1">
@@ -8876,10 +8860,10 @@
         <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="101" spans="1:6" hidden="1">
@@ -8887,10 +8871,10 @@
         <v>42</v>
       </c>
       <c r="B101" t="s">
-        <v>282</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>283</v>
+        <v>185</v>
+      </c>
+      <c r="C101" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:6" hidden="1">
@@ -8898,10 +8882,10 @@
         <v>42</v>
       </c>
       <c r="B102" t="s">
-        <v>280</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>281</v>
+        <v>352</v>
+      </c>
+      <c r="C102" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="103" spans="1:6" hidden="1">
@@ -8909,10 +8893,13 @@
         <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>185</v>
+        <v>354</v>
       </c>
       <c r="C103" t="s">
         <v>355</v>
+      </c>
+      <c r="D103" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="104" spans="1:6" hidden="1">
@@ -8925,6 +8912,9 @@
       <c r="C104" t="s">
         <v>357</v>
       </c>
+      <c r="F104" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="105" spans="1:6" hidden="1">
       <c r="A105" t="s">
@@ -8936,36 +8926,36 @@
       <c r="C105" t="s">
         <v>359</v>
       </c>
-      <c r="D105" t="s">
-        <v>207</v>
+      <c r="F105" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="106" spans="1:6" hidden="1">
       <c r="A106" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B106" t="s">
+        <v>231</v>
+      </c>
+      <c r="C106" t="s">
         <v>360</v>
       </c>
-      <c r="C106" t="s">
-        <v>361</v>
-      </c>
       <c r="F106" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="107" spans="1:6" hidden="1">
       <c r="A107" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B107" t="s">
+        <v>361</v>
+      </c>
+      <c r="C107" t="s">
         <v>362</v>
       </c>
-      <c r="C107" t="s">
-        <v>363</v>
-      </c>
       <c r="F107" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
     </row>
     <row r="108" spans="1:6" hidden="1">
@@ -8973,52 +8963,47 @@
         <v>28</v>
       </c>
       <c r="B108" t="s">
-        <v>231</v>
+        <v>363</v>
       </c>
       <c r="C108" t="s">
         <v>364</v>
       </c>
       <c r="F108" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:6" hidden="1">
       <c r="A109" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B109" t="s">
-        <v>365</v>
+        <v>136</v>
       </c>
       <c r="C109" t="s">
         <v>366</v>
       </c>
-      <c r="F109" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="110" spans="1:6" hidden="1">
       <c r="A110" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B110" t="s">
         <v>367</v>
       </c>
-      <c r="C110" t="s">
-        <v>368</v>
-      </c>
-      <c r="F110" t="s">
-        <v>369</v>
-      </c>
+      <c r="C110"/>
     </row>
     <row r="111" spans="1:6" hidden="1">
       <c r="A111" t="s">
         <v>58</v>
       </c>
       <c r="B111" t="s">
-        <v>136</v>
-      </c>
-      <c r="C111" t="s">
-        <v>370</v>
+        <v>279</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F111" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="112" spans="1:6" hidden="1">
@@ -9026,58 +9011,59 @@
         <v>58</v>
       </c>
       <c r="B112" t="s">
-        <v>371</v>
-      </c>
-      <c r="C112"/>
+        <v>281</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F112" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="113" spans="1:10" hidden="1">
       <c r="A113" t="s">
         <v>58</v>
       </c>
       <c r="B113" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F113" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:10" hidden="1">
-      <c r="A114" t="s">
-        <v>58</v>
-      </c>
       <c r="B114" t="s">
-        <v>282</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="F114" t="s">
-        <v>159</v>
+        <v>370</v>
+      </c>
+      <c r="C114" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="115" spans="1:10" hidden="1">
       <c r="A115" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B115" t="s">
-        <v>284</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>285</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C115"/>
       <c r="F115" t="s">
-        <v>373</v>
+        <v>138</v>
       </c>
     </row>
     <row r="116" spans="1:10" hidden="1">
+      <c r="A116" t="s">
+        <v>68</v>
+      </c>
       <c r="B116" t="s">
-        <v>374</v>
-      </c>
-      <c r="C116" t="s">
-        <v>375</v>
+        <v>133</v>
+      </c>
+      <c r="C116"/>
+      <c r="F116" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="117" spans="1:10" hidden="1">
@@ -9085,11 +9071,16 @@
         <v>68</v>
       </c>
       <c r="B117" t="s">
-        <v>136</v>
-      </c>
-      <c r="C117"/>
+        <v>185</v>
+      </c>
+      <c r="C117" t="s">
+        <v>372</v>
+      </c>
       <c r="F117" t="s">
-        <v>138</v>
+        <v>163</v>
+      </c>
+      <c r="J117" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="118" spans="1:10" hidden="1">
@@ -9097,11 +9088,16 @@
         <v>68</v>
       </c>
       <c r="B118" t="s">
-        <v>133</v>
-      </c>
-      <c r="C118"/>
+        <v>187</v>
+      </c>
+      <c r="C118" t="s">
+        <v>373</v>
+      </c>
       <c r="F118" t="s">
-        <v>135</v>
+        <v>163</v>
+      </c>
+      <c r="J118" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="119" spans="1:10" hidden="1">
@@ -9109,47 +9105,37 @@
         <v>68</v>
       </c>
       <c r="B119" t="s">
-        <v>185</v>
+        <v>375</v>
       </c>
       <c r="C119" t="s">
         <v>376</v>
       </c>
       <c r="F119" t="s">
-        <v>163</v>
-      </c>
-      <c r="J119" t="s">
-        <v>279</v>
+        <v>129</v>
       </c>
     </row>
     <row r="120" spans="1:10" hidden="1">
       <c r="A120" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B120" t="s">
-        <v>187</v>
-      </c>
-      <c r="C120" t="s">
-        <v>377</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C120"/>
       <c r="F120" t="s">
-        <v>163</v>
-      </c>
-      <c r="J120" t="s">
-        <v>378</v>
+        <v>120</v>
       </c>
     </row>
     <row r="121" spans="1:10" hidden="1">
       <c r="A121" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B121" t="s">
-        <v>379</v>
-      </c>
-      <c r="C121" t="s">
-        <v>380</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="C121"/>
       <c r="F121" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="122" spans="1:10" hidden="1">
@@ -9157,23 +9143,22 @@
         <v>63</v>
       </c>
       <c r="B122" t="s">
-        <v>133</v>
+        <v>378</v>
       </c>
       <c r="C122"/>
-      <c r="F122" t="s">
-        <v>120</v>
-      </c>
     </row>
     <row r="123" spans="1:10" hidden="1">
       <c r="A123" t="s">
         <v>63</v>
       </c>
       <c r="B123" t="s">
+        <v>379</v>
+      </c>
+      <c r="C123" t="s">
+        <v>380</v>
+      </c>
+      <c r="G123" s="16" t="s">
         <v>381</v>
-      </c>
-      <c r="C123"/>
-      <c r="F123" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="124" spans="1:10" hidden="1">
@@ -9183,68 +9168,65 @@
       <c r="B124" t="s">
         <v>382</v>
       </c>
-      <c r="C124"/>
+      <c r="C124" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="125" spans="1:10" hidden="1">
       <c r="A125" t="s">
         <v>63</v>
       </c>
-      <c r="B125" t="s">
-        <v>383</v>
-      </c>
-      <c r="C125" t="s">
+      <c r="B125" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="G125" s="16" t="s">
-        <v>385</v>
-      </c>
+      <c r="C125"/>
     </row>
     <row r="126" spans="1:10" hidden="1">
       <c r="A126" t="s">
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>386</v>
-      </c>
-      <c r="C126" t="s">
-        <v>387</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="C126"/>
     </row>
     <row r="127" spans="1:10" hidden="1">
       <c r="A127" t="s">
         <v>63</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" t="s">
+        <v>386</v>
+      </c>
+      <c r="C127" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" hidden="1">
+      <c r="B128" t="s">
+        <v>370</v>
+      </c>
+      <c r="C128" t="s">
         <v>388</v>
       </c>
-      <c r="C127"/>
-    </row>
-    <row r="128" spans="1:10" hidden="1">
-      <c r="A128" t="s">
-        <v>63</v>
-      </c>
-      <c r="B128" t="s">
-        <v>389</v>
-      </c>
-      <c r="C128"/>
     </row>
     <row r="129" spans="1:7" hidden="1">
       <c r="A129" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="B129" t="s">
-        <v>390</v>
-      </c>
-      <c r="C129" t="s">
-        <v>391</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="C129"/>
     </row>
     <row r="130" spans="1:7" hidden="1">
+      <c r="A130" t="s">
+        <v>37</v>
+      </c>
       <c r="B130" t="s">
-        <v>374</v>
+        <v>231</v>
       </c>
       <c r="C130" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="131" spans="1:7" hidden="1">
@@ -9252,19 +9234,21 @@
         <v>37</v>
       </c>
       <c r="B131" t="s">
-        <v>334</v>
-      </c>
-      <c r="C131"/>
+        <v>241</v>
+      </c>
+      <c r="C131" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="132" spans="1:7" hidden="1">
       <c r="A132" t="s">
         <v>37</v>
       </c>
       <c r="B132" t="s">
-        <v>231</v>
+        <v>391</v>
       </c>
       <c r="C132" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="133" spans="1:7" hidden="1">
@@ -9272,83 +9256,86 @@
         <v>37</v>
       </c>
       <c r="B133" t="s">
-        <v>241</v>
+        <v>393</v>
       </c>
       <c r="C133" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1">
-      <c r="A134" t="s">
+    <row r="134" spans="1:7" s="4" customFormat="1" hidden="1">
+      <c r="A134" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="4" t="s">
         <v>396</v>
       </c>
+      <c r="D134" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="G134" s="6"/>
     </row>
     <row r="135" spans="1:7" hidden="1">
       <c r="A135" t="s">
         <v>37</v>
       </c>
       <c r="B135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C135" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" s="4" customFormat="1" hidden="1">
-      <c r="A136" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" hidden="1">
+      <c r="A136" t="s">
         <v>37</v>
       </c>
-      <c r="B136" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="C136" s="4" t="s">
+      <c r="B136" t="s">
         <v>400</v>
       </c>
-      <c r="D136" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E136" s="4" t="s">
+      <c r="C136" t="s">
         <v>401</v>
       </c>
-      <c r="G136" s="6"/>
     </row>
     <row r="137" spans="1:7" hidden="1">
-      <c r="A137" t="s">
-        <v>37</v>
-      </c>
-      <c r="B137" t="s">
+      <c r="A137" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C137" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="C137" t="s">
+    </row>
+    <row r="138" spans="1:7" hidden="1">
+      <c r="A138" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C138" s="5" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1">
-      <c r="A138" t="s">
-        <v>37</v>
-      </c>
-      <c r="B138" t="s">
-        <v>404</v>
-      </c>
-      <c r="C138" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" hidden="1">
+    <row r="139" spans="1:7">
       <c r="A139" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>345</v>
+        <v>220</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
+      </c>
+      <c r="F139" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="140" spans="1:7" hidden="1">
@@ -9356,10 +9343,10 @@
         <v>82</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>246</v>
+        <v>405</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:7" hidden="1">
@@ -9367,7 +9354,7 @@
         <v>82</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>293</v>
+        <v>407</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>408</v>
@@ -9378,10 +9365,10 @@
         <v>82</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>220</v>
+        <v>409</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:7" hidden="1">
@@ -9389,21 +9376,24 @@
         <v>82</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" hidden="1">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="60" hidden="1">
       <c r="A144" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
+      </c>
+      <c r="G144" s="16" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="145" spans="1:7" hidden="1">
@@ -9411,10 +9401,10 @@
         <v>82</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="146" spans="1:7" hidden="1">
@@ -9422,57 +9412,72 @@
         <v>82</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="57.75" hidden="1">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" hidden="1">
       <c r="A147" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>418</v>
+        <v>133</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="G147" s="16" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1">
-      <c r="A148" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B148" s="4" t="s">
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>100</v>
+      </c>
+      <c r="B148" t="s">
+        <v>220</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C148" s="5" t="s">
+      <c r="D148" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" hidden="1">
-      <c r="A149" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B149" s="4" t="s">
+      <c r="E148" t="s">
         <v>423</v>
       </c>
-      <c r="C149" s="5" t="s">
+      <c r="F148" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>100</v>
+      </c>
+      <c r="B149" t="s">
         <v>424</v>
       </c>
+      <c r="C149" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D149" t="s">
+        <v>426</v>
+      </c>
+      <c r="F149" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="150" spans="1:7" hidden="1">
-      <c r="A150" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>425</v>
+      <c r="A150" t="s">
+        <v>100</v>
+      </c>
+      <c r="B150" t="s">
+        <v>231</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F150" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="151" spans="1:7" hidden="1">
@@ -9480,19 +9485,16 @@
         <v>100</v>
       </c>
       <c r="B151" t="s">
-        <v>275</v>
+        <v>429</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="D151" t="s">
-        <v>427</v>
-      </c>
-      <c r="E151" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F151" t="s">
-        <v>120</v>
+        <v>129</v>
+      </c>
+      <c r="G151" s="16" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="152" spans="1:7" hidden="1">
@@ -9500,16 +9502,13 @@
         <v>100</v>
       </c>
       <c r="B152" t="s">
-        <v>429</v>
+        <v>279</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="D152" t="s">
-        <v>431</v>
+        <v>280</v>
       </c>
       <c r="F152" t="s">
-        <v>432</v>
+        <v>368</v>
       </c>
     </row>
     <row r="153" spans="1:7" hidden="1">
@@ -9517,10 +9516,10 @@
         <v>100</v>
       </c>
       <c r="B153" t="s">
-        <v>231</v>
+        <v>281</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>433</v>
+        <v>282</v>
       </c>
       <c r="F153" t="s">
         <v>159</v>
@@ -9531,58 +9530,46 @@
         <v>100</v>
       </c>
       <c r="B154" t="s">
-        <v>434</v>
+        <v>283</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>435</v>
+        <v>284</v>
       </c>
       <c r="F154" t="s">
-        <v>129</v>
-      </c>
-      <c r="G154" s="16" t="s">
-        <v>436</v>
+        <v>369</v>
       </c>
     </row>
     <row r="155" spans="1:7" hidden="1">
       <c r="A155" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B155" t="s">
-        <v>280</v>
+        <v>432</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="F155" t="s">
-        <v>372</v>
+        <v>433</v>
       </c>
     </row>
     <row r="156" spans="1:7" hidden="1">
       <c r="A156" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B156" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="F156" t="s">
-        <v>159</v>
+        <v>434</v>
       </c>
     </row>
     <row r="157" spans="1:7" hidden="1">
       <c r="A157" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B157" t="s">
-        <v>284</v>
+        <v>435</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F157" t="s">
-        <v>373</v>
+        <v>436</v>
       </c>
     </row>
     <row r="158" spans="1:7" hidden="1">
@@ -9601,10 +9588,10 @@
         <v>105</v>
       </c>
       <c r="B159" t="s">
-        <v>246</v>
+        <v>439</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="160" spans="1:7" hidden="1">
@@ -9612,9 +9599,6 @@
         <v>105</v>
       </c>
       <c r="B160" t="s">
-        <v>440</v>
-      </c>
-      <c r="C160" s="1" t="s">
         <v>441</v>
       </c>
     </row>
@@ -9625,79 +9609,49 @@
       <c r="B161" t="s">
         <v>442</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>443</v>
-      </c>
     </row>
     <row r="162" spans="1:7" hidden="1">
       <c r="A162" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="B162" t="s">
+        <v>443</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="F162" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" hidden="1">
+      <c r="A163" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B163" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="30" hidden="1">
+      <c r="A164" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B164" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" hidden="1">
-      <c r="A163" t="s">
-        <v>105</v>
-      </c>
-      <c r="B163" t="s">
+      <c r="C164" s="1" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" hidden="1">
-      <c r="A164" t="s">
-        <v>105</v>
-      </c>
-      <c r="B164" t="s">
+      <c r="E164" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" hidden="1">
-      <c r="A165" t="s">
-        <v>28</v>
-      </c>
-      <c r="B165" t="s">
+      <c r="G164" s="16" t="s">
         <v>448</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="F165" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" hidden="1">
-      <c r="A166" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B166" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="29.25" hidden="1">
-      <c r="A167" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B167" t="s">
-        <v>450</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E167" t="s">
-        <v>452</v>
-      </c>
-      <c r="G167" s="16" t="s">
-        <v>453</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J107">
-    <sortCondition ref="A2:A107"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J105">
+    <sortCondition ref="A2:A105"/>
   </sortState>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1" xr:uid="{EAF3A632-FFC2-461F-8E3C-46D4F5CA1EA8}"/>
@@ -9741,55 +9695,55 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>453</v>
+      </c>
+      <c r="F1" s="31" t="s">
         <v>454</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>458</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>459</v>
       </c>
       <c r="G1" t="s">
         <v>63</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="K1" t="s">
+        <v>457</v>
+      </c>
+      <c r="M1" t="s">
+        <v>458</v>
+      </c>
+      <c r="N1" t="s">
+        <v>459</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="K1" t="s">
+      <c r="R1" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="M1" t="s">
+      <c r="S1" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="N1" t="s">
+      <c r="T1" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -9800,10 +9754,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E2" s="31">
         <v>1</v>
@@ -9815,7 +9769,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="I2" s="3">
         <v>10</v>
@@ -9839,10 +9793,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="E3" s="31">
         <v>1</v>
@@ -9854,7 +9808,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="I3" s="3">
         <v>200</v>
@@ -9878,10 +9832,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E4" s="31">
         <v>2</v>
@@ -9891,7 +9845,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="I4" s="3">
         <v>15</v>
@@ -9915,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E5" s="31">
         <v>3</v>
@@ -9928,7 +9882,7 @@
         <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -9955,7 +9909,7 @@
         <v>73</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="E6" s="31">
         <v>4</v>
@@ -9967,7 +9921,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="I6" s="3">
         <v>0</v>
@@ -9994,7 +9948,7 @@
         <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="E7" s="31"/>
       <c r="F7" s="31">
@@ -10004,7 +9958,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="I7" s="3">
         <v>256</v>
@@ -10031,7 +9985,7 @@
         <v>73</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E8" s="31">
         <v>6</v>
@@ -10041,7 +9995,7 @@
         <v>7</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="I8" s="3">
         <v>24</v>
@@ -10068,7 +10022,7 @@
         <v>73</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E9" s="31"/>
       <c r="F9" s="31">
@@ -10078,7 +10032,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="I9" s="3">
         <v>51</v>
@@ -10117,78 +10071,78 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="10" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="11" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="D4" s="17"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="11" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="11" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="11" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="D7" s="17"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="10" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -10196,47 +10150,47 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D9" s="17"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="11" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D10" s="17"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="11" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="D11" s="17"/>
     </row>
     <row r="12" spans="1:4" ht="30">
       <c r="A12" s="11" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="D12" s="17"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="10" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -10244,724 +10198,724 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="11" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D14" s="17"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="11" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D15" s="17"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="11" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="11" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D17" s="17"/>
     </row>
     <row r="18" spans="1:6">
       <c r="E18" s="13" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="45">
       <c r="A19" s="12" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30">
       <c r="A20" s="12" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="60">
       <c r="A21" s="12" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30">
       <c r="A22" s="12" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="135">
       <c r="A23" s="12" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B23" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>539</v>
-      </c>
       <c r="E23" s="14" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="270">
       <c r="A24" s="12" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="75">
       <c r="A25" s="12" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="120">
       <c r="A26" s="12" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B26" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="C26" s="16" t="s">
         <v>547</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>552</v>
-      </c>
       <c r="E26" s="14" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="75">
       <c r="A27" s="12" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="75">
       <c r="A28" s="12" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="75">
       <c r="A29" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="75">
       <c r="A30" s="12" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="75">
       <c r="A31" s="12" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="45">
       <c r="A32" s="12" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="C32" s="19"/>
       <c r="E32" s="14" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30">
       <c r="A33" s="12" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30">
       <c r="A34" s="12" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="12" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="12" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="12" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B37" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="E37" s="14" t="s">
         <v>588</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>592</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>593</v>
-      </c>
       <c r="F37" s="8" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="12" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="12" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="45">
       <c r="A40" s="12" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="60">
       <c r="A41" s="12" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="60">
       <c r="A42" s="12" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="45">
       <c r="A43" s="12" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="30">
       <c r="A44" s="12" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="105">
       <c r="A45" s="12" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="45">
       <c r="A46" s="12" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B46" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="E46" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="E46" s="14" t="s">
-        <v>631</v>
-      </c>
       <c r="F46" s="8" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="30">
       <c r="A47" s="12" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="30">
       <c r="A48" s="12" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B48" s="23" t="s">
+        <v>629</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="F48" s="15" t="s">
         <v>634</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>638</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="12" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="12" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B50" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>641</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>645</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="60">
       <c r="A51" s="12" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="60">
       <c r="A52" s="12" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B52" s="23" t="s">
+        <v>643</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>647</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>648</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>652</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="12" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="165">
       <c r="A54" s="12" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="30">
       <c r="A55" s="12" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B55" s="23" t="s">
+        <v>654</v>
+      </c>
+      <c r="C55" s="16" t="s">
         <v>659</v>
       </c>
-      <c r="C55" s="16" t="s">
-        <v>664</v>
-      </c>
       <c r="E55" s="14" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="12" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="60">
       <c r="A57" s="12" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="60">
       <c r="A58" s="12" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="45">
       <c r="A59" s="12" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="45">
       <c r="A60" s="12" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="45">
       <c r="A61" s="12" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="B61" s="23" t="s">
+        <v>675</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>679</v>
+      </c>
+      <c r="F61" s="8" t="s">
         <v>680</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>684</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="45">
       <c r="A62" s="12" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -10982,234 +10936,234 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="D1" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="E1" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="F1" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="B2" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C2" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="D2" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C3" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="D3" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="C4" t="s">
+        <v>690</v>
+      </c>
+      <c r="D4" t="s">
         <v>695</v>
-      </c>
-      <c r="D4" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="C5" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="D5" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="F5" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C6" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="D6" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="C7" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D7" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="C8" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D8" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="C9" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D9" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="C10" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D10" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="C11" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D11" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="C12" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D12" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="C13" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D13" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C14" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D14" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="C15" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D15" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="C16" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D16" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C17" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D17" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="C18" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D18" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="C19" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D19" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="C20" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D20" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -11242,7 +11196,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="28" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="B1" s="39" t="s">
         <v>47</v>
@@ -11256,353 +11210,353 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="29" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="B2" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="C2" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="D2" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="29" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="B3" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="C3" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="D3" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="H3" s="25"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="29" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="B4" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C4" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D4" t="s">
+        <v>720</v>
+      </c>
+      <c r="E4" t="s">
+        <v>723</v>
+      </c>
+      <c r="F4" t="s">
+        <v>724</v>
+      </c>
+      <c r="G4" t="s">
         <v>725</v>
-      </c>
-      <c r="E4" t="s">
-        <v>728</v>
-      </c>
-      <c r="F4" t="s">
-        <v>729</v>
-      </c>
-      <c r="G4" t="s">
-        <v>730</v>
       </c>
       <c r="H4" s="25"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="29" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="B5" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="H5" s="25"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="29" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="B6" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="C6" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="D6" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="H6" s="25"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="29" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="B7" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="C7" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="D7" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="E7" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="H7" s="25"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="29" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="B8" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C8" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="D8" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="H8" s="25"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="29" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="B9" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C9" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="H9" s="25"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="29" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B10" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C10" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="D10" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="H10" s="25"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="29" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B11" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C11" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="D11" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="H11" s="25"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="29" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="B12" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C12" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D12" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="E12" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="F12" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="G12" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="H12" s="25"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="29" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="B13" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C13" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D13" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="E13" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="F13" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="G13" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="H13" s="25"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="29" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="B14" t="s">
+        <v>731</v>
+      </c>
+      <c r="C14" t="s">
+        <v>734</v>
+      </c>
+      <c r="D14" t="s">
+        <v>733</v>
+      </c>
+      <c r="E14" t="s">
         <v>736</v>
       </c>
-      <c r="C14" t="s">
-        <v>739</v>
-      </c>
-      <c r="D14" t="s">
-        <v>738</v>
-      </c>
-      <c r="E14" t="s">
-        <v>741</v>
-      </c>
       <c r="F14" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="G14" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="29" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="B15" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C15" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D15" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="E15" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="F15" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G15" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="H15" s="25"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="29" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="B16" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C16" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D16" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="E16" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="F16" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G16" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="H16" s="25"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="29" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B17" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C17" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="E17" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="H17" s="25"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="29" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B18" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C18" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="H18" s="25"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="29" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B19" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C19" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="D19" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="29" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="B20" t="s">
+        <v>731</v>
+      </c>
+      <c r="C20" t="s">
+        <v>734</v>
+      </c>
+      <c r="D20" t="s">
+        <v>733</v>
+      </c>
+      <c r="E20" t="s">
         <v>736</v>
       </c>
-      <c r="C20" t="s">
-        <v>739</v>
-      </c>
-      <c r="D20" t="s">
-        <v>738</v>
-      </c>
-      <c r="E20" t="s">
-        <v>741</v>
-      </c>
       <c r="F20" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="G20" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="30" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="26"/>
@@ -11620,6 +11574,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D1F78A46A5B61544A3F5E5F9D558353B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd5889db134979e54dcf054cdc4727ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a7019f60-298e-442e-b6f6-687001478962" xmlns:ns3="244a3a2d-c3b8-4eaa-9334-4c3b8cbc7cc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fdf5543a8e45e11fa247a01810ff6e7b" ns2:_="" ns3:_="">
     <xsd:import namespace="a7019f60-298e-442e-b6f6-687001478962"/>
@@ -11820,7 +11780,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -11829,20 +11789,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51BB428E-D1CA-47E8-B784-F33B49A13D8D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
 </file>
--- a/data/input/Low Level Field Detail Design(6).xlsx
+++ b/data/input/Low Level Field Detail Design(6).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29212"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgroupcloud.sharepoint.com/teams/CampaignManagementTransformation/Shared Documents/ROI and Attribution/Data Engineering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB48945F-A91D-44AD-9ABB-43DC99024615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E6729C6-65E5-484D-96B1-009B6DAB83A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="1" activeTab="4" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
   </bookViews>
   <sheets>
     <sheet name="objects" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,9 @@
     <sheet name="Interaction Types" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Attributes!$A$1:$J$164</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Channels!$A$1:$F$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Attributes!$A$1:$J$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Channels!$A$1:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">objects!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -119,7 +120,7 @@
     See comment on product family</t>
       </text>
     </comment>
-    <comment ref="C91" authorId="6" shapeId="0" xr:uid="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
+    <comment ref="C92" authorId="6" shapeId="0" xr:uid="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -134,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="792">
   <si>
     <t>Name</t>
   </si>
@@ -1635,12 +1636,6 @@
     <t>Identified the company that was targeted with the communication.</t>
   </si>
   <si>
-    <t>targeted_person_id</t>
-  </si>
-  <si>
-    <t>Identifies the person the marketing activity targeted.</t>
-  </si>
-  <si>
     <t>Name of the tool</t>
   </si>
   <si>
@@ -1698,25 +1693,70 @@
     <t>company_market_channel</t>
   </si>
   <si>
+    <t>Describes which business area in BT is responsible for marketing and sales to this account.</t>
+  </si>
+  <si>
+    <t>Different market channel may have different parameter rulesets.</t>
+  </si>
+  <si>
+    <t>A key filter in most dashboards as almost all audiences will care about only companis from a single group in this list.</t>
+  </si>
+  <si>
+    <t>SMB, CPS, Wholesale, Global</t>
+  </si>
+  <si>
     <t>company_business_type</t>
   </si>
   <si>
-    <t>Billing Account, CUG, WK</t>
-  </si>
-  <si>
-    <t>CUG, Billing Account, SAC, World Key</t>
+    <t>Describes the granularity/ Type of account at a size level. Also how BT thinks about this account. Used to understand the hierarchy.</t>
+  </si>
+  <si>
+    <t>Used as part of the linking strategy to understand how closely linked a marketing activity is to an outcome. We may look at the largest grain of company needed for form the link.</t>
+  </si>
+  <si>
+    <t>Not Relevant for analytics</t>
+  </si>
+  <si>
+    <t>CUG, Billing Account, SAC, World Key, LE</t>
   </si>
   <si>
     <t>owner_id</t>
   </si>
   <si>
-    <t>Who is the sales person assigned to manage this company as an account.</t>
+    <t>Who is the sales person assigned to manage this company as an account. There may be multiple or other roles associated with the account.</t>
+  </si>
+  <si>
+    <t>Not Used for modelling</t>
+  </si>
+  <si>
+    <t>Potentially supports the ability for users to filter down to only accounts they Owner / Another way to find relevant accounts.</t>
   </si>
   <si>
     <t>vertical</t>
   </si>
   <si>
+    <t>This is a placeholder for descriptive fields for the type of work this company does. We are looking for fields that would identify similar companies that might be expected to respond similarly to marketing or purchase similar products from BT</t>
+  </si>
+  <si>
+    <t>List of Values</t>
+  </si>
+  <si>
+    <t>Finacial Services, Healthcare, Retail,... (exact values dependant on the data)</t>
+  </si>
+  <si>
     <t>industry</t>
+  </si>
+  <si>
+    <t>This is a placeholder for descriptive fields for the type of work this company does. We are looking for fields that would identify similar companies that might be expected to respond similarly to marketing or purchase similar products from BT, This would be a more granular view of the same information as verticle. Could be SIC codes type information.</t>
+  </si>
+  <si>
+    <t>Not Used For modelling Currently, But could form an attribute for a algorithmic model</t>
+  </si>
+  <si>
+    <t>A dimension for filtering or comparison</t>
+  </si>
+  <si>
+    <t>"Customer-Data &amp; Personalisation (CDP/RT-CDP) Software", "AI-Driven Medical Imaging Diagnostics", "RegTech Compliance Automation Platforms"</t>
   </si>
   <si>
     <t>location</t>
@@ -1899,6 +1939,12 @@
     <t>Sythentic ID given to head tool</t>
   </si>
   <si>
+    <t>targeted_person_id</t>
+  </si>
+  <si>
+    <t>Identifies the person the marketing activity targeted.</t>
+  </si>
+  <si>
     <t>communication_mode</t>
   </si>
   <si>
@@ -1910,6 +1956,36 @@
   <si>
     <t>Push
 Pull</t>
+  </si>
+  <si>
+    <t>The friendly or offical name of the company.</t>
+  </si>
+  <si>
+    <t>Needed for selection of the company specific dashboard and as a dimension in some detailed breakdowns.</t>
+  </si>
+  <si>
+    <t>Clevertouch Consulting ltd</t>
+  </si>
+  <si>
+    <t>product_yca_tier</t>
+  </si>
+  <si>
+    <t>Identifiest the Tier of the product that is the closest common parent to the product of the order and the product of the Campaign or Asset.</t>
+  </si>
+  <si>
+    <t>Used as a paremeter to govern how much attribution is given to this link.</t>
+  </si>
+  <si>
+    <t>List of Values [Tiers}</t>
+  </si>
+  <si>
+    <t>company_yca_type</t>
+  </si>
+  <si>
+    <t>Gives the company_business_type of the closest common parent of the company the order was associated and the company assoicated to the activity.</t>
+  </si>
+  <si>
+    <t>List of value [Company Types]</t>
   </si>
   <si>
     <t>Activity ID</t>
@@ -5750,6 +5826,9 @@
     <t>Comment</t>
   </si>
   <si>
+    <t>Interaction Types</t>
+  </si>
+  <si>
     <t>Paid Digital Ads</t>
   </si>
   <si>
@@ -5759,12 +5838,21 @@
     <t>IP Inferred</t>
   </si>
   <si>
+    <t>Digital</t>
+  </si>
+  <si>
+    <t>Pull</t>
+  </si>
+  <si>
     <t>Content Syndication</t>
   </si>
   <si>
     <t>Audience Inferred</t>
   </si>
   <si>
+    <t>Digital?</t>
+  </si>
+  <si>
     <t>Web</t>
   </si>
   <si>
@@ -5774,6 +5862,9 @@
     <t>Above the Line - Non Digital</t>
   </si>
   <si>
+    <t>Physical</t>
+  </si>
+  <si>
     <t>Placeholder For multiple channels</t>
   </si>
   <si>
@@ -5789,12 +5880,18 @@
     <t>Known Person</t>
   </si>
   <si>
+    <t>Push</t>
+  </si>
+  <si>
     <t>Virtual Events</t>
   </si>
   <si>
     <t>Self Identified</t>
   </si>
   <si>
+    <t>Events</t>
+  </si>
+  <si>
     <t>F2F Events</t>
   </si>
   <si>
@@ -5822,6 +5919,18 @@
     <t>App Push Notification</t>
   </si>
   <si>
+    <t>Telemarketing</t>
+  </si>
+  <si>
+    <t>Conversation</t>
+  </si>
+  <si>
+    <t>Online Chat</t>
+  </si>
+  <si>
+    <t>Self Identified / IP Inferred</t>
+  </si>
+  <si>
     <t>Sales Meetings</t>
   </si>
   <si>
@@ -5834,9 +5943,36 @@
     <t>Sales Email</t>
   </si>
   <si>
+    <t>Inbound Calls</t>
+  </si>
+  <si>
     <t>Channel</t>
   </si>
   <si>
+    <t>Interactsion Concatnated</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Column5</t>
+  </si>
+  <si>
+    <t>Column6</t>
+  </si>
+  <si>
+    <t>Column7</t>
+  </si>
+  <si>
     <t>Viewed</t>
   </si>
   <si>
@@ -5909,10 +6045,19 @@
     <t>Engaged</t>
   </si>
   <si>
-    <t>Inbound Calls</t>
-  </si>
-  <si>
     <t>Called</t>
+  </si>
+  <si>
+    <t>Attempted</t>
+  </si>
+  <si>
+    <t>Conversed</t>
+  </si>
+  <si>
+    <t>Initiated</t>
+  </si>
+  <si>
+    <t>Disconnected</t>
   </si>
 </sst>
 </file>
@@ -6105,7 +6250,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -6143,56 +6288,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -6216,11 +6311,107 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6293,9 +6484,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -6312,20 +6500,84 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -6372,33 +6624,53 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D396AB2F-F9BE-4F78-8BC5-51EC98BD60B1}" name="Table1" displayName="Table1" ref="A1:J164" totalsRowShown="0">
-  <autoFilter ref="A1:J164" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
-    <filterColumn colId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D396AB2F-F9BE-4F78-8BC5-51EC98BD60B1}" name="Table1" displayName="Table1" ref="A1:J167" totalsRowShown="0">
+  <autoFilter ref="A1:J167" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
+    <filterColumn colId="0">
       <filters>
-        <filter val="product"/>
-        <filter val="product_family"/>
-        <filter val="product_id"/>
-        <filter val="product_parent_id"/>
-        <filter val="product_price_type"/>
-        <filter val="product_quantity"/>
+        <filter val="Attribution Linking Table"/>
+        <filter val="Company"/>
+        <filter val="Person Company Role"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J162">
-    <sortCondition ref="A1:A162"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J165">
+    <sortCondition ref="B1:B165"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{FA10E4DE-EA14-4D6D-B2DE-B36300D4BF76}" name="Object" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{FA10E4DE-EA14-4D6D-B2DE-B36300D4BF76}" name="Object" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{32E1B4A0-4AC4-478E-B858-9CDAC148562B}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{85FF24E0-DD58-4F79-B3D0-388BE33FFF38}" name="Description" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{85FF24E0-DD58-4F79-B3D0-388BE33FFF38}" name="Description" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{DDF2A8F8-D578-432C-9C8E-513579A7E305}" name="Purpose(modelling)"/>
     <tableColumn id="5" xr3:uid="{16FB7B03-B8ED-4DDE-99A6-CE5534013176}" name="Purpose(Analytics)"/>
     <tableColumn id="6" xr3:uid="{ED2E566B-7FFE-4EB2-A8E3-BAB3EAAF699B}" name="Format"/>
-    <tableColumn id="7" xr3:uid="{8529F2E9-FE33-49C3-9957-B17949619D35}" name="Example Values" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{8529F2E9-FE33-49C3-9957-B17949619D35}" name="Example Values" dataDxfId="4"/>
     <tableColumn id="8" xr3:uid="{6F705DBE-267C-4645-8C93-CB99BEC6A154}" name="Tokenised"/>
     <tableColumn id="9" xr3:uid="{193B0F12-7095-425B-833D-884F117D2CC8}" name="Tokenised Reason"/>
     <tableColumn id="10" xr3:uid="{D6E8B652-AD77-4FB5-BD6A-F4C444E11ED9}" name="Requirement"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D96477C-ECA9-4EBE-A35F-BB664900AC81}" name="Table2" displayName="Table2" ref="A1:J23" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:J23" xr:uid="{6D96477C-ECA9-4EBE-A35F-BB664900AC81}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{EACA768A-938B-44E7-89E1-1321528ABE92}" name="Channel" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{C41B0F01-37EC-4C6A-ABBC-015577D1F75A}" name="Interactsion Concatnated" dataDxfId="1">
+      <calculatedColumnFormula>_xlfn.TEXTJOIN(";",TRUE,C2:I2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{329D1A88-3265-4F13-8A3B-7827457D6F32}" name="Interactions"/>
+    <tableColumn id="4" xr3:uid="{1A3012FB-7917-49D1-90EF-600C1CB8AF3D}" name="Column1"/>
+    <tableColumn id="5" xr3:uid="{B6D0889D-ECB5-4551-81F5-F8F0CA2C7966}" name="Column2"/>
+    <tableColumn id="6" xr3:uid="{14E78471-B42C-46A7-BD1C-9D7851118FD7}" name="Column3"/>
+    <tableColumn id="7" xr3:uid="{CA5A524F-838E-43AD-9CF2-84DFE3771ACC}" name="Column4"/>
+    <tableColumn id="8" xr3:uid="{E6176540-475B-4EEA-94F4-70616D68E722}" name="Column5"/>
+    <tableColumn id="9" xr3:uid="{CC2AC228-2DF6-4FF9-8A82-C7A0F3A6F6DD}" name="Column6" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{2A4CC5FF-AB1D-442B-92F9-F5CF06779A32}" name="Column7">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Channels!B:B,Channels!B:B,"MISSING",0,1)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6778,7 +7050,7 @@
   <threadedComment ref="B61" dT="2025-03-07T22:24:32.38" personId="{B662DE40-7D09-46E5-994D-04657B702874}" id="{3477900C-1235-4AD9-B6B9-B36EBE216470}" parentId="{8497C7DA-1239-4373-88D7-CCD3FD1374B1}">
     <text>See comment on product family</text>
   </threadedComment>
-  <threadedComment ref="C91" dT="2025-03-06T16:36:49.39" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
+  <threadedComment ref="C92" dT="2025-03-06T16:36:49.39" personId="{14C944A1-1481-401E-974A-00A50AE6EDAF}" id="{B341755A-7D9C-4B12-B3E8-F721DABD8A3A}">
     <text xml:space="preserve">@David Irvine 
 example please . is it a available field in existing Marketo Activities?
 </text>
@@ -6792,7 +7064,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF98BEB6-65EB-437D-B437-4DFA85EC4A08}">
   <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.42578125" bestFit="1" customWidth="1"/>
@@ -6849,11 +7121,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="90">
-      <c r="A2" s="34" t="s">
+    <row r="2" spans="1:13" ht="72.599999999999994">
+      <c r="A2" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="31" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -6885,11 +7157,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="75">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:13" ht="72.599999999999994">
+      <c r="A3" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="32" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -6918,11 +7190,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="75">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:13" ht="72.599999999999994">
+      <c r="A4" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="32" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -6951,7 +7223,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="60">
+    <row r="5" spans="1:13" ht="57.95">
       <c r="A5" s="9" t="s">
         <v>33</v>
       </c>
@@ -6984,7 +7256,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="60">
+    <row r="6" spans="1:13" ht="43.5">
       <c r="A6" s="7" t="s">
         <v>37</v>
       </c>
@@ -7017,8 +7289,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="105">
-      <c r="A7" s="34" t="s">
+    <row r="7" spans="1:13" ht="101.45">
+      <c r="A7" s="31" t="s">
         <v>42</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -7050,8 +7322,8 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="105">
-      <c r="A8" s="34" t="s">
+    <row r="8" spans="1:13" ht="72.599999999999994">
+      <c r="A8" s="31" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -7083,7 +7355,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="30">
+    <row r="9" spans="1:13" ht="29.1">
       <c r="A9" s="7" t="s">
         <v>52</v>
       </c>
@@ -7104,7 +7376,7 @@
       </c>
       <c r="G9">
         <f>COUNTIF(Attributes!A:A,objects!A9)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
         <v>27</v>
@@ -7113,8 +7385,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="75">
-      <c r="A10" s="34" t="s">
+    <row r="10" spans="1:13" ht="57.95">
+      <c r="A10" s="31" t="s">
         <v>58</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -7146,8 +7418,8 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="120">
-      <c r="A11" s="34" t="s">
+    <row r="11" spans="1:13" ht="87">
+      <c r="A11" s="31" t="s">
         <v>63</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -7167,7 +7439,7 @@
       </c>
       <c r="G11">
         <f>COUNTIF(Attributes!A:A,objects!A11)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -7179,8 +7451,8 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="60">
-      <c r="A12" s="37" t="s">
+    <row r="12" spans="1:13" ht="57.95">
+      <c r="A12" s="34" t="s">
         <v>68</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -7209,8 +7481,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="45">
-      <c r="A13" s="34" t="s">
+    <row r="13" spans="1:13" ht="43.5">
+      <c r="A13" s="31" t="s">
         <v>73</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -7242,8 +7514,8 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="105">
-      <c r="A14" s="34" t="s">
+    <row r="14" spans="1:13" ht="101.45">
+      <c r="A14" s="31" t="s">
         <v>78</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -7272,7 +7544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="60">
+    <row r="15" spans="1:13" ht="57.95">
       <c r="A15" s="7" t="s">
         <v>82</v>
       </c>
@@ -7302,7 +7574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="45">
+    <row r="16" spans="1:13" ht="43.5">
       <c r="A16" s="7" t="s">
         <v>86</v>
       </c>
@@ -7332,7 +7604,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="60">
+    <row r="17" spans="1:9" ht="57.95">
       <c r="A17" s="3" t="s">
         <v>89</v>
       </c>
@@ -7362,7 +7634,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="75">
+    <row r="18" spans="1:9" ht="57.95">
       <c r="A18" s="3" t="s">
         <v>95</v>
       </c>
@@ -7392,7 +7664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="45">
+    <row r="19" spans="1:9" ht="54.75" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>100</v>
       </c>
@@ -7418,7 +7690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="45">
+    <row r="20" spans="1:9" ht="43.5">
       <c r="A20" s="3" t="s">
         <v>105</v>
       </c>
@@ -7445,18 +7717,19 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M20" xr:uid="{BF98BEB6-65EB-437D-B437-4DFA85EC4A08}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
-  <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:J171"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="136" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.7109375" customWidth="1"/>
@@ -7498,112 +7771,112 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1">
-      <c r="A2" s="36" t="s">
+    <row r="2" spans="1:10">
+      <c r="A2" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="33" t="s">
         <v>119</v>
       </c>
       <c r="F2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1">
-      <c r="A3" s="36" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="33" t="s">
         <v>122</v>
       </c>
       <c r="F3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1">
-      <c r="A4" s="36" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="33" t="s">
         <v>125</v>
       </c>
       <c r="F4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1">
-      <c r="A5" s="36" t="s">
+    <row r="5" spans="1:10">
+      <c r="A5" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="33" t="s">
         <v>128</v>
       </c>
       <c r="F5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1">
-      <c r="A6" s="36" t="s">
+    <row r="6" spans="1:10">
+      <c r="A6" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="33" t="s">
         <v>131</v>
       </c>
       <c r="F6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1">
-      <c r="A7" s="36" t="s">
+    <row r="7" spans="1:10">
+      <c r="A7" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="33" t="s">
         <v>134</v>
       </c>
       <c r="F7" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1">
-      <c r="A8" s="36" t="s">
+    <row r="8" spans="1:10">
+      <c r="A8" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="33" t="s">
         <v>137</v>
       </c>
       <c r="F8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="107.25" hidden="1" customHeight="1">
-      <c r="A9" s="36" t="s">
+    <row r="9" spans="1:10" ht="107.25" customHeight="1">
+      <c r="A9" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="33" t="s">
         <v>140</v>
       </c>
       <c r="F9" t="s">
@@ -7613,14 +7886,14 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1">
-      <c r="A10" s="36" t="s">
+    <row r="10" spans="1:10">
+      <c r="A10" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="33" t="s">
         <v>143</v>
       </c>
       <c r="F10" t="s">
@@ -7759,7 +8032,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="45" hidden="1">
+    <row r="20" spans="1:7" ht="43.5" hidden="1">
       <c r="A20" t="s">
         <v>155</v>
       </c>
@@ -7976,7 +8249,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="60" hidden="1">
+    <row r="34" spans="1:7" ht="57.95" hidden="1">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -8032,7 +8305,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -8046,7 +8319,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="135" hidden="1">
+    <row r="39" spans="1:7" ht="130.5" hidden="1">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -8105,7 +8378,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="45" hidden="1">
+    <row r="43" spans="1:7" ht="43.5" hidden="1">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -8125,7 +8398,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="75" hidden="1">
+    <row r="44" spans="1:7" ht="72.599999999999994" hidden="1">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -8142,7 +8415,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="45" hidden="1">
+    <row r="45" spans="1:7" ht="43.5" hidden="1">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -8192,7 +8465,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="27" hidden="1">
+    <row r="49" spans="1:10" ht="26.45" hidden="1">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -8205,7 +8478,7 @@
       <c r="F49" t="s">
         <v>250</v>
       </c>
-      <c r="G49" s="38" t="s">
+      <c r="G49" s="35" t="s">
         <v>251</v>
       </c>
     </row>
@@ -8354,7 +8627,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="60">
+    <row r="61" spans="1:10" ht="57.95" hidden="1">
       <c r="A61" s="4" t="s">
         <v>33</v>
       </c>
@@ -8441,7 +8714,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" hidden="1">
       <c r="A67" t="s">
         <v>73</v>
       </c>
@@ -8472,7 +8745,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="45" hidden="1">
+    <row r="69" spans="1:10" ht="43.5" hidden="1">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -8665,7 +8938,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" hidden="1">
       <c r="A85" s="4" t="s">
         <v>73</v>
       </c>
@@ -8676,7 +8949,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" hidden="1">
       <c r="A86" s="4" t="s">
         <v>73</v>
       </c>
@@ -8735,96 +9008,87 @@
         <v>334</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="45" hidden="1">
-      <c r="A91" t="s">
+    <row r="91" spans="1:10" ht="15" hidden="1">
+      <c r="A91" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B91" t="s">
-        <v>335</v>
-      </c>
-      <c r="C91" t="s">
-        <v>336</v>
-      </c>
-      <c r="D91" t="s">
-        <v>337</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="F91" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" hidden="1">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="29.25" hidden="1">
       <c r="A92" t="s">
         <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>187</v>
+        <v>335</v>
       </c>
       <c r="C92" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" hidden="1">
+        <v>336</v>
+      </c>
+      <c r="D92" t="s">
+        <v>337</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="F92" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="15" hidden="1">
       <c r="A93" t="s">
         <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>341</v>
+        <v>187</v>
       </c>
       <c r="C93" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" hidden="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15" hidden="1">
       <c r="A94" t="s">
         <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>265</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" hidden="1">
+        <v>341</v>
+      </c>
+      <c r="C94" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="15" hidden="1">
       <c r="A95" t="s">
         <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>231</v>
-      </c>
-      <c r="C95" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" hidden="1">
+        <v>265</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="15" hidden="1">
       <c r="A96" t="s">
         <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>345</v>
+        <v>231</v>
       </c>
       <c r="C96" t="s">
-        <v>346</v>
-      </c>
-      <c r="D96" t="s">
-        <v>347</v>
-      </c>
-      <c r="E96" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" hidden="1">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15" hidden="1">
       <c r="A97" t="s">
         <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C97" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D97" t="s">
         <v>347</v>
@@ -8833,101 +9097,104 @@
         <v>348</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1">
+    <row r="98" spans="1:6" ht="15" hidden="1">
       <c r="A98" t="s">
         <v>42</v>
       </c>
       <c r="B98" t="s">
-        <v>283</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" hidden="1">
+        <v>349</v>
+      </c>
+      <c r="C98" t="s">
+        <v>350</v>
+      </c>
+      <c r="D98" t="s">
+        <v>347</v>
+      </c>
+      <c r="E98" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="15" hidden="1">
       <c r="A99" t="s">
         <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" hidden="1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15" hidden="1">
       <c r="A100" t="s">
         <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" hidden="1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="15" hidden="1">
       <c r="A101" t="s">
         <v>42</v>
       </c>
       <c r="B101" t="s">
-        <v>185</v>
-      </c>
-      <c r="C101" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" hidden="1">
+        <v>279</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15" hidden="1">
       <c r="A102" t="s">
         <v>42</v>
       </c>
       <c r="B102" t="s">
-        <v>352</v>
+        <v>185</v>
       </c>
       <c r="C102" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" hidden="1">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15" hidden="1">
       <c r="A103" t="s">
         <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C103" t="s">
-        <v>355</v>
-      </c>
-      <c r="D103" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" hidden="1">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="15" hidden="1">
       <c r="A104" t="s">
         <v>42</v>
       </c>
       <c r="B104" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C104" t="s">
-        <v>357</v>
-      </c>
-      <c r="F104" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" hidden="1">
+        <v>355</v>
+      </c>
+      <c r="D104" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15" hidden="1">
       <c r="A105" t="s">
         <v>42</v>
       </c>
       <c r="B105" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C105" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F105" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="106" spans="1:6" hidden="1">
@@ -8938,7 +9205,7 @@
         <v>231</v>
       </c>
       <c r="C106" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F106" t="s">
         <v>159</v>
@@ -8949,10 +9216,10 @@
         <v>28</v>
       </c>
       <c r="B107" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C107" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F107" t="s">
         <v>159</v>
@@ -8963,13 +9230,13 @@
         <v>28</v>
       </c>
       <c r="B108" t="s">
+        <v>361</v>
+      </c>
+      <c r="C108" t="s">
+        <v>362</v>
+      </c>
+      <c r="F108" t="s">
         <v>363</v>
-      </c>
-      <c r="C108" t="s">
-        <v>364</v>
-      </c>
-      <c r="F108" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:6" hidden="1">
@@ -8980,7 +9247,7 @@
         <v>136</v>
       </c>
       <c r="C109" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:6" hidden="1">
@@ -8988,7 +9255,7 @@
         <v>58</v>
       </c>
       <c r="B110" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C110"/>
     </row>
@@ -9003,7 +9270,7 @@
         <v>280</v>
       </c>
       <c r="F111" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:6" hidden="1">
@@ -9031,18 +9298,18 @@
         <v>284</v>
       </c>
       <c r="F113" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="114" spans="1:10" hidden="1">
       <c r="B114" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C114" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" hidden="1">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
         <v>68</v>
       </c>
@@ -9054,7 +9321,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1">
+    <row r="116" spans="1:10">
       <c r="A116" t="s">
         <v>68</v>
       </c>
@@ -9066,7 +9333,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1">
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
         <v>68</v>
       </c>
@@ -9074,7 +9341,7 @@
         <v>185</v>
       </c>
       <c r="C117" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F117" t="s">
         <v>163</v>
@@ -9083,7 +9350,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1">
+    <row r="118" spans="1:10">
       <c r="A118" t="s">
         <v>68</v>
       </c>
@@ -9091,30 +9358,30 @@
         <v>187</v>
       </c>
       <c r="C118" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F118" t="s">
         <v>163</v>
       </c>
       <c r="J118" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" hidden="1">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
       <c r="A119" t="s">
         <v>68</v>
       </c>
       <c r="B119" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C119" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F119" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1">
+    <row r="120" spans="1:10">
       <c r="A120" t="s">
         <v>63</v>
       </c>
@@ -9126,87 +9393,138 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1">
+    <row r="121" spans="1:10">
       <c r="A121" t="s">
         <v>63</v>
       </c>
       <c r="B121" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C121"/>
       <c r="F121" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1">
+    <row r="122" spans="1:10">
       <c r="A122" t="s">
         <v>63</v>
       </c>
       <c r="B122" t="s">
+        <v>376</v>
+      </c>
+      <c r="C122" t="s">
+        <v>377</v>
+      </c>
+      <c r="D122" t="s">
         <v>378</v>
       </c>
-      <c r="C122"/>
-    </row>
-    <row r="123" spans="1:10" hidden="1">
+      <c r="E122" t="s">
+        <v>379</v>
+      </c>
+      <c r="G122" s="16" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
       <c r="A123" t="s">
         <v>63</v>
       </c>
       <c r="B123" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C123" t="s">
-        <v>380</v>
+        <v>382</v>
+      </c>
+      <c r="D123" t="s">
+        <v>383</v>
+      </c>
+      <c r="E123" t="s">
+        <v>384</v>
       </c>
       <c r="G123" s="16" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" hidden="1">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
       <c r="A124" t="s">
         <v>63</v>
       </c>
       <c r="B124" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C124" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" hidden="1">
+        <v>387</v>
+      </c>
+      <c r="D124" t="s">
+        <v>388</v>
+      </c>
+      <c r="E124" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
       <c r="A125" t="s">
         <v>63</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="C125"/>
-    </row>
-    <row r="126" spans="1:10" hidden="1">
+        <v>390</v>
+      </c>
+      <c r="C125" t="s">
+        <v>391</v>
+      </c>
+      <c r="F125" t="s">
+        <v>392</v>
+      </c>
+      <c r="G125" s="16" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="29.1">
       <c r="A126" t="s">
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>385</v>
-      </c>
-      <c r="C126"/>
-    </row>
-    <row r="127" spans="1:10" hidden="1">
+        <v>394</v>
+      </c>
+      <c r="C126" t="s">
+        <v>395</v>
+      </c>
+      <c r="D126" t="s">
+        <v>396</v>
+      </c>
+      <c r="E126" t="s">
+        <v>397</v>
+      </c>
+      <c r="F126" t="s">
+        <v>392</v>
+      </c>
+      <c r="G126" s="16" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
       <c r="A127" t="s">
         <v>63</v>
       </c>
       <c r="B127" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="C127" t="s">
-        <v>387</v>
+        <v>400</v>
+      </c>
+      <c r="D127" t="s">
+        <v>396</v>
+      </c>
+      <c r="E127" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:10" hidden="1">
       <c r="B128" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C128" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
     </row>
     <row r="129" spans="1:7" hidden="1">
@@ -9226,7 +9544,7 @@
         <v>231</v>
       </c>
       <c r="C130" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="131" spans="1:7" hidden="1">
@@ -9237,7 +9555,7 @@
         <v>241</v>
       </c>
       <c r="C131" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
     </row>
     <row r="132" spans="1:7" hidden="1">
@@ -9245,10 +9563,10 @@
         <v>37</v>
       </c>
       <c r="B132" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="C132" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
     </row>
     <row r="133" spans="1:7" hidden="1">
@@ -9256,10 +9574,10 @@
         <v>37</v>
       </c>
       <c r="B133" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="C133" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
     </row>
     <row r="134" spans="1:7" s="4" customFormat="1" hidden="1">
@@ -9267,16 +9585,16 @@
         <v>37</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>207</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="G134" s="6"/>
     </row>
@@ -9285,10 +9603,10 @@
         <v>37</v>
       </c>
       <c r="B135" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="C135" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
     </row>
     <row r="136" spans="1:7" hidden="1">
@@ -9296,10 +9614,10 @@
         <v>37</v>
       </c>
       <c r="B136" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C136" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
     </row>
     <row r="137" spans="1:7" hidden="1">
@@ -9310,10 +9628,10 @@
         <v>341</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" hidden="1">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="29.1" hidden="1">
       <c r="A138" s="4" t="s">
         <v>82</v>
       </c>
@@ -9321,10 +9639,10 @@
         <v>246</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" hidden="1">
       <c r="A139" s="4" t="s">
         <v>82</v>
       </c>
@@ -9332,7 +9650,7 @@
         <v>220</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="F139" t="s">
         <v>289</v>
@@ -9343,10 +9661,10 @@
         <v>82</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
     </row>
     <row r="141" spans="1:7" hidden="1">
@@ -9354,10 +9672,10 @@
         <v>82</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
     </row>
     <row r="142" spans="1:7" hidden="1">
@@ -9365,10 +9683,10 @@
         <v>82</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
     </row>
     <row r="143" spans="1:7" hidden="1">
@@ -9376,46 +9694,46 @@
         <v>82</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="60" hidden="1">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="57.95" hidden="1">
       <c r="A144" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="G144" s="16" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" hidden="1">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="29.1" hidden="1">
       <c r="A145" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" hidden="1">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="29.1" hidden="1">
       <c r="A146" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
     </row>
     <row r="147" spans="1:7" hidden="1">
@@ -9426,10 +9744,10 @@
         <v>133</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" hidden="1">
       <c r="A148" t="s">
         <v>100</v>
       </c>
@@ -9437,33 +9755,33 @@
         <v>220</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="D148" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="E148" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="F148" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" hidden="1">
       <c r="A149" t="s">
         <v>100</v>
       </c>
       <c r="B149" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="D149" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="F149" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
     </row>
     <row r="150" spans="1:7" hidden="1">
@@ -9474,7 +9792,7 @@
         <v>231</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="F150" t="s">
         <v>159</v>
@@ -9485,16 +9803,16 @@
         <v>100</v>
       </c>
       <c r="B151" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="F151" t="s">
         <v>129</v>
       </c>
       <c r="G151" s="16" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
     </row>
     <row r="152" spans="1:7" hidden="1">
@@ -9508,7 +9826,7 @@
         <v>280</v>
       </c>
       <c r="F152" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="153" spans="1:7" hidden="1">
@@ -9536,7 +9854,7 @@
         <v>284</v>
       </c>
       <c r="F154" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="155" spans="1:7" hidden="1">
@@ -9544,10 +9862,10 @@
         <v>105</v>
       </c>
       <c r="B155" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
     </row>
     <row r="156" spans="1:7" hidden="1">
@@ -9558,7 +9876,7 @@
         <v>246</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
     </row>
     <row r="157" spans="1:7" hidden="1">
@@ -9566,10 +9884,10 @@
         <v>105</v>
       </c>
       <c r="B157" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
     </row>
     <row r="158" spans="1:7" hidden="1">
@@ -9577,10 +9895,10 @@
         <v>105</v>
       </c>
       <c r="B158" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
     </row>
     <row r="159" spans="1:7" hidden="1">
@@ -9588,10 +9906,10 @@
         <v>105</v>
       </c>
       <c r="B159" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
     </row>
     <row r="160" spans="1:7" hidden="1">
@@ -9599,7 +9917,7 @@
         <v>105</v>
       </c>
       <c r="B160" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="161" spans="1:7" hidden="1">
@@ -9607,7 +9925,7 @@
         <v>105</v>
       </c>
       <c r="B161" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
     </row>
     <row r="162" spans="1:7" hidden="1">
@@ -9615,40 +9933,108 @@
         <v>28</v>
       </c>
       <c r="B162" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="F162" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1">
-      <c r="A163" s="3" t="s">
+    <row r="163" spans="1:7" ht="15" hidden="1">
+      <c r="A163" t="s">
         <v>42</v>
       </c>
       <c r="B163" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="30" hidden="1">
+        <v>458</v>
+      </c>
+      <c r="C163" t="s">
+        <v>459</v>
+      </c>
+      <c r="F163" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="29.1" hidden="1">
       <c r="A164" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B164" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="E164" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="G164" s="16" t="s">
-        <v>448</v>
-      </c>
-    </row>
+        <v>463</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B165" t="s">
+        <v>231</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E165" t="s">
+        <v>465</v>
+      </c>
+      <c r="F165" t="s">
+        <v>159</v>
+      </c>
+      <c r="G165" s="16" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="29.25">
+      <c r="A166" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B166" t="s">
+        <v>467</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D166" t="s">
+        <v>469</v>
+      </c>
+      <c r="E166" t="s">
+        <v>384</v>
+      </c>
+      <c r="F166" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="29.25">
+      <c r="A167" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B167" t="s">
+        <v>471</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D167" t="s">
+        <v>469</v>
+      </c>
+      <c r="E167" t="s">
+        <v>384</v>
+      </c>
+      <c r="F167" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="15"/>
+    <row r="171" spans="1:7" ht="15"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J105">
     <sortCondition ref="A2:A105"/>
@@ -9680,7 +10066,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FEA969B-2E99-43A3-91BB-BD5F9824B477}">
   <dimension ref="A1:T9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
@@ -9695,55 +10081,55 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="3" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>453</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>454</v>
+        <v>477</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>478</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>479</v>
       </c>
       <c r="G1" t="s">
         <v>63</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="K1" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="M1" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="N1" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>461</v>
+        <v>486</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -9754,33 +10140,33 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="E2" s="31">
+        <v>491</v>
+      </c>
+      <c r="E2" s="28">
         <v>1</v>
       </c>
-      <c r="F2" s="31">
+      <c r="F2" s="28">
         <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="I2" s="3">
         <v>10</v>
       </c>
-      <c r="K2" s="32">
+      <c r="K2" s="29">
         <v>0.1</v>
       </c>
-      <c r="M2" s="33">
+      <c r="M2" s="30">
         <v>1000</v>
       </c>
-      <c r="N2" s="33">
+      <c r="N2" s="30">
         <f>M2*K2</f>
         <v>100</v>
       </c>
@@ -9793,33 +10179,33 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="E3" s="31">
+        <v>494</v>
+      </c>
+      <c r="E3" s="28">
         <v>1</v>
       </c>
-      <c r="F3" s="31">
+      <c r="F3" s="28">
         <v>5</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="I3" s="3">
         <v>200</v>
       </c>
-      <c r="K3" s="32">
+      <c r="K3" s="29">
         <v>0.02</v>
       </c>
-      <c r="M3" s="33">
+      <c r="M3" s="30">
         <v>250</v>
       </c>
-      <c r="N3" s="33">
+      <c r="N3" s="30">
         <f t="shared" ref="N3:N9" si="0">M3*K3</f>
         <v>5</v>
       </c>
@@ -9832,31 +10218,31 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="E4" s="31">
+        <v>496</v>
+      </c>
+      <c r="E4" s="28">
         <v>2</v>
       </c>
-      <c r="F4" s="31"/>
+      <c r="F4" s="28"/>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="I4" s="3">
         <v>15</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="29">
         <v>0.6</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="30">
         <v>250</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="30">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
@@ -9869,31 +10255,31 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="E5" s="31">
+        <v>498</v>
+      </c>
+      <c r="E5" s="28">
         <v>3</v>
       </c>
-      <c r="F5" s="31"/>
+      <c r="F5" s="28"/>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="29">
         <v>0.52</v>
       </c>
-      <c r="M5" s="33">
+      <c r="M5" s="30">
         <v>1000</v>
       </c>
-      <c r="N5" s="33">
+      <c r="N5" s="30">
         <f t="shared" si="0"/>
         <v>520</v>
       </c>
@@ -9909,30 +10295,30 @@
         <v>73</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="E6" s="31">
+        <v>500</v>
+      </c>
+      <c r="E6" s="28">
         <v>4</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="28">
         <v>6</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="I6" s="3">
         <v>0</v>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="29">
         <v>0.1</v>
       </c>
-      <c r="M6" s="33">
+      <c r="M6" s="30">
         <v>555</v>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="30">
         <f t="shared" si="0"/>
         <v>55.5</v>
       </c>
@@ -9948,28 +10334,28 @@
         <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31">
+        <v>501</v>
+      </c>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28">
         <v>5</v>
       </c>
       <c r="G7">
         <v>6</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="I7" s="3">
         <v>256</v>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="29">
         <v>1E-3</v>
       </c>
-      <c r="M7" s="33">
+      <c r="M7" s="30">
         <v>789</v>
       </c>
-      <c r="N7" s="33">
+      <c r="N7" s="30">
         <f t="shared" si="0"/>
         <v>0.78900000000000003</v>
       </c>
@@ -9985,28 +10371,28 @@
         <v>73</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="E8" s="31">
+        <v>502</v>
+      </c>
+      <c r="E8" s="28">
         <v>6</v>
       </c>
-      <c r="F8" s="31"/>
+      <c r="F8" s="28"/>
       <c r="G8">
         <v>7</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="I8" s="3">
         <v>24</v>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="29">
         <v>1E-3</v>
       </c>
-      <c r="M8" s="33">
+      <c r="M8" s="30">
         <v>5</v>
       </c>
-      <c r="N8" s="33">
+      <c r="N8" s="30">
         <f t="shared" si="0"/>
         <v>5.0000000000000001E-3</v>
       </c>
@@ -10022,28 +10408,28 @@
         <v>73</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31">
+        <v>503</v>
+      </c>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28">
         <v>8</v>
       </c>
       <c r="G9">
         <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="I9" s="3">
         <v>51</v>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="29">
         <v>1E-3</v>
       </c>
-      <c r="M9" s="33">
+      <c r="M9" s="30">
         <v>1000000</v>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="30">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
@@ -10056,7 +10442,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2AC8CA7-C3B2-4113-BDC9-28FC11714663}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="47.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.7109375" style="16" customWidth="1"/>
@@ -10066,83 +10452,83 @@
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="10" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="11" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="D4" s="17"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="11" t="s">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="11" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="11" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="D7" s="17"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="10" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -10150,47 +10536,47 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17" t="s">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="D9" s="17"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="11" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17" t="s">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="D10" s="17"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="11" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="D11" s="17"/>
     </row>
-    <row r="12" spans="1:4" ht="30">
+    <row r="12" spans="1:4">
       <c r="A12" s="11" t="s">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17" t="s">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="D12" s="17"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="10" t="s">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -10198,724 +10584,724 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="11" t="s">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17" t="s">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="D14" s="17"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="11" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17" t="s">
-        <v>506</v>
+        <v>531</v>
       </c>
       <c r="D15" s="17"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="11" t="s">
-        <v>507</v>
+        <v>532</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="11" t="s">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17" t="s">
-        <v>510</v>
+        <v>535</v>
       </c>
       <c r="D17" s="17"/>
     </row>
     <row r="18" spans="1:6">
       <c r="E18" s="13" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="45">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="43.5">
       <c r="A19" s="12" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="30">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="29.1">
       <c r="A20" s="12" t="s">
-        <v>518</v>
+        <v>543</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>521</v>
+        <v>546</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="60">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="57.95">
       <c r="A21" s="12" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>526</v>
+        <v>551</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="30">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="29.1">
       <c r="A22" s="12" t="s">
-        <v>528</v>
+        <v>553</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>531</v>
+        <v>556</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="135">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="130.5">
       <c r="A23" s="12" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>534</v>
+        <v>559</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>535</v>
+        <v>560</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="270">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="231.95">
       <c r="A24" s="12" t="s">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>538</v>
+        <v>563</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="75">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="57.95">
       <c r="A25" s="12" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="120">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="116.1">
       <c r="A26" s="12" t="s">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>548</v>
+        <v>573</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="75">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="57.95">
       <c r="A27" s="12" t="s">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="75">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="57.95">
       <c r="A28" s="12" t="s">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="75">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="57.95">
       <c r="A29" s="12" t="s">
-        <v>556</v>
+        <v>581</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="75">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="57.95">
       <c r="A30" s="12" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="75">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="57.95">
       <c r="A31" s="12" t="s">
-        <v>562</v>
+        <v>587</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="45">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="43.5">
       <c r="A32" s="12" t="s">
-        <v>566</v>
+        <v>591</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="C32" s="19"/>
       <c r="E32" s="14" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="30">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="12" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="30">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="29.1">
       <c r="A34" s="12" t="s">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="12" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="12" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>586</v>
+        <v>611</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="12" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>589</v>
+        <v>614</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="12" t="s">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="12" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="45">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="29.1">
       <c r="A40" s="12" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="60">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="57.95">
       <c r="A41" s="12" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="60">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="43.5">
       <c r="A42" s="12" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="45">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="43.5">
       <c r="A43" s="12" t="s">
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="30">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="29.1">
       <c r="A44" s="12" t="s">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>617</v>
+        <v>642</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>618</v>
+        <v>643</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="105">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="101.45">
       <c r="A45" s="12" t="s">
-        <v>620</v>
+        <v>645</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>621</v>
+        <v>646</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>622</v>
+        <v>647</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="45">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="29.1">
       <c r="A46" s="12" t="s">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>621</v>
+        <v>646</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="30">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="12" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>630</v>
+        <v>655</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="30">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="12" t="s">
-        <v>632</v>
+        <v>657</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>633</v>
+        <v>658</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>634</v>
+        <v>659</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="12" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>638</v>
+        <v>663</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="12" t="s">
-        <v>639</v>
+        <v>664</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="60">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="43.5">
       <c r="A51" s="12" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>644</v>
+        <v>669</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="60">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="43.5">
       <c r="A52" s="12" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>648</v>
+        <v>673</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="12" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="165">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="130.5">
       <c r="A54" s="12" t="s">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="30">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="29.1">
       <c r="A55" s="12" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="12" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="60">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="43.5">
       <c r="A57" s="12" t="s">
-        <v>665</v>
+        <v>690</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>666</v>
+        <v>691</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="60">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="43.5">
       <c r="A58" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="B58" s="23" t="s">
         <v>668</v>
       </c>
-      <c r="B58" s="23" t="s">
-        <v>643</v>
-      </c>
       <c r="E58" s="14" t="s">
-        <v>669</v>
+        <v>694</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="45">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="29.1">
       <c r="A59" s="12" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>621</v>
+        <v>646</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="45">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="43.5">
       <c r="A60" s="12" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="45">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="43.5">
       <c r="A61" s="12" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>679</v>
+        <v>704</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="45">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="43.5">
       <c r="A62" s="12" t="s">
-        <v>681</v>
+        <v>706</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>682</v>
+        <v>707</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>683</v>
+        <v>708</v>
       </c>
     </row>
   </sheetData>
@@ -10926,253 +11312,474 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8D126A-E50F-4373-9159-5B9100CAC9A2}">
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" customWidth="1"/>
     <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="85.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>684</v>
+        <v>709</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="D1" t="s">
-        <v>686</v>
+        <v>711</v>
       </c>
       <c r="E1" t="s">
-        <v>687</v>
+        <v>712</v>
       </c>
       <c r="F1" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>713</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>460</v>
+      </c>
+      <c r="H1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="B2" t="s">
-        <v>689</v>
+        <v>715</v>
       </c>
       <c r="C2" t="s">
-        <v>690</v>
+        <v>716</v>
       </c>
       <c r="D2" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>717</v>
+      </c>
+      <c r="E2" t="s">
+        <v>718</v>
+      </c>
+      <c r="G2" t="s">
+        <v>719</v>
+      </c>
+      <c r="H2" t="str">
+        <f>_xlfn.XLOOKUP(B2,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Viewed;Clicked;Submit Form</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="B3" t="s">
-        <v>692</v>
+        <v>720</v>
       </c>
       <c r="C3" t="s">
-        <v>690</v>
+        <v>716</v>
       </c>
       <c r="D3" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>721</v>
+      </c>
+      <c r="E3" t="s">
+        <v>722</v>
+      </c>
+      <c r="G3" t="s">
+        <v>719</v>
+      </c>
+      <c r="H3" t="str">
+        <f>_xlfn.XLOOKUP(B3,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Viewed;Clicked;Submit Form</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="B4" t="s">
-        <v>694</v>
+        <v>723</v>
       </c>
       <c r="C4" t="s">
-        <v>690</v>
+        <v>716</v>
       </c>
       <c r="D4" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>724</v>
+      </c>
+      <c r="E4" t="s">
+        <v>718</v>
+      </c>
+      <c r="G4" t="s">
+        <v>719</v>
+      </c>
+      <c r="H4" t="str">
+        <f>_xlfn.XLOOKUP(B4,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Page View;Link Click;Submit Form;Watch Video;Download;Live Chat?</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="B5" t="s">
-        <v>696</v>
+        <v>725</v>
       </c>
       <c r="C5" t="s">
-        <v>690</v>
+        <v>716</v>
       </c>
       <c r="D5" t="s">
-        <v>693</v>
+        <v>721</v>
+      </c>
+      <c r="E5" t="s">
+        <v>726</v>
       </c>
       <c r="F5" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>727</v>
+      </c>
+      <c r="G5" t="s">
+        <v>719</v>
+      </c>
+      <c r="H5" t="str">
+        <f>_xlfn.XLOOKUP(B5,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Viewed</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="B6" t="s">
-        <v>698</v>
+        <v>728</v>
       </c>
       <c r="C6" t="s">
-        <v>690</v>
+        <v>716</v>
       </c>
       <c r="D6" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>721</v>
+      </c>
+      <c r="E6" t="s">
+        <v>718</v>
+      </c>
+      <c r="G6" t="s">
+        <v>719</v>
+      </c>
+      <c r="H6" t="str">
+        <f>_xlfn.XLOOKUP(B6,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Viewed;Clicked;Responded</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7" t="s">
-        <v>699</v>
+        <v>729</v>
       </c>
       <c r="C7" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D7" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>731</v>
+      </c>
+      <c r="E7" t="s">
+        <v>718</v>
+      </c>
+      <c r="G7" t="s">
+        <v>732</v>
+      </c>
+      <c r="H7" t="str">
+        <f>_xlfn.XLOOKUP(B7,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Viewed;Clicked;Responded;Opt-Out</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8" t="s">
-        <v>702</v>
+        <v>733</v>
       </c>
       <c r="C8" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D8" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>734</v>
+      </c>
+      <c r="E8" t="s">
+        <v>735</v>
+      </c>
+      <c r="G8" t="s">
+        <v>732</v>
+      </c>
+      <c r="H8" t="str">
+        <f>_xlfn.XLOOKUP(B8,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Registered;Attended;View on Demand</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="B9" t="s">
-        <v>704</v>
+        <v>736</v>
       </c>
       <c r="C9" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D9" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>734</v>
+      </c>
+      <c r="E9" t="s">
+        <v>735</v>
+      </c>
+      <c r="G9" t="s">
+        <v>732</v>
+      </c>
+      <c r="H9" t="str">
+        <f>_xlfn.XLOOKUP(B9,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Registered;Attended</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="B10" t="s">
-        <v>705</v>
+        <v>737</v>
       </c>
       <c r="C10" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D10" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>734</v>
+      </c>
+      <c r="E10" t="s">
+        <v>735</v>
+      </c>
+      <c r="H10" t="str">
+        <f>_xlfn.XLOOKUP(B10,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Registered;Attended;View on Demand</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="B11" t="s">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="C11" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D11" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>731</v>
+      </c>
+      <c r="E11" t="s">
+        <v>726</v>
+      </c>
+      <c r="H11" t="str">
+        <f>_xlfn.XLOOKUP(B11,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Sent;Delivered;Bounced</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="B12" t="s">
-        <v>707</v>
+        <v>739</v>
       </c>
       <c r="C12" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D12" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>731</v>
+      </c>
+      <c r="E12" t="s">
+        <v>718</v>
+      </c>
+      <c r="H12" t="str">
+        <f>_xlfn.XLOOKUP(B12,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="B13" t="s">
-        <v>708</v>
+        <v>740</v>
       </c>
       <c r="C13" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D13" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>731</v>
+      </c>
+      <c r="E13" t="s">
+        <v>718</v>
+      </c>
+      <c r="H13" t="str">
+        <f>_xlfn.XLOOKUP(B13,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="B14" t="s">
-        <v>709</v>
+        <v>741</v>
       </c>
       <c r="C14" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D14" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>731</v>
+      </c>
+      <c r="E14" t="s">
+        <v>718</v>
+      </c>
+      <c r="H14" t="str">
+        <f>_xlfn.XLOOKUP(B14,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="B15" t="s">
-        <v>710</v>
+        <v>742</v>
       </c>
       <c r="C15" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D15" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>731</v>
+      </c>
+      <c r="E15" t="s">
+        <v>718</v>
+      </c>
+      <c r="H15" t="str">
+        <f>_xlfn.XLOOKUP(B15,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="B16" t="s">
-        <v>711</v>
+        <v>743</v>
       </c>
       <c r="C16" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D16" t="s">
-        <v>701</v>
+        <v>731</v>
+      </c>
+      <c r="E16" t="s">
+        <v>718</v>
+      </c>
+      <c r="H16" t="str">
+        <f>_xlfn.XLOOKUP(B16,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" t="s">
-        <v>712</v>
+        <v>744</v>
       </c>
       <c r="C17" t="s">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="D17" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
+        <v>731</v>
+      </c>
+      <c r="E17" t="s">
+        <v>718</v>
+      </c>
+      <c r="H17" t="str">
+        <f>_xlfn.XLOOKUP(B17,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Sent;Received;Clicked</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="15">
       <c r="B18" t="s">
-        <v>713</v>
+        <v>745</v>
       </c>
       <c r="C18" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="D18" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
+        <v>731</v>
+      </c>
+      <c r="E18" t="s">
+        <v>746</v>
+      </c>
+      <c r="H18" t="str">
+        <f>_xlfn.XLOOKUP(B18,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Attempted;Answered;Conversed</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="15">
       <c r="B19" t="s">
-        <v>715</v>
+        <v>747</v>
       </c>
       <c r="C19" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="D19" t="s">
-        <v>701</v>
+        <v>748</v>
+      </c>
+      <c r="E19" t="s">
+        <v>746</v>
+      </c>
+      <c r="H19" t="str">
+        <f>_xlfn.XLOOKUP(B19,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Initiated;Answered;Disconnected</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" t="s">
-        <v>716</v>
+        <v>749</v>
       </c>
       <c r="C20" t="s">
-        <v>714</v>
+        <v>750</v>
       </c>
       <c r="D20" t="s">
-        <v>701</v>
+        <v>731</v>
+      </c>
+      <c r="E20" t="s">
+        <v>746</v>
+      </c>
+      <c r="H20" t="str">
+        <f>_xlfn.XLOOKUP(B20,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Invited;Attended</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" t="s">
+        <v>751</v>
+      </c>
+      <c r="C21" t="s">
+        <v>750</v>
+      </c>
+      <c r="D21" t="s">
+        <v>731</v>
+      </c>
+      <c r="E21" t="s">
+        <v>746</v>
+      </c>
+      <c r="H21" t="str">
+        <f>_xlfn.XLOOKUP(B21,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Dialled;Answered;Engaged</v>
       </c>
     </row>
     <row r="22" spans="2:8">
-      <c r="H22" s="16"/>
+      <c r="B22" t="s">
+        <v>752</v>
+      </c>
+      <c r="C22" t="s">
+        <v>750</v>
+      </c>
+      <c r="D22" t="s">
+        <v>731</v>
+      </c>
+      <c r="E22" t="s">
+        <v>718</v>
+      </c>
+      <c r="H22" t="str">
+        <f>_xlfn.XLOOKUP(B22,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="47" t="s">
+        <v>753</v>
+      </c>
+      <c r="C23" t="s">
+        <v>730</v>
+      </c>
+      <c r="D23" t="s">
+        <v>731</v>
+      </c>
+      <c r="E23" t="s">
+        <v>746</v>
+      </c>
+      <c r="G23" t="s">
+        <v>719</v>
+      </c>
+      <c r="H23" t="str">
+        <f>_xlfn.XLOOKUP(B23,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
+        <v>Called</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="H24" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F20" xr:uid="{6B8D126A-E50F-4373-9159-5B9100CAC9A2}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F20">
-      <sortCondition ref="C1:C20"/>
+  <autoFilter ref="A1:F22" xr:uid="{6B8D126A-E50F-4373-9159-5B9100CAC9A2}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F22">
+      <sortCondition ref="C1:C22"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11181,405 +11788,623 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAF728D-8DC4-43CB-A2BE-8E22F440F4CC}">
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="28" t="s">
-        <v>717</v>
-      </c>
-      <c r="B1" s="39" t="s">
+    <row r="1" spans="1:10" ht="15">
+      <c r="A1" s="40" t="s">
+        <v>754</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>755</v>
+      </c>
+      <c r="C1" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="41"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="29" t="s">
-        <v>689</v>
-      </c>
-      <c r="B2" t="s">
-        <v>718</v>
+      <c r="D1" s="37" t="s">
+        <v>756</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>757</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>758</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>759</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>760</v>
+      </c>
+      <c r="I1" s="38" t="s">
+        <v>761</v>
+      </c>
+      <c r="J1" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15">
+      <c r="A2" s="44" t="s">
+        <v>715</v>
+      </c>
+      <c r="B2" s="41" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,C2:I2)</f>
+        <v>Viewed;Clicked;Submit Form</v>
       </c>
       <c r="C2" t="s">
-        <v>719</v>
+        <v>763</v>
       </c>
       <c r="D2" t="s">
+        <v>764</v>
+      </c>
+      <c r="E2" t="s">
+        <v>765</v>
+      </c>
+      <c r="I2" s="25"/>
+      <c r="J2" t="str">
+        <f>_xlfn.XLOOKUP(A2,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Paid Digital Ads</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
+      <c r="A3" s="44" t="s">
         <v>720</v>
       </c>
-      <c r="H2" s="25"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="29" t="s">
-        <v>692</v>
-      </c>
-      <c r="B3" t="s">
-        <v>718</v>
+      <c r="B3" s="42" t="str">
+        <f t="shared" ref="B3:B21" si="0">_xlfn.TEXTJOIN(";",TRUE,C3:I3)</f>
+        <v>Viewed;Clicked;Submit Form</v>
       </c>
       <c r="C3" t="s">
-        <v>719</v>
+        <v>763</v>
       </c>
       <c r="D3" t="s">
-        <v>720</v>
-      </c>
-      <c r="H3" s="25"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="29" t="s">
-        <v>694</v>
-      </c>
-      <c r="B4" t="s">
-        <v>721</v>
+        <v>764</v>
+      </c>
+      <c r="E3" t="s">
+        <v>765</v>
+      </c>
+      <c r="I3" s="25"/>
+      <c r="J3" t="str">
+        <f>_xlfn.XLOOKUP(A3,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Content Syndication</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="44" t="s">
+        <v>723</v>
+      </c>
+      <c r="B4" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Page View;Link Click;Submit Form;Watch Video;Download;Live Chat?</v>
       </c>
       <c r="C4" t="s">
-        <v>722</v>
+        <v>766</v>
       </c>
       <c r="D4" t="s">
-        <v>720</v>
+        <v>767</v>
       </c>
       <c r="E4" t="s">
-        <v>723</v>
+        <v>765</v>
       </c>
       <c r="F4" t="s">
-        <v>724</v>
+        <v>768</v>
       </c>
       <c r="G4" t="s">
+        <v>769</v>
+      </c>
+      <c r="H4" t="s">
+        <v>770</v>
+      </c>
+      <c r="I4" s="25"/>
+      <c r="J4" t="str">
+        <f>_xlfn.XLOOKUP(A4,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Web</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15">
+      <c r="A5" s="44" t="s">
         <v>725</v>
       </c>
-      <c r="H4" s="25"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="29" t="s">
-        <v>696</v>
-      </c>
-      <c r="B5" t="s">
-        <v>718</v>
-      </c>
-      <c r="H5" s="25"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="29" t="s">
-        <v>698</v>
-      </c>
-      <c r="B6" t="s">
-        <v>718</v>
+      <c r="B5" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Viewed</v>
+      </c>
+      <c r="C5" t="s">
+        <v>763</v>
+      </c>
+      <c r="I5" s="25"/>
+      <c r="J5" t="str">
+        <f>_xlfn.XLOOKUP(A5,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Above the Line - Non Digital</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15">
+      <c r="A6" s="44" t="s">
+        <v>728</v>
+      </c>
+      <c r="B6" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Viewed;Clicked;Responded</v>
       </c>
       <c r="C6" t="s">
-        <v>719</v>
+        <v>763</v>
       </c>
       <c r="D6" t="s">
-        <v>726</v>
-      </c>
-      <c r="H6" s="25"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="29" t="s">
-        <v>699</v>
-      </c>
-      <c r="B7" t="s">
-        <v>718</v>
+        <v>764</v>
+      </c>
+      <c r="E6" t="s">
+        <v>771</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6" t="str">
+        <f>_xlfn.XLOOKUP(A6,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Social Posts</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15">
+      <c r="A7" s="44" t="s">
+        <v>729</v>
+      </c>
+      <c r="B7" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Viewed;Clicked;Responded;Opt-Out</v>
       </c>
       <c r="C7" t="s">
-        <v>719</v>
+        <v>763</v>
       </c>
       <c r="D7" t="s">
-        <v>726</v>
+        <v>764</v>
       </c>
       <c r="E7" t="s">
-        <v>727</v>
-      </c>
-      <c r="H7" s="25"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="B8" t="s">
-        <v>728</v>
+        <v>771</v>
+      </c>
+      <c r="F7" t="s">
+        <v>772</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" t="str">
+        <f>_xlfn.XLOOKUP(A7,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Social Outbound Messages</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15">
+      <c r="A8" s="44" t="s">
+        <v>733</v>
+      </c>
+      <c r="B8" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Registered;Attended;View on Demand</v>
       </c>
       <c r="C8" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="D8" t="s">
-        <v>730</v>
-      </c>
-      <c r="H8" s="25"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="29" t="s">
-        <v>704</v>
-      </c>
-      <c r="B9" t="s">
-        <v>728</v>
+        <v>774</v>
+      </c>
+      <c r="E8" t="s">
+        <v>775</v>
+      </c>
+      <c r="I8" s="25"/>
+      <c r="J8" t="str">
+        <f>_xlfn.XLOOKUP(A8,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Virtual Events</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15">
+      <c r="A9" s="44" t="s">
+        <v>736</v>
+      </c>
+      <c r="B9" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Registered;Attended</v>
       </c>
       <c r="C9" t="s">
-        <v>729</v>
-      </c>
-      <c r="H9" s="25"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="29" t="s">
-        <v>705</v>
-      </c>
-      <c r="B10" t="s">
-        <v>728</v>
+        <v>773</v>
+      </c>
+      <c r="D9" t="s">
+        <v>774</v>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" t="str">
+        <f>_xlfn.XLOOKUP(A9,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>F2F Events</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15">
+      <c r="A10" s="44" t="s">
+        <v>737</v>
+      </c>
+      <c r="B10" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Registered;Attended;View on Demand</v>
       </c>
       <c r="C10" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="D10" t="s">
-        <v>730</v>
-      </c>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="29" t="s">
-        <v>706</v>
-      </c>
-      <c r="B11" t="s">
-        <v>731</v>
+        <v>774</v>
+      </c>
+      <c r="E10" t="s">
+        <v>775</v>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" t="str">
+        <f>_xlfn.XLOOKUP(A10,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Webinars</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15">
+      <c r="A11" s="44" t="s">
+        <v>738</v>
+      </c>
+      <c r="B11" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Sent;Delivered;Bounced</v>
       </c>
       <c r="C11" t="s">
-        <v>732</v>
+        <v>776</v>
       </c>
       <c r="D11" t="s">
-        <v>733</v>
-      </c>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="29" t="s">
-        <v>707</v>
-      </c>
-      <c r="B12" t="s">
-        <v>731</v>
+        <v>777</v>
+      </c>
+      <c r="E11" t="s">
+        <v>778</v>
+      </c>
+      <c r="I11" s="25"/>
+      <c r="J11" t="str">
+        <f>_xlfn.XLOOKUP(A11,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Direct Mail</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15">
+      <c r="A12" s="44" t="s">
+        <v>739</v>
+      </c>
+      <c r="B12" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
       </c>
       <c r="C12" t="s">
-        <v>734</v>
+        <v>776</v>
       </c>
       <c r="D12" t="s">
-        <v>735</v>
+        <v>779</v>
       </c>
       <c r="E12" t="s">
-        <v>719</v>
+        <v>780</v>
       </c>
       <c r="F12" t="s">
-        <v>726</v>
+        <v>764</v>
       </c>
       <c r="G12" t="s">
-        <v>727</v>
-      </c>
-      <c r="H12" s="25"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="29" t="s">
-        <v>708</v>
-      </c>
-      <c r="B13" t="s">
-        <v>731</v>
+        <v>771</v>
+      </c>
+      <c r="H12" t="s">
+        <v>772</v>
+      </c>
+      <c r="I12" s="25"/>
+      <c r="J12" t="str">
+        <f>_xlfn.XLOOKUP(A12,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Whatsapp</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15">
+      <c r="A13" s="44" t="s">
+        <v>740</v>
+      </c>
+      <c r="B13" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
       </c>
       <c r="C13" t="s">
-        <v>734</v>
+        <v>776</v>
       </c>
       <c r="D13" t="s">
-        <v>735</v>
+        <v>779</v>
       </c>
       <c r="E13" t="s">
-        <v>719</v>
+        <v>780</v>
       </c>
       <c r="F13" t="s">
-        <v>726</v>
+        <v>764</v>
       </c>
       <c r="G13" t="s">
-        <v>727</v>
-      </c>
-      <c r="H13" s="25"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="29" t="s">
-        <v>709</v>
-      </c>
-      <c r="B14" t="s">
-        <v>731</v>
+        <v>771</v>
+      </c>
+      <c r="H13" t="s">
+        <v>772</v>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" t="str">
+        <f>_xlfn.XLOOKUP(A13,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>RCS</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15">
+      <c r="A14" s="44" t="s">
+        <v>741</v>
+      </c>
+      <c r="B14" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
       </c>
       <c r="C14" t="s">
-        <v>734</v>
+        <v>776</v>
       </c>
       <c r="D14" t="s">
-        <v>733</v>
+        <v>779</v>
       </c>
       <c r="E14" t="s">
-        <v>736</v>
+        <v>778</v>
       </c>
       <c r="F14" t="s">
-        <v>719</v>
+        <v>781</v>
       </c>
       <c r="G14" t="s">
-        <v>727</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="29" t="s">
-        <v>710</v>
-      </c>
-      <c r="B15" t="s">
-        <v>731</v>
+        <v>764</v>
+      </c>
+      <c r="H14" t="s">
+        <v>772</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>771</v>
+      </c>
+      <c r="J14" t="str">
+        <f>_xlfn.XLOOKUP(A14,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Email</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
+      <c r="A15" s="44" t="s">
+        <v>742</v>
+      </c>
+      <c r="B15" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
       </c>
       <c r="C15" t="s">
-        <v>734</v>
+        <v>776</v>
       </c>
       <c r="D15" t="s">
-        <v>733</v>
+        <v>779</v>
       </c>
       <c r="E15" t="s">
-        <v>719</v>
+        <v>778</v>
       </c>
       <c r="F15" t="s">
-        <v>737</v>
+        <v>764</v>
       </c>
       <c r="G15" t="s">
-        <v>727</v>
-      </c>
-      <c r="H15" s="25"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="29" t="s">
-        <v>711</v>
-      </c>
-      <c r="B16" t="s">
-        <v>731</v>
+        <v>782</v>
+      </c>
+      <c r="H15" t="s">
+        <v>772</v>
+      </c>
+      <c r="I15" s="25"/>
+      <c r="J15" t="str">
+        <f>_xlfn.XLOOKUP(A15,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>SMS</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15">
+      <c r="A16" s="44" t="s">
+        <v>743</v>
+      </c>
+      <c r="B16" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
       </c>
       <c r="C16" t="s">
-        <v>734</v>
+        <v>776</v>
       </c>
       <c r="D16" t="s">
-        <v>733</v>
+        <v>779</v>
       </c>
       <c r="E16" t="s">
-        <v>719</v>
+        <v>778</v>
       </c>
       <c r="F16" t="s">
-        <v>737</v>
+        <v>764</v>
       </c>
       <c r="G16" t="s">
-        <v>727</v>
-      </c>
-      <c r="H16" s="25"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="29" t="s">
-        <v>712</v>
-      </c>
-      <c r="B17" t="s">
-        <v>731</v>
+        <v>782</v>
+      </c>
+      <c r="H16" t="s">
+        <v>772</v>
+      </c>
+      <c r="I16" s="25"/>
+      <c r="J16" t="str">
+        <f>_xlfn.XLOOKUP(A16,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>MMS</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15">
+      <c r="A17" s="44" t="s">
+        <v>744</v>
+      </c>
+      <c r="B17" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Sent;Received;Clicked</v>
       </c>
       <c r="C17" t="s">
-        <v>734</v>
-      </c>
-      <c r="E17" t="s">
-        <v>719</v>
-      </c>
-      <c r="H17" s="25"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="29" t="s">
-        <v>713</v>
-      </c>
-      <c r="B18" t="s">
-        <v>738</v>
+        <v>776</v>
+      </c>
+      <c r="D17" t="s">
+        <v>779</v>
+      </c>
+      <c r="F17" t="s">
+        <v>764</v>
+      </c>
+      <c r="I17" s="25"/>
+      <c r="J17" t="str">
+        <f>_xlfn.XLOOKUP(A17,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>App Push Notification</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15">
+      <c r="A18" s="44" t="s">
+        <v>749</v>
+      </c>
+      <c r="B18" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Invited;Attended</v>
       </c>
       <c r="C18" t="s">
-        <v>729</v>
-      </c>
-      <c r="H18" s="25"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="29" t="s">
-        <v>715</v>
-      </c>
-      <c r="B19" t="s">
-        <v>739</v>
+        <v>783</v>
+      </c>
+      <c r="D18" t="s">
+        <v>774</v>
+      </c>
+      <c r="I18" s="25"/>
+      <c r="J18" t="str">
+        <f>_xlfn.XLOOKUP(A18,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Sales Meetings</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15">
+      <c r="A19" s="44" t="s">
+        <v>751</v>
+      </c>
+      <c r="B19" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Dialled;Answered;Engaged</v>
       </c>
       <c r="C19" t="s">
-        <v>740</v>
+        <v>784</v>
       </c>
       <c r="D19" t="s">
-        <v>741</v>
-      </c>
-      <c r="H19" s="25"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="29" t="s">
-        <v>716</v>
-      </c>
-      <c r="B20" t="s">
-        <v>731</v>
+        <v>785</v>
+      </c>
+      <c r="E19" t="s">
+        <v>786</v>
+      </c>
+      <c r="I19" s="25"/>
+      <c r="J19" t="str">
+        <f>_xlfn.XLOOKUP(A19,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Sales Calls</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15">
+      <c r="A20" s="44" t="s">
+        <v>752</v>
+      </c>
+      <c r="B20" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
       </c>
       <c r="C20" t="s">
-        <v>734</v>
+        <v>776</v>
       </c>
       <c r="D20" t="s">
-        <v>733</v>
+        <v>779</v>
       </c>
       <c r="E20" t="s">
-        <v>736</v>
+        <v>778</v>
       </c>
       <c r="F20" t="s">
-        <v>719</v>
+        <v>781</v>
       </c>
       <c r="G20" t="s">
-        <v>727</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="30" t="s">
-        <v>742</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>743</v>
-      </c>
-      <c r="C21" s="26"/>
+        <v>764</v>
+      </c>
+      <c r="H20" t="s">
+        <v>772</v>
+      </c>
+      <c r="I20" s="25" t="s">
+        <v>771</v>
+      </c>
+      <c r="J20" t="str">
+        <f>_xlfn.XLOOKUP(A20,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Sales Email</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15">
+      <c r="A21" s="45" t="s">
+        <v>753</v>
+      </c>
+      <c r="B21" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v>Called</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>787</v>
+      </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
-      <c r="H21" s="27"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="27"/>
+      <c r="J21" t="str">
+        <f>_xlfn.XLOOKUP(A21,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Inbound Calls</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15">
+      <c r="A22" s="44" t="s">
+        <v>745</v>
+      </c>
+      <c r="B22" s="42" t="str">
+        <f t="shared" ref="B22:B23" si="1">_xlfn.TEXTJOIN(";",TRUE,C22:I22)</f>
+        <v>Attempted;Answered;Conversed</v>
+      </c>
+      <c r="C22" t="s">
+        <v>788</v>
+      </c>
+      <c r="D22" t="s">
+        <v>785</v>
+      </c>
+      <c r="E22" t="s">
+        <v>789</v>
+      </c>
+      <c r="I22" s="25"/>
+      <c r="J22" t="str">
+        <f>_xlfn.XLOOKUP(A22,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Telemarketing</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="44" t="s">
+        <v>747</v>
+      </c>
+      <c r="B23" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>Initiated;Answered;Disconnected</v>
+      </c>
+      <c r="C23" t="s">
+        <v>790</v>
+      </c>
+      <c r="D23" t="s">
+        <v>785</v>
+      </c>
+      <c r="E23" t="s">
+        <v>791</v>
+      </c>
+      <c r="I23" s="25"/>
+      <c r="J23" t="str">
+        <f>_xlfn.XLOOKUP(A23,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
+        <v>Online Chat</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:H1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D1F78A46A5B61544A3F5E5F9D558353B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd5889db134979e54dcf054cdc4727ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a7019f60-298e-442e-b6f6-687001478962" xmlns:ns3="244a3a2d-c3b8-4eaa-9334-4c3b8cbc7cc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fdf5543a8e45e11fa247a01810ff6e7b" ns2:_="" ns3:_="">
     <xsd:import namespace="a7019f60-298e-442e-b6f6-687001478962"/>
@@ -11780,7 +12605,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -11789,14 +12614,20 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51BB428E-D1CA-47E8-B784-F33B49A13D8D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51BB428E-D1CA-47E8-B784-F33B49A13D8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
 </file>
--- a/data/input/Low Level Field Detail Design(6).xlsx
+++ b/data/input/Low Level Field Detail Design(6).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgroupcloud.sharepoint.com/teams/CampaignManagementTransformation/Shared Documents/ROI and Attribution/Data Engineering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E6729C6-65E5-484D-96B1-009B6DAB83A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA6B9540-07E2-4BC7-BE4A-5E7C961D53C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="1" activeTab="4" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
   </bookViews>
   <sheets>
     <sheet name="objects" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="793">
   <si>
     <t>Name</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>Each Row represents the relationship between an outcome and an activity for a Given model.</t>
+  </si>
+  <si>
+    <t>Dependant</t>
   </si>
   <si>
     <t>Person</t>
@@ -6515,7 +6518,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6628,9 +6631,8 @@
   <autoFilter ref="A1:J167" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Attribution Linking Table"/>
-        <filter val="Company"/>
-        <filter val="Person Company Role"/>
+        <filter val="Attribution Model Output Table"/>
+        <filter val="Attrribution Model"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -7384,25 +7386,28 @@
       <c r="I9">
         <v>18</v>
       </c>
+      <c r="J9" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="57.95">
       <c r="A10" s="31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <f>COUNTIF(Attributes!A:A,objects!A10)</f>
@@ -7420,22 +7425,22 @@
     </row>
     <row r="11" spans="1:13" ht="87">
       <c r="A11" s="31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11">
         <f>COUNTIF(Attributes!A:A,objects!A11)</f>
@@ -7453,22 +7458,22 @@
     </row>
     <row r="12" spans="1:13" ht="57.95">
       <c r="A12" s="34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G12">
         <f>COUNTIF(Attributes!A:A,objects!A12)</f>
@@ -7480,25 +7485,28 @@
       <c r="I12">
         <v>8</v>
       </c>
+      <c r="J12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="13" spans="1:13" ht="43.5">
       <c r="A13" s="31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13">
         <f>COUNTIF(Attributes!A:A,objects!A13)</f>
@@ -7516,29 +7524,29 @@
     </row>
     <row r="14" spans="1:13" ht="101.45">
       <c r="A14" s="31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14">
         <f>COUNTIF(Attributes!A:A,objects!A14)</f>
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -7546,29 +7554,29 @@
     </row>
     <row r="15" spans="1:13" ht="57.95">
       <c r="A15" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15">
         <f>COUNTIF(Attributes!A:A,objects!A15)</f>
         <v>11</v>
       </c>
       <c r="H15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I15">
         <v>11</v>
@@ -7576,112 +7584,118 @@
     </row>
     <row r="16" spans="1:13" ht="43.5">
       <c r="A16" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G16">
         <f>COUNTIF(Attributes!A:A,objects!A16)</f>
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I16">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="57.95">
+    <row r="17" spans="1:10" ht="57.95">
       <c r="A17" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17">
         <f>COUNTIF(Attributes!A:A,objects!A17)</f>
         <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="I17">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="57.95">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="57.95">
       <c r="A18" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <f>COUNTIF(Attributes!A:A,objects!A18)</f>
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="I18">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="54.75" customHeight="1">
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="54.75" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H19" t="s">
         <v>27</v>
@@ -7690,24 +7704,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="43.5">
+    <row r="20" spans="1:10" ht="43.5">
       <c r="A20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B20" t="s">
         <v>53</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H20" t="s">
         <v>27</v>
@@ -7741,7 +7755,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -7750,343 +7764,343 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" hidden="1">
       <c r="A2" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" hidden="1">
       <c r="A3" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" hidden="1">
       <c r="A4" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" hidden="1">
       <c r="A5" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" hidden="1">
       <c r="A6" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" hidden="1">
       <c r="A7" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" hidden="1">
       <c r="A8" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="107.25" customHeight="1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="107.25" hidden="1" customHeight="1">
       <c r="A9" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" hidden="1">
       <c r="A10" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F10" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" hidden="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" hidden="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" hidden="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F13" t="s">
         <v>150</v>
       </c>
-      <c r="C13" t="s">
-        <v>151</v>
-      </c>
-      <c r="F13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" hidden="1">
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G14" s="16">
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
         <v>156</v>
       </c>
-      <c r="F15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" hidden="1">
-      <c r="A16" t="s">
-        <v>155</v>
-      </c>
       <c r="B16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G16" s="16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F18" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="43.5">
+      <c r="A20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" t="s">
+        <v>175</v>
+      </c>
+      <c r="F21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" t="s">
+        <v>178</v>
+      </c>
+      <c r="F22" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" hidden="1">
-      <c r="A17" t="s">
-        <v>155</v>
-      </c>
-      <c r="B17" t="s">
-        <v>161</v>
-      </c>
-      <c r="C17" t="s">
-        <v>162</v>
-      </c>
-      <c r="F17" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" hidden="1">
-      <c r="A18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F18" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" hidden="1">
-      <c r="A19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C19" t="s">
-        <v>167</v>
-      </c>
-      <c r="F19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="43.5" hidden="1">
-      <c r="A20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B20" t="s">
-        <v>168</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F20" t="s">
-        <v>129</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" hidden="1">
-      <c r="A21" t="s">
-        <v>155</v>
-      </c>
-      <c r="B21" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" t="s">
-        <v>174</v>
-      </c>
-      <c r="F21" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" hidden="1">
-      <c r="A22" t="s">
-        <v>155</v>
-      </c>
-      <c r="B22" t="s">
-        <v>176</v>
-      </c>
-      <c r="C22" t="s">
-        <v>177</v>
-      </c>
-      <c r="F22" t="s">
-        <v>159</v>
-      </c>
       <c r="G22" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:7" hidden="1">
@@ -8094,13 +8108,13 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C23" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:7" hidden="1">
@@ -8108,13 +8122,13 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:7" hidden="1">
@@ -8122,13 +8136,13 @@
         <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:7" hidden="1">
@@ -8136,13 +8150,13 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:7" hidden="1">
@@ -8150,13 +8164,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:7" hidden="1">
@@ -8164,16 +8178,16 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:7" hidden="1">
@@ -8181,13 +8195,13 @@
         <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C29" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:7" hidden="1">
@@ -8195,19 +8209,19 @@
         <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D30" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E30" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:7" hidden="1">
@@ -8215,10 +8229,10 @@
         <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32" spans="1:7" hidden="1">
@@ -8226,10 +8240,10 @@
         <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:7" hidden="1">
@@ -8237,16 +8251,16 @@
         <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C33" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D33" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="57.95" hidden="1">
@@ -8254,19 +8268,19 @@
         <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C34" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D34" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:7" hidden="1">
@@ -8274,13 +8288,13 @@
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C35" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="1:7" hidden="1">
@@ -8288,10 +8302,10 @@
         <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C36" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:7" hidden="1">
@@ -8299,10 +8313,10 @@
         <v>13</v>
       </c>
       <c r="B37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C37" t="s">
         <v>219</v>
-      </c>
-      <c r="C37" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:7" hidden="1">
@@ -8310,13 +8324,13 @@
         <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C38" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F38" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="130.5" hidden="1">
@@ -8324,13 +8338,13 @@
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:7" hidden="1">
@@ -8338,10 +8352,10 @@
         <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:7" hidden="1">
@@ -8349,16 +8363,16 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C41" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D41" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:7" hidden="1">
@@ -8366,16 +8380,16 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E42" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F42" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="43.5" hidden="1">
@@ -8383,19 +8397,19 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
+        <v>235</v>
+      </c>
+      <c r="C43" t="s">
+        <v>236</v>
+      </c>
+      <c r="E43" t="s">
         <v>234</v>
       </c>
-      <c r="C43" t="s">
-        <v>235</v>
-      </c>
-      <c r="E43" t="s">
-        <v>233</v>
-      </c>
       <c r="F43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="72.599999999999994" hidden="1">
@@ -8403,16 +8417,16 @@
         <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="43.5" hidden="1">
@@ -8420,16 +8434,16 @@
         <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:7" hidden="1">
@@ -8437,10 +8451,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47" spans="1:7" hidden="1">
@@ -8448,10 +8462,10 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C47" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:7" hidden="1">
@@ -8459,10 +8473,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="26.45" hidden="1">
@@ -8470,16 +8484,16 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C49" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F49" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G49" s="35" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="50" spans="1:10" hidden="1">
@@ -8487,10 +8501,10 @@
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:10" hidden="1">
@@ -8498,16 +8512,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C51" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J51" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:10" hidden="1">
@@ -8515,16 +8529,16 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C52" t="s">
+        <v>258</v>
+      </c>
+      <c r="F52" t="s">
+        <v>139</v>
+      </c>
+      <c r="J52" t="s">
         <v>256</v>
-      </c>
-      <c r="C52" t="s">
-        <v>257</v>
-      </c>
-      <c r="F52" t="s">
-        <v>138</v>
-      </c>
-      <c r="J52" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:10" hidden="1">
@@ -8532,13 +8546,13 @@
         <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:10" hidden="1">
@@ -8546,13 +8560,13 @@
         <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="55" spans="1:10" hidden="1">
@@ -8560,10 +8574,10 @@
         <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C55" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="56" spans="1:10" hidden="1">
@@ -8571,10 +8585,10 @@
         <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" spans="1:10" hidden="1">
@@ -8582,10 +8596,10 @@
         <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58" spans="1:10" hidden="1">
@@ -8593,10 +8607,10 @@
         <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C58" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" spans="1:10" hidden="1">
@@ -8604,16 +8618,16 @@
         <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C59" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D59" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60" spans="1:10" hidden="1">
@@ -8621,10 +8635,10 @@
         <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C60" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="57.95" hidden="1">
@@ -8632,22 +8646,22 @@
         <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F61" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J61" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="62" spans="1:10" hidden="1">
@@ -8655,10 +8669,10 @@
         <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -8668,10 +8682,10 @@
         <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -8681,303 +8695,303 @@
         <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
     </row>
     <row r="65" spans="1:10" hidden="1">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B65" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C65" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="66" spans="1:10" hidden="1">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B66" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J66" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" spans="1:10" hidden="1">
       <c r="A67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C67" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F67" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="68" spans="1:10" hidden="1">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C68" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F68" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="43.5" hidden="1">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C69" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F69" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="70" spans="1:10" hidden="1">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C70" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:10" hidden="1">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C71" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" spans="1:10" hidden="1">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C72"/>
     </row>
     <row r="73" spans="1:10" hidden="1">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C73"/>
     </row>
     <row r="74" spans="1:10" hidden="1">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C74"/>
     </row>
     <row r="75" spans="1:10" hidden="1">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C75"/>
     </row>
     <row r="76" spans="1:10" hidden="1">
       <c r="A76" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C76"/>
     </row>
     <row r="77" spans="1:10" hidden="1">
       <c r="A77" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B77" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C77" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F77" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:10" hidden="1">
       <c r="A78" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F78" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="79" spans="1:10" hidden="1">
       <c r="A79" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B79" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C79" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="1:10" hidden="1">
       <c r="A80" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B80" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F80" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81" spans="1:10" hidden="1">
       <c r="A81" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B81" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C81" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F81" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="82" spans="1:10" hidden="1">
       <c r="A82" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B82" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C82" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="83" spans="1:10" hidden="1">
       <c r="A83" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B83" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C83" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F83" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="84" spans="1:10" hidden="1">
       <c r="A84" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J84" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="85" spans="1:10" hidden="1">
       <c r="A85" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="86" spans="1:10" hidden="1">
       <c r="A86" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C86" s="4"/>
     </row>
     <row r="87" spans="1:10" hidden="1">
       <c r="A87" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="88" spans="1:10" hidden="1">
       <c r="A88" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="89" spans="1:10" hidden="1">
@@ -8985,13 +8999,13 @@
         <v>42</v>
       </c>
       <c r="B89" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C89" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D89" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="90" spans="1:10" hidden="1">
@@ -8999,13 +9013,13 @@
         <v>42</v>
       </c>
       <c r="B90" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C90" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F90" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15" hidden="1">
@@ -9013,7 +9027,7 @@
         <v>42</v>
       </c>
       <c r="B91" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="29.25" hidden="1">
@@ -9021,19 +9035,19 @@
         <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C92" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D92" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F92" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="15" hidden="1">
@@ -9041,10 +9055,10 @@
         <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C93" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="15" hidden="1">
@@ -9052,10 +9066,10 @@
         <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C94" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="15" hidden="1">
@@ -9063,10 +9077,10 @@
         <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="15" hidden="1">
@@ -9074,10 +9088,10 @@
         <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C96" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15" hidden="1">
@@ -9085,16 +9099,16 @@
         <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C97" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D97" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E97" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" hidden="1">
@@ -9102,16 +9116,16 @@
         <v>42</v>
       </c>
       <c r="B98" t="s">
+        <v>350</v>
+      </c>
+      <c r="C98" t="s">
+        <v>351</v>
+      </c>
+      <c r="D98" t="s">
+        <v>348</v>
+      </c>
+      <c r="E98" t="s">
         <v>349</v>
-      </c>
-      <c r="C98" t="s">
-        <v>350</v>
-      </c>
-      <c r="D98" t="s">
-        <v>347</v>
-      </c>
-      <c r="E98" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15" hidden="1">
@@ -9119,10 +9133,10 @@
         <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="15" hidden="1">
@@ -9130,10 +9144,10 @@
         <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="15" hidden="1">
@@ -9141,10 +9155,10 @@
         <v>42</v>
       </c>
       <c r="B101" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" hidden="1">
@@ -9152,10 +9166,10 @@
         <v>42</v>
       </c>
       <c r="B102" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C102" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15" hidden="1">
@@ -9163,10 +9177,10 @@
         <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C103" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="15" hidden="1">
@@ -9174,13 +9188,13 @@
         <v>42</v>
       </c>
       <c r="B104" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C104" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D104" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="15" hidden="1">
@@ -9188,13 +9202,13 @@
         <v>42</v>
       </c>
       <c r="B105" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C105" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F105" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="1:6" hidden="1">
@@ -9202,13 +9216,13 @@
         <v>28</v>
       </c>
       <c r="B106" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C106" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F106" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="107" spans="1:6" hidden="1">
@@ -9216,13 +9230,13 @@
         <v>28</v>
       </c>
       <c r="B107" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C107" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F107" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108" spans="1:6" hidden="1">
@@ -9230,301 +9244,301 @@
         <v>28</v>
       </c>
       <c r="B108" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C108" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F108" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:6" hidden="1">
       <c r="A109" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B109" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C109" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:6" hidden="1">
       <c r="A110" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B110" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C110"/>
     </row>
     <row r="111" spans="1:6" hidden="1">
       <c r="A111" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B111" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F111" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:6" hidden="1">
       <c r="A112" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B112" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F112" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113" spans="1:10" hidden="1">
       <c r="A113" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B113" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F113" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="114" spans="1:10" hidden="1">
       <c r="B114" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C114" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" hidden="1">
       <c r="A115" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B115" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C115"/>
       <c r="F115" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" hidden="1">
       <c r="A116" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B116" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C116"/>
       <c r="F116" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" hidden="1">
       <c r="A117" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B117" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C117" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F117" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J117" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" hidden="1">
       <c r="A118" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B118" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C118" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F118" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J118" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" hidden="1">
       <c r="A119" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B119" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C119" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F119" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" hidden="1">
       <c r="A120" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C120"/>
       <c r="F120" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" hidden="1">
       <c r="A121" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B121" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C121"/>
       <c r="F121" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" hidden="1">
       <c r="A122" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B122" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C122" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D122" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E122" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G122" s="16" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" hidden="1">
       <c r="A123" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B123" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C123" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D123" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E123" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G123" s="16" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" hidden="1">
       <c r="A124" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E124" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" hidden="1">
       <c r="A125" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C125" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F125" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G125" s="16" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="29.1" hidden="1">
+      <c r="A126" t="s">
+        <v>64</v>
+      </c>
+      <c r="B126" t="s">
+        <v>395</v>
+      </c>
+      <c r="C126" t="s">
+        <v>396</v>
+      </c>
+      <c r="D126" t="s">
+        <v>397</v>
+      </c>
+      <c r="E126" t="s">
+        <v>398</v>
+      </c>
+      <c r="F126" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" ht="29.1">
-      <c r="A126" t="s">
-        <v>63</v>
-      </c>
-      <c r="B126" t="s">
-        <v>394</v>
-      </c>
-      <c r="C126" t="s">
-        <v>395</v>
-      </c>
-      <c r="D126" t="s">
-        <v>396</v>
-      </c>
-      <c r="E126" t="s">
+      <c r="G126" s="16" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" hidden="1">
+      <c r="A127" t="s">
+        <v>64</v>
+      </c>
+      <c r="B127" t="s">
+        <v>400</v>
+      </c>
+      <c r="C127" t="s">
+        <v>401</v>
+      </c>
+      <c r="D127" t="s">
         <v>397</v>
       </c>
-      <c r="F126" t="s">
-        <v>392</v>
-      </c>
-      <c r="G126" s="16" t="s">
+      <c r="E127" t="s">
         <v>398</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10">
-      <c r="A127" t="s">
-        <v>63</v>
-      </c>
-      <c r="B127" t="s">
-        <v>399</v>
-      </c>
-      <c r="C127" t="s">
-        <v>400</v>
-      </c>
-      <c r="D127" t="s">
-        <v>396</v>
-      </c>
-      <c r="E127" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:10" hidden="1">
       <c r="B128" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C128" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="129" spans="1:7" hidden="1">
@@ -9532,7 +9546,7 @@
         <v>37</v>
       </c>
       <c r="B129" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C129"/>
     </row>
@@ -9541,10 +9555,10 @@
         <v>37</v>
       </c>
       <c r="B130" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C130" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="131" spans="1:7" hidden="1">
@@ -9552,10 +9566,10 @@
         <v>37</v>
       </c>
       <c r="B131" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C131" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="132" spans="1:7" hidden="1">
@@ -9563,10 +9577,10 @@
         <v>37</v>
       </c>
       <c r="B132" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C132" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="133" spans="1:7" hidden="1">
@@ -9574,10 +9588,10 @@
         <v>37</v>
       </c>
       <c r="B133" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C133" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="134" spans="1:7" s="4" customFormat="1" hidden="1">
@@ -9585,16 +9599,16 @@
         <v>37</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G134" s="6"/>
     </row>
@@ -9603,10 +9617,10 @@
         <v>37</v>
       </c>
       <c r="B135" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C135" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="136" spans="1:7" hidden="1">
@@ -9614,318 +9628,318 @@
         <v>37</v>
       </c>
       <c r="B136" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C136" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="137" spans="1:7" hidden="1">
       <c r="A137" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="29.1" hidden="1">
       <c r="A138" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="139" spans="1:7" hidden="1">
       <c r="A139" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F139" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="140" spans="1:7" hidden="1">
       <c r="A140" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="141" spans="1:7" hidden="1">
       <c r="A141" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="142" spans="1:7" hidden="1">
       <c r="A142" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="143" spans="1:7" hidden="1">
       <c r="A143" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="57.95" hidden="1">
       <c r="A144" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G144" s="16" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="29.1" hidden="1">
       <c r="A145" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="29.1" hidden="1">
       <c r="A146" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="147" spans="1:7" hidden="1">
       <c r="A147" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="148" spans="1:7" hidden="1">
       <c r="A148" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B148" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D148" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E148" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F148" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="149" spans="1:7" hidden="1">
       <c r="A149" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B149" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D149" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F149" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="150" spans="1:7" hidden="1">
       <c r="A150" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B150" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F150" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="151" spans="1:7" hidden="1">
       <c r="A151" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B151" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F151" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G151" s="16" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="152" spans="1:7" hidden="1">
       <c r="A152" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B152" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F152" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="153" spans="1:7" hidden="1">
       <c r="A153" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B153" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F153" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="154" spans="1:7" hidden="1">
       <c r="A154" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B154" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F154" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="155" spans="1:7" hidden="1">
       <c r="A155" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B155" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="156" spans="1:7" hidden="1">
       <c r="A156" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B156" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="157" spans="1:7" hidden="1">
       <c r="A157" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B157" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="158" spans="1:7" hidden="1">
       <c r="A158" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B158" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="159" spans="1:7" hidden="1">
       <c r="A159" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B159" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="160" spans="1:7" hidden="1">
       <c r="A160" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B160" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="161" spans="1:7" hidden="1">
       <c r="A161" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B161" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="162" spans="1:7" hidden="1">
@@ -9933,13 +9947,13 @@
         <v>28</v>
       </c>
       <c r="B162" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F162" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" hidden="1">
@@ -9947,13 +9961,13 @@
         <v>42</v>
       </c>
       <c r="B163" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C163" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F163" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="29.1" hidden="1">
@@ -9961,76 +9975,76 @@
         <v>21</v>
       </c>
       <c r="B164" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E164" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G164" s="16" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" hidden="1">
       <c r="A165" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B165" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E165" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F165" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G165" s="16" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="29.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="29.25" hidden="1">
       <c r="A166" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B166" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D166" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E166" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F166" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="29.25">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="29.25" hidden="1">
       <c r="A167" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B167" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D167" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E167" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F167" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15"/>
@@ -10081,55 +10095,55 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -10140,10 +10154,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E2" s="28">
         <v>1</v>
@@ -10155,7 +10169,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I2" s="3">
         <v>10</v>
@@ -10179,10 +10193,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E3" s="28">
         <v>1</v>
@@ -10194,7 +10208,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I3" s="3">
         <v>200</v>
@@ -10218,10 +10232,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E4" s="28">
         <v>2</v>
@@ -10231,7 +10245,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I4" s="3">
         <v>15</v>
@@ -10255,10 +10269,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E5" s="28">
         <v>3</v>
@@ -10268,7 +10282,7 @@
         <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -10292,10 +10306,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E6" s="28">
         <v>4</v>
@@ -10307,7 +10321,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I6" s="3">
         <v>0</v>
@@ -10331,10 +10345,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E7" s="28"/>
       <c r="F7" s="28">
@@ -10344,7 +10358,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I7" s="3">
         <v>256</v>
@@ -10368,10 +10382,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E8" s="28">
         <v>6</v>
@@ -10381,7 +10395,7 @@
         <v>7</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I8" s="3">
         <v>24</v>
@@ -10405,10 +10419,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="28">
@@ -10418,7 +10432,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="I9" s="3">
         <v>51</v>
@@ -10457,78 +10471,78 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D3" s="17"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D4" s="17"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D5" s="17"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D7" s="17"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -10536,47 +10550,47 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D9" s="17"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D10" s="17"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D11" s="17"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D12" s="17"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -10584,724 +10598,724 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D14" s="17"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D15" s="17"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D17" s="17"/>
     </row>
     <row r="18" spans="1:6">
       <c r="E18" s="13" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="43.5">
       <c r="A19" s="12" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="29.1">
       <c r="A20" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="57.95">
       <c r="A21" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="29.1">
       <c r="A22" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="130.5">
       <c r="A23" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="231.95">
       <c r="A24" s="12" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="57.95">
       <c r="A25" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="116.1">
       <c r="A26" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="57.95">
       <c r="A27" s="12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="57.95">
       <c r="A28" s="12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="57.95">
       <c r="A29" s="12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="57.95">
       <c r="A30" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="57.95">
       <c r="A31" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="43.5">
       <c r="A32" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C32" s="19"/>
       <c r="E32" s="14" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="12" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="29.1">
       <c r="A34" s="12" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="12" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="12" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="12" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="29.1">
       <c r="A40" s="12" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="57.95">
       <c r="A41" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="43.5">
       <c r="A42" s="12" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="43.5">
       <c r="A43" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="29.1">
       <c r="A44" s="12" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="101.45">
       <c r="A45" s="12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="29.1">
       <c r="A46" s="12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="12" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="12" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="43.5">
       <c r="A51" s="12" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="43.5">
       <c r="A52" s="12" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="12" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="130.5">
       <c r="A54" s="12" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="29.1">
       <c r="A55" s="12" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="12" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="43.5">
       <c r="A57" s="12" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="43.5">
       <c r="A58" s="12" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="29.1">
       <c r="A59" s="12" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="43.5">
       <c r="A60" s="12" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="43.5">
       <c r="A61" s="12" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="43.5">
       <c r="A62" s="12" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>
@@ -11323,45 +11337,45 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="B2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2" t="str">
         <f>_xlfn.XLOOKUP(B2,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11370,19 +11384,19 @@
     </row>
     <row r="3" spans="1:8">
       <c r="B3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C3" t="s">
+        <v>717</v>
+      </c>
+      <c r="D3" t="s">
+        <v>722</v>
+      </c>
+      <c r="E3" t="s">
+        <v>723</v>
+      </c>
+      <c r="G3" t="s">
         <v>720</v>
-      </c>
-      <c r="C3" t="s">
-        <v>716</v>
-      </c>
-      <c r="D3" t="s">
-        <v>721</v>
-      </c>
-      <c r="E3" t="s">
-        <v>722</v>
-      </c>
-      <c r="G3" t="s">
-        <v>719</v>
       </c>
       <c r="H3" t="str">
         <f>_xlfn.XLOOKUP(B3,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11391,19 +11405,19 @@
     </row>
     <row r="4" spans="1:8">
       <c r="B4" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D4" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H4" t="str">
         <f>_xlfn.XLOOKUP(B4,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11412,22 +11426,22 @@
     </row>
     <row r="5" spans="1:8">
       <c r="B5" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C5" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E5" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F5" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H5" t="str">
         <f>_xlfn.XLOOKUP(B5,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11436,19 +11450,19 @@
     </row>
     <row r="6" spans="1:8">
       <c r="B6" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C6" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D6" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E6" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G6" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H6" t="str">
         <f>_xlfn.XLOOKUP(B6,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11457,19 +11471,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="B7" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C7" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D7" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E7" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G7" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H7" t="str">
         <f>_xlfn.XLOOKUP(B7,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11478,19 +11492,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="B8" t="s">
+        <v>734</v>
+      </c>
+      <c r="C8" t="s">
+        <v>731</v>
+      </c>
+      <c r="D8" t="s">
+        <v>735</v>
+      </c>
+      <c r="E8" t="s">
+        <v>736</v>
+      </c>
+      <c r="G8" t="s">
         <v>733</v>
-      </c>
-      <c r="C8" t="s">
-        <v>730</v>
-      </c>
-      <c r="D8" t="s">
-        <v>734</v>
-      </c>
-      <c r="E8" t="s">
-        <v>735</v>
-      </c>
-      <c r="G8" t="s">
-        <v>732</v>
       </c>
       <c r="H8" t="str">
         <f>_xlfn.XLOOKUP(B8,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11499,19 +11513,19 @@
     </row>
     <row r="9" spans="1:8">
       <c r="B9" t="s">
+        <v>737</v>
+      </c>
+      <c r="C9" t="s">
+        <v>731</v>
+      </c>
+      <c r="D9" t="s">
+        <v>735</v>
+      </c>
+      <c r="E9" t="s">
         <v>736</v>
       </c>
-      <c r="C9" t="s">
-        <v>730</v>
-      </c>
-      <c r="D9" t="s">
-        <v>734</v>
-      </c>
-      <c r="E9" t="s">
-        <v>735</v>
-      </c>
       <c r="G9" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H9" t="str">
         <f>_xlfn.XLOOKUP(B9,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11520,16 +11534,16 @@
     </row>
     <row r="10" spans="1:8">
       <c r="B10" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C10" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D10" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E10" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H10" t="str">
         <f>_xlfn.XLOOKUP(B10,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11538,16 +11552,16 @@
     </row>
     <row r="11" spans="1:8">
       <c r="B11" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C11" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D11" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E11" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H11" t="str">
         <f>_xlfn.XLOOKUP(B11,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11556,16 +11570,16 @@
     </row>
     <row r="12" spans="1:8">
       <c r="B12" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C12" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E12" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H12" t="str">
         <f>_xlfn.XLOOKUP(B12,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11574,16 +11588,16 @@
     </row>
     <row r="13" spans="1:8">
       <c r="B13" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C13" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D13" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E13" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H13" t="str">
         <f>_xlfn.XLOOKUP(B13,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11592,16 +11606,16 @@
     </row>
     <row r="14" spans="1:8">
       <c r="B14" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C14" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D14" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E14" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H14" t="str">
         <f>_xlfn.XLOOKUP(B14,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11610,16 +11624,16 @@
     </row>
     <row r="15" spans="1:8">
       <c r="B15" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C15" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D15" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E15" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H15" t="str">
         <f>_xlfn.XLOOKUP(B15,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11628,16 +11642,16 @@
     </row>
     <row r="16" spans="1:8">
       <c r="B16" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C16" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D16" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E16" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H16" t="str">
         <f>_xlfn.XLOOKUP(B16,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11646,16 +11660,16 @@
     </row>
     <row r="17" spans="2:8">
       <c r="B17" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C17" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D17" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E17" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H17" t="str">
         <f>_xlfn.XLOOKUP(B17,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11664,16 +11678,16 @@
     </row>
     <row r="18" spans="2:8" ht="15">
       <c r="B18" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C18" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D18" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E18" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H18" t="str">
         <f>_xlfn.XLOOKUP(B18,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11682,16 +11696,16 @@
     </row>
     <row r="19" spans="2:8" ht="15">
       <c r="B19" t="s">
+        <v>748</v>
+      </c>
+      <c r="C19" t="s">
+        <v>731</v>
+      </c>
+      <c r="D19" t="s">
+        <v>749</v>
+      </c>
+      <c r="E19" t="s">
         <v>747</v>
-      </c>
-      <c r="C19" t="s">
-        <v>730</v>
-      </c>
-      <c r="D19" t="s">
-        <v>748</v>
-      </c>
-      <c r="E19" t="s">
-        <v>746</v>
       </c>
       <c r="H19" t="str">
         <f>_xlfn.XLOOKUP(B19,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11700,16 +11714,16 @@
     </row>
     <row r="20" spans="2:8">
       <c r="B20" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C20" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D20" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E20" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H20" t="str">
         <f>_xlfn.XLOOKUP(B20,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11718,16 +11732,16 @@
     </row>
     <row r="21" spans="2:8">
       <c r="B21" t="s">
+        <v>752</v>
+      </c>
+      <c r="C21" t="s">
         <v>751</v>
       </c>
-      <c r="C21" t="s">
-        <v>750</v>
-      </c>
       <c r="D21" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E21" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H21" t="str">
         <f>_xlfn.XLOOKUP(B21,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11736,16 +11750,16 @@
     </row>
     <row r="22" spans="2:8">
       <c r="B22" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C22" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D22" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E22" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H22" t="str">
         <f>_xlfn.XLOOKUP(B22,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11754,19 +11768,19 @@
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="47" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C23" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D23" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E23" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G23" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H23" t="str">
         <f>_xlfn.XLOOKUP(B23,Table2[Channel],Table2[Interactsion Concatnated],"",0,1)</f>
@@ -11803,52 +11817,52 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15">
       <c r="A1" s="40" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C1" s="37" t="s">
         <v>47</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="I1" s="38" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="J1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15">
       <c r="A2" s="44" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B2" s="41" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,C2:I2)</f>
         <v>Viewed;Clicked;Submit Form</v>
       </c>
       <c r="C2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="I2" s="25"/>
       <c r="J2" t="str">
@@ -11858,20 +11872,20 @@
     </row>
     <row r="3" spans="1:10" ht="15">
       <c r="A3" s="44" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B3" s="42" t="str">
         <f t="shared" ref="B3:B21" si="0">_xlfn.TEXTJOIN(";",TRUE,C3:I3)</f>
         <v>Viewed;Clicked;Submit Form</v>
       </c>
       <c r="C3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="I3" s="25"/>
       <c r="J3" t="str">
@@ -11881,29 +11895,29 @@
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="A4" s="44" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B4" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Page View;Link Click;Submit Form;Watch Video;Download;Live Chat?</v>
       </c>
       <c r="C4" t="s">
+        <v>767</v>
+      </c>
+      <c r="D4" t="s">
+        <v>768</v>
+      </c>
+      <c r="E4" t="s">
         <v>766</v>
       </c>
-      <c r="D4" t="s">
-        <v>767</v>
-      </c>
-      <c r="E4" t="s">
-        <v>765</v>
-      </c>
       <c r="F4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="G4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="I4" s="25"/>
       <c r="J4" t="str">
@@ -11913,14 +11927,14 @@
     </row>
     <row r="5" spans="1:10" ht="15">
       <c r="A5" s="44" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B5" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Viewed</v>
       </c>
       <c r="C5" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="I5" s="25"/>
       <c r="J5" t="str">
@@ -11930,20 +11944,20 @@
     </row>
     <row r="6" spans="1:10" ht="15">
       <c r="A6" s="44" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B6" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Viewed;Clicked;Responded</v>
       </c>
       <c r="C6" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D6" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E6" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="I6" s="25"/>
       <c r="J6" t="str">
@@ -11953,23 +11967,23 @@
     </row>
     <row r="7" spans="1:10" ht="15">
       <c r="A7" s="44" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B7" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Viewed;Clicked;Responded;Opt-Out</v>
       </c>
       <c r="C7" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D7" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E7" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F7" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I7" s="25"/>
       <c r="J7" t="str">
@@ -11979,20 +11993,20 @@
     </row>
     <row r="8" spans="1:10" ht="15">
       <c r="A8" s="44" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B8" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Registered;Attended;View on Demand</v>
       </c>
       <c r="C8" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D8" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E8" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I8" s="25"/>
       <c r="J8" t="str">
@@ -12002,17 +12016,17 @@
     </row>
     <row r="9" spans="1:10" ht="15">
       <c r="A9" s="44" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B9" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Registered;Attended</v>
       </c>
       <c r="C9" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="I9" s="25"/>
       <c r="J9" t="str">
@@ -12022,20 +12036,20 @@
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="A10" s="44" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B10" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Registered;Attended;View on Demand</v>
       </c>
       <c r="C10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D10" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E10" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I10" s="25"/>
       <c r="J10" t="str">
@@ -12045,20 +12059,20 @@
     </row>
     <row r="11" spans="1:10" ht="15">
       <c r="A11" s="44" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B11" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Sent;Delivered;Bounced</v>
       </c>
       <c r="C11" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D11" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E11" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="I11" s="25"/>
       <c r="J11" t="str">
@@ -12068,29 +12082,29 @@
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="A12" s="44" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B12" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
       </c>
       <c r="C12" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D12" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E12" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F12" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="G12" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H12" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I12" s="25"/>
       <c r="J12" t="str">
@@ -12100,29 +12114,29 @@
     </row>
     <row r="13" spans="1:10" ht="15">
       <c r="A13" s="44" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B13" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Sent;Received;Read;Clicked;Responded;Opt-Out</v>
       </c>
       <c r="C13" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D13" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E13" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F13" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="G13" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H13" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" t="str">
@@ -12132,32 +12146,32 @@
     </row>
     <row r="14" spans="1:10" ht="15">
       <c r="A14" s="44" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B14" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
       </c>
       <c r="C14" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D14" t="s">
+        <v>780</v>
+      </c>
+      <c r="E14" t="s">
         <v>779</v>
       </c>
-      <c r="E14" t="s">
-        <v>778</v>
-      </c>
       <c r="F14" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G14" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H14" t="s">
+        <v>773</v>
+      </c>
+      <c r="I14" s="25" t="s">
         <v>772</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>771</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(A14,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
@@ -12166,29 +12180,29 @@
     </row>
     <row r="15" spans="1:10" ht="15">
       <c r="A15" s="44" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B15" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
       </c>
       <c r="C15" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D15" t="s">
+        <v>780</v>
+      </c>
+      <c r="E15" t="s">
         <v>779</v>
       </c>
-      <c r="E15" t="s">
-        <v>778</v>
-      </c>
       <c r="F15" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="G15" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H15" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I15" s="25"/>
       <c r="J15" t="str">
@@ -12198,29 +12212,29 @@
     </row>
     <row r="16" spans="1:10" ht="15">
       <c r="A16" s="44" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B16" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Sent;Received;Bounced;Clicked;Responsed;Opt-Out</v>
       </c>
       <c r="C16" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D16" t="s">
+        <v>780</v>
+      </c>
+      <c r="E16" t="s">
         <v>779</v>
       </c>
-      <c r="E16" t="s">
-        <v>778</v>
-      </c>
       <c r="F16" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="G16" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H16" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I16" s="25"/>
       <c r="J16" t="str">
@@ -12230,20 +12244,20 @@
     </row>
     <row r="17" spans="1:10" ht="15">
       <c r="A17" s="44" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B17" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Sent;Received;Clicked</v>
       </c>
       <c r="C17" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D17" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F17" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="I17" s="25"/>
       <c r="J17" t="str">
@@ -12253,17 +12267,17 @@
     </row>
     <row r="18" spans="1:10" ht="15">
       <c r="A18" s="44" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B18" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Invited;Attended</v>
       </c>
       <c r="C18" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D18" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="I18" s="25"/>
       <c r="J18" t="str">
@@ -12273,20 +12287,20 @@
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="A19" s="44" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B19" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Dialled;Answered;Engaged</v>
       </c>
       <c r="C19" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D19" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E19" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="I19" s="25"/>
       <c r="J19" t="str">
@@ -12296,32 +12310,32 @@
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" s="44" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B20" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Sent;Received;Bounced;Opened;Clicked;Opt-Out;Responded</v>
       </c>
       <c r="C20" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D20" t="s">
+        <v>780</v>
+      </c>
+      <c r="E20" t="s">
         <v>779</v>
       </c>
-      <c r="E20" t="s">
-        <v>778</v>
-      </c>
       <c r="F20" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G20" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H20" t="s">
+        <v>773</v>
+      </c>
+      <c r="I20" s="25" t="s">
         <v>772</v>
-      </c>
-      <c r="I20" s="25" t="s">
-        <v>771</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(A20,Channels!B:B,Channels!B:B,"MISSING",0,1)</f>
@@ -12330,14 +12344,14 @@
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="A21" s="45" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B21" s="43" t="str">
         <f t="shared" si="0"/>
         <v>Called</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
@@ -12352,20 +12366,20 @@
     </row>
     <row r="22" spans="1:10" ht="15">
       <c r="A22" s="44" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B22" s="42" t="str">
         <f t="shared" ref="B22:B23" si="1">_xlfn.TEXTJOIN(";",TRUE,C22:I22)</f>
         <v>Attempted;Answered;Conversed</v>
       </c>
       <c r="C22" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D22" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E22" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="I22" s="25"/>
       <c r="J22" t="str">
@@ -12375,20 +12389,20 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="44" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B23" s="42" t="str">
         <f t="shared" si="1"/>
         <v>Initiated;Answered;Disconnected</v>
       </c>
       <c r="C23" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D23" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E23" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="I23" s="25"/>
       <c r="J23" t="str">
@@ -12405,6 +12419,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D1F78A46A5B61544A3F5E5F9D558353B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd5889db134979e54dcf054cdc4727ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a7019f60-298e-442e-b6f6-687001478962" xmlns:ns3="244a3a2d-c3b8-4eaa-9334-4c3b8cbc7cc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fdf5543a8e45e11fa247a01810ff6e7b" ns2:_="" ns3:_="">
     <xsd:import namespace="a7019f60-298e-442e-b6f6-687001478962"/>
@@ -12605,29 +12634,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51BB428E-D1CA-47E8-B784-F33B49A13D8D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51BB428E-D1CA-47E8-B784-F33B49A13D8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
 </file>
--- a/data/input/Low Level Field Detail Design(6).xlsx
+++ b/data/input/Low Level Field Detail Design(6).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgroupcloud.sharepoint.com/teams/CampaignManagementTransformation/Shared Documents/ROI and Attribution/Data Engineering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA6B9540-07E2-4BC7-BE4A-5E7C961D53C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9CABA46-BF39-46C6-A7D5-944861D4720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
   </bookViews>
@@ -7077,6 +7077,7 @@
     <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="28" customWidth="1"/>
     <col min="12" max="12" width="31.85546875" customWidth="1"/>
     <col min="13" max="13" width="22.28515625" customWidth="1"/>
@@ -7321,7 +7322,7 @@
         <v>15</v>
       </c>
       <c r="J7">
-        <v>10000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="72.599999999999994">
@@ -7354,7 +7355,7 @@
         <v>17</v>
       </c>
       <c r="J8">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="29.1">
@@ -7420,7 +7421,7 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>5000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="87">
@@ -7453,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="J11">
-        <v>3000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="57.95">
@@ -7519,7 +7520,7 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>7000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="101.45">
@@ -12419,21 +12420,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D1F78A46A5B61544A3F5E5F9D558353B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd5889db134979e54dcf054cdc4727ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a7019f60-298e-442e-b6f6-687001478962" xmlns:ns3="244a3a2d-c3b8-4eaa-9334-4c3b8cbc7cc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fdf5543a8e45e11fa247a01810ff6e7b" ns2:_="" ns3:_="">
     <xsd:import namespace="a7019f60-298e-442e-b6f6-687001478962"/>
@@ -12634,8 +12620,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51BB428E-D1CA-47E8-B784-F33B49A13D8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12643,5 +12644,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51BB428E-D1CA-47E8-B784-F33B49A13D8D}"/>
 </file>
--- a/data/input/Low Level Field Detail Design(6).xlsx
+++ b/data/input/Low Level Field Detail Design(6).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://btgroupcloud.sharepoint.com/teams/CampaignManagementTransformation/Shared Documents/ROI and Attribution/Data Engineering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9CABA46-BF39-46C6-A7D5-944861D4720A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F159CB11-530D-4788-8D07-F07A13A7A3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" xr2:uid="{EFC15C39-DC71-4D84-BB64-C304B1E6FB49}"/>
   </bookViews>
   <sheets>
     <sheet name="objects" sheetId="1" r:id="rId1"/>
@@ -6631,8 +6631,7 @@
   <autoFilter ref="A1:J167" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Attribution Model Output Table"/>
-        <filter val="Attrribution Model"/>
+        <filter val="Orders"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -7066,7 +7065,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF98BEB6-65EB-437D-B437-4DFA85EC4A08}">
   <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.42578125" bestFit="1" customWidth="1"/>
@@ -7124,7 +7123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="72.599999999999994">
+    <row r="2" spans="1:13" ht="90">
       <c r="A2" s="31" t="s">
         <v>13</v>
       </c>
@@ -7160,7 +7159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="72.599999999999994">
+    <row r="3" spans="1:13" ht="75">
       <c r="A3" s="32" t="s">
         <v>21</v>
       </c>
@@ -7193,7 +7192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="72.599999999999994">
+    <row r="4" spans="1:13" ht="75">
       <c r="A4" s="32" t="s">
         <v>28</v>
       </c>
@@ -7226,7 +7225,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="57.95">
+    <row r="5" spans="1:13" ht="60">
       <c r="A5" s="9" t="s">
         <v>33</v>
       </c>
@@ -7259,7 +7258,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="43.5">
+    <row r="6" spans="1:13" ht="60">
       <c r="A6" s="7" t="s">
         <v>37</v>
       </c>
@@ -7292,7 +7291,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="101.45">
+    <row r="7" spans="1:13" ht="105">
       <c r="A7" s="31" t="s">
         <v>42</v>
       </c>
@@ -7325,7 +7324,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="72.599999999999994">
+    <row r="8" spans="1:13" ht="105">
       <c r="A8" s="31" t="s">
         <v>47</v>
       </c>
@@ -7358,7 +7357,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="29.1">
+    <row r="9" spans="1:13" ht="30">
       <c r="A9" s="7" t="s">
         <v>52</v>
       </c>
@@ -7391,7 +7390,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="57.95">
+    <row r="10" spans="1:13" ht="75">
       <c r="A10" s="31" t="s">
         <v>59</v>
       </c>
@@ -7424,7 +7423,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="87">
+    <row r="11" spans="1:13" ht="120">
       <c r="A11" s="31" t="s">
         <v>64</v>
       </c>
@@ -7457,7 +7456,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="57.95">
+    <row r="12" spans="1:13" ht="60">
       <c r="A12" s="34" t="s">
         <v>69</v>
       </c>
@@ -7490,7 +7489,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="43.5">
+    <row r="13" spans="1:13" ht="45">
       <c r="A13" s="31" t="s">
         <v>74</v>
       </c>
@@ -7520,10 +7519,10 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>7000000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="101.45">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="105">
       <c r="A14" s="31" t="s">
         <v>79</v>
       </c>
@@ -7553,7 +7552,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="57.95">
+    <row r="15" spans="1:13" ht="60">
       <c r="A15" s="7" t="s">
         <v>83</v>
       </c>
@@ -7583,7 +7582,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="43.5">
+    <row r="16" spans="1:13" ht="45">
       <c r="A16" s="7" t="s">
         <v>87</v>
       </c>
@@ -7613,7 +7612,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="57.95">
+    <row r="17" spans="1:10" ht="60">
       <c r="A17" s="3" t="s">
         <v>90</v>
       </c>
@@ -7646,7 +7645,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="57.95">
+    <row r="18" spans="1:10" ht="75">
       <c r="A18" s="3" t="s">
         <v>96</v>
       </c>
@@ -7705,7 +7704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="43.5">
+    <row r="20" spans="1:10" ht="45">
       <c r="A20" s="3" t="s">
         <v>106</v>
       </c>
@@ -7739,8 +7738,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE1AD4F9-4E3A-41DA-9532-E435FAC78061}">
-  <dimension ref="A1:J171"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:J167"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.85546875" bestFit="1" customWidth="1"/>
@@ -7915,7 +7914,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" hidden="1">
       <c r="A11" t="s">
         <v>90</v>
       </c>
@@ -7929,7 +7928,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" hidden="1">
       <c r="A12" t="s">
         <v>90</v>
       </c>
@@ -7943,7 +7942,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" hidden="1">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -7957,7 +7956,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" hidden="1">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -7974,7 +7973,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" hidden="1">
       <c r="A15" t="s">
         <v>156</v>
       </c>
@@ -7988,7 +7987,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" hidden="1">
       <c r="A16" t="s">
         <v>156</v>
       </c>
@@ -8005,7 +8004,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>156</v>
       </c>
@@ -8019,7 +8018,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>156</v>
       </c>
@@ -8033,7 +8032,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>156</v>
       </c>
@@ -8047,7 +8046,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="43.5">
+    <row r="20" spans="1:7" ht="45" hidden="1">
       <c r="A20" t="s">
         <v>156</v>
       </c>
@@ -8070,7 +8069,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>156</v>
       </c>
@@ -8087,7 +8086,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>156</v>
       </c>
@@ -8264,7 +8263,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="57.95" hidden="1">
+    <row r="34" spans="1:7" ht="60" hidden="1">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -8334,7 +8333,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="130.5" hidden="1">
+    <row r="39" spans="1:7" ht="135" hidden="1">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -8393,7 +8392,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="43.5" hidden="1">
+    <row r="43" spans="1:7" ht="45" hidden="1">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -8413,7 +8412,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="72.599999999999994" hidden="1">
+    <row r="44" spans="1:7" ht="75" hidden="1">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -8430,7 +8429,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="43.5" hidden="1">
+    <row r="45" spans="1:7" ht="45" hidden="1">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -8480,7 +8479,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="26.45" hidden="1">
+    <row r="49" spans="1:10" ht="27" hidden="1">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -8642,7 +8641,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="57.95" hidden="1">
+    <row r="61" spans="1:10" ht="60" hidden="1">
       <c r="A61" s="4" t="s">
         <v>33</v>
       </c>
@@ -8704,7 +8703,7 @@
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
     </row>
-    <row r="65" spans="1:10" hidden="1">
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -8715,7 +8714,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1">
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -8729,7 +8728,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1">
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -8743,7 +8742,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1">
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
         <v>74</v>
       </c>
@@ -8760,7 +8759,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="43.5" hidden="1">
+    <row r="69" spans="1:10" ht="45">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -8777,7 +8776,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1">
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -8788,7 +8787,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1">
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -8799,7 +8798,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1">
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -8808,7 +8807,7 @@
       </c>
       <c r="C72"/>
     </row>
-    <row r="73" spans="1:10" hidden="1">
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -8817,7 +8816,7 @@
       </c>
       <c r="C73"/>
     </row>
-    <row r="74" spans="1:10" hidden="1">
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -8826,7 +8825,7 @@
       </c>
       <c r="C74"/>
     </row>
-    <row r="75" spans="1:10" hidden="1">
+    <row r="75" spans="1:10">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -8835,7 +8834,7 @@
       </c>
       <c r="C75"/>
     </row>
-    <row r="76" spans="1:10" hidden="1">
+    <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
         <v>74</v>
       </c>
@@ -8844,7 +8843,7 @@
       </c>
       <c r="C76"/>
     </row>
-    <row r="77" spans="1:10" hidden="1">
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
         <v>74</v>
       </c>
@@ -8858,7 +8857,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1">
+    <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
         <v>74</v>
       </c>
@@ -8872,7 +8871,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1">
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
         <v>74</v>
       </c>
@@ -8883,7 +8882,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1">
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
         <v>74</v>
       </c>
@@ -8897,7 +8896,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1">
+    <row r="81" spans="1:10">
       <c r="A81" t="s">
         <v>74</v>
       </c>
@@ -8914,7 +8913,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1">
+    <row r="82" spans="1:10">
       <c r="A82" t="s">
         <v>74</v>
       </c>
@@ -8925,7 +8924,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1">
+    <row r="83" spans="1:10">
       <c r="A83" t="s">
         <v>74</v>
       </c>
@@ -8939,7 +8938,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1">
+    <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
         <v>74</v>
       </c>
@@ -8953,7 +8952,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1">
+    <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
         <v>74</v>
       </c>
@@ -8964,7 +8963,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1">
+    <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
         <v>74</v>
       </c>
@@ -8973,7 +8972,7 @@
       </c>
       <c r="C86" s="4"/>
     </row>
-    <row r="87" spans="1:10" hidden="1">
+    <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
         <v>74</v>
       </c>
@@ -8984,7 +8983,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1">
+    <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
         <v>74</v>
       </c>
@@ -9023,7 +9022,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15" hidden="1">
+    <row r="91" spans="1:10" hidden="1">
       <c r="A91" s="3" t="s">
         <v>42</v>
       </c>
@@ -9031,7 +9030,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="29.25" hidden="1">
+    <row r="92" spans="1:10" ht="45" hidden="1">
       <c r="A92" t="s">
         <v>42</v>
       </c>
@@ -9051,7 +9050,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="15" hidden="1">
+    <row r="93" spans="1:10" hidden="1">
       <c r="A93" t="s">
         <v>42</v>
       </c>
@@ -9062,7 +9061,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15" hidden="1">
+    <row r="94" spans="1:10" hidden="1">
       <c r="A94" t="s">
         <v>42</v>
       </c>
@@ -9073,7 +9072,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="15" hidden="1">
+    <row r="95" spans="1:10" hidden="1">
       <c r="A95" t="s">
         <v>42</v>
       </c>
@@ -9084,7 +9083,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="15" hidden="1">
+    <row r="96" spans="1:10" hidden="1">
       <c r="A96" t="s">
         <v>42</v>
       </c>
@@ -9095,7 +9094,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="15" hidden="1">
+    <row r="97" spans="1:6" hidden="1">
       <c r="A97" t="s">
         <v>42</v>
       </c>
@@ -9112,7 +9111,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="15" hidden="1">
+    <row r="98" spans="1:6" hidden="1">
       <c r="A98" t="s">
         <v>42</v>
       </c>
@@ -9129,7 +9128,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15" hidden="1">
+    <row r="99" spans="1:6" hidden="1">
       <c r="A99" t="s">
         <v>42</v>
       </c>
@@ -9140,7 +9139,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="15" hidden="1">
+    <row r="100" spans="1:6" hidden="1">
       <c r="A100" t="s">
         <v>42</v>
       </c>
@@ -9151,7 +9150,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15" hidden="1">
+    <row r="101" spans="1:6" hidden="1">
       <c r="A101" t="s">
         <v>42</v>
       </c>
@@ -9162,7 +9161,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15" hidden="1">
+    <row r="102" spans="1:6" hidden="1">
       <c r="A102" t="s">
         <v>42</v>
       </c>
@@ -9173,7 +9172,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15" hidden="1">
+    <row r="103" spans="1:6" hidden="1">
       <c r="A103" t="s">
         <v>42</v>
       </c>
@@ -9184,7 +9183,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="15" hidden="1">
+    <row r="104" spans="1:6" hidden="1">
       <c r="A104" t="s">
         <v>42</v>
       </c>
@@ -9198,7 +9197,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="15" hidden="1">
+    <row r="105" spans="1:6" hidden="1">
       <c r="A105" t="s">
         <v>42</v>
       </c>
@@ -9494,7 +9493,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="29.1" hidden="1">
+    <row r="126" spans="1:10" ht="30" hidden="1">
       <c r="A126" t="s">
         <v>64</v>
       </c>
@@ -9646,7 +9645,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="29.1" hidden="1">
+    <row r="138" spans="1:7" ht="30" hidden="1">
       <c r="A138" s="4" t="s">
         <v>83</v>
       </c>
@@ -9715,7 +9714,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="57.95" hidden="1">
+    <row r="144" spans="1:7" ht="60" hidden="1">
       <c r="A144" s="4" t="s">
         <v>83</v>
       </c>
@@ -9729,7 +9728,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="29.1" hidden="1">
+    <row r="145" spans="1:7" ht="30" hidden="1">
       <c r="A145" s="4" t="s">
         <v>83</v>
       </c>
@@ -9740,7 +9739,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="29.1" hidden="1">
+    <row r="146" spans="1:7" ht="30" hidden="1">
       <c r="A146" s="4" t="s">
         <v>83</v>
       </c>
@@ -9957,7 +9956,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="15" hidden="1">
+    <row r="163" spans="1:7" hidden="1">
       <c r="A163" t="s">
         <v>42</v>
       </c>
@@ -9971,7 +9970,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="29.1" hidden="1">
+    <row r="164" spans="1:7" ht="30" hidden="1">
       <c r="A164" s="3" t="s">
         <v>21</v>
       </c>
@@ -10008,7 +10007,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="29.25" hidden="1">
+    <row r="166" spans="1:7" ht="30" hidden="1">
       <c r="A166" s="39" t="s">
         <v>52</v>
       </c>
@@ -10028,7 +10027,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="29.25" hidden="1">
+    <row r="167" spans="1:7" ht="30" hidden="1">
       <c r="A167" s="39" t="s">
         <v>52</v>
       </c>
@@ -10048,8 +10047,6 @@
         <v>474</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="15"/>
-    <row r="171" spans="1:7" ht="15"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J105">
     <sortCondition ref="A2:A105"/>
@@ -10081,7 +10078,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FEA969B-2E99-43A3-91BB-BD5F9824B477}">
   <dimension ref="A1:T9"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
@@ -10457,7 +10454,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2AC8CA7-C3B2-4113-BDC9-28FC11714663}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="47.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.7109375" style="16" customWidth="1"/>
@@ -10467,7 +10464,7 @@
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10579,7 +10576,7 @@
       </c>
       <c r="D11" s="17"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="30">
       <c r="A12" s="11" t="s">
         <v>526</v>
       </c>
@@ -10645,7 +10642,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="43.5">
+    <row r="19" spans="1:6" ht="45">
       <c r="A19" s="12" t="s">
         <v>539</v>
       </c>
@@ -10662,7 +10659,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="29.1">
+    <row r="20" spans="1:6" ht="30">
       <c r="A20" s="12" t="s">
         <v>544</v>
       </c>
@@ -10679,7 +10676,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="57.95">
+    <row r="21" spans="1:6" ht="60">
       <c r="A21" s="12" t="s">
         <v>507</v>
       </c>
@@ -10699,7 +10696,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="29.1">
+    <row r="22" spans="1:6" ht="30">
       <c r="A22" s="12" t="s">
         <v>554</v>
       </c>
@@ -10716,7 +10713,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="130.5">
+    <row r="23" spans="1:6" ht="135">
       <c r="A23" s="12" t="s">
         <v>559</v>
       </c>
@@ -10733,7 +10730,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="231.95">
+    <row r="24" spans="1:6" ht="270">
       <c r="A24" s="12" t="s">
         <v>563</v>
       </c>
@@ -10750,7 +10747,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="57.95">
+    <row r="25" spans="1:6" ht="75">
       <c r="A25" s="12" t="s">
         <v>567</v>
       </c>
@@ -10767,7 +10764,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="116.1">
+    <row r="26" spans="1:6" ht="120">
       <c r="A26" s="12" t="s">
         <v>572</v>
       </c>
@@ -10784,7 +10781,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="57.95">
+    <row r="27" spans="1:6" ht="75">
       <c r="A27" s="12" t="s">
         <v>576</v>
       </c>
@@ -10798,7 +10795,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="57.95">
+    <row r="28" spans="1:6" ht="75">
       <c r="A28" s="12" t="s">
         <v>579</v>
       </c>
@@ -10812,7 +10809,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="57.95">
+    <row r="29" spans="1:6" ht="75">
       <c r="A29" s="12" t="s">
         <v>582</v>
       </c>
@@ -10826,7 +10823,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="57.95">
+    <row r="30" spans="1:6" ht="75">
       <c r="A30" s="12" t="s">
         <v>585</v>
       </c>
@@ -10840,7 +10837,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="57.95">
+    <row r="31" spans="1:6" ht="75">
       <c r="A31" s="12" t="s">
         <v>588</v>
       </c>
@@ -10857,7 +10854,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="43.5">
+    <row r="32" spans="1:6" ht="45">
       <c r="A32" s="12" t="s">
         <v>592</v>
       </c>
@@ -10872,7 +10869,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" ht="30">
       <c r="A33" s="12" t="s">
         <v>596</v>
       </c>
@@ -10886,7 +10883,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="29.1">
+    <row r="34" spans="1:6" ht="30">
       <c r="A34" s="12" t="s">
         <v>600</v>
       </c>
@@ -10979,7 +10976,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="29.1">
+    <row r="40" spans="1:6" ht="45">
       <c r="A40" s="12" t="s">
         <v>623</v>
       </c>
@@ -10993,7 +10990,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="57.95">
+    <row r="41" spans="1:6" ht="60">
       <c r="A41" s="12" t="s">
         <v>627</v>
       </c>
@@ -11007,7 +11004,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="43.5">
+    <row r="42" spans="1:6" ht="60">
       <c r="A42" s="12" t="s">
         <v>631</v>
       </c>
@@ -11024,7 +11021,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="43.5">
+    <row r="43" spans="1:6" ht="45">
       <c r="A43" s="12" t="s">
         <v>636</v>
       </c>
@@ -11041,7 +11038,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="29.1">
+    <row r="44" spans="1:6" ht="30">
       <c r="A44" s="12" t="s">
         <v>641</v>
       </c>
@@ -11058,7 +11055,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="101.45">
+    <row r="45" spans="1:6" ht="105">
       <c r="A45" s="12" t="s">
         <v>646</v>
       </c>
@@ -11075,7 +11072,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="29.1">
+    <row r="46" spans="1:6" ht="45">
       <c r="A46" s="12" t="s">
         <v>651</v>
       </c>
@@ -11089,7 +11086,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" ht="30">
       <c r="A47" s="12" t="s">
         <v>654</v>
       </c>
@@ -11103,7 +11100,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" ht="30">
       <c r="A48" s="12" t="s">
         <v>658</v>
       </c>
@@ -11145,7 +11142,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="43.5">
+    <row r="51" spans="1:6" ht="60">
       <c r="A51" s="12" t="s">
         <v>668</v>
       </c>
@@ -11159,7 +11156,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="43.5">
+    <row r="52" spans="1:6" ht="60">
       <c r="A52" s="12" t="s">
         <v>672</v>
       </c>
@@ -11187,7 +11184,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="130.5">
+    <row r="54" spans="1:6" ht="165">
       <c r="A54" s="12" t="s">
         <v>679</v>
       </c>
@@ -11204,7 +11201,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="29.1">
+    <row r="55" spans="1:6" ht="30">
       <c r="A55" s="12" t="s">
         <v>684</v>
       </c>
@@ -11235,7 +11232,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="43.5">
+    <row r="57" spans="1:6" ht="60">
       <c r="A57" s="12" t="s">
         <v>691</v>
       </c>
@@ -11249,7 +11246,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="43.5">
+    <row r="58" spans="1:6" ht="60">
       <c r="A58" s="12" t="s">
         <v>694</v>
       </c>
@@ -11263,7 +11260,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="29.1">
+    <row r="59" spans="1:6" ht="45">
       <c r="A59" s="12" t="s">
         <v>697</v>
       </c>
@@ -11277,7 +11274,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="43.5">
+    <row r="60" spans="1:6" ht="45">
       <c r="A60" s="12" t="s">
         <v>700</v>
       </c>
@@ -11291,7 +11288,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="43.5">
+    <row r="61" spans="1:6" ht="45">
       <c r="A61" s="12" t="s">
         <v>704</v>
       </c>
@@ -11305,7 +11302,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="43.5">
+    <row r="62" spans="1:6" ht="45">
       <c r="A62" s="12" t="s">
         <v>707</v>
       </c>
@@ -11328,7 +11325,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8D126A-E50F-4373-9159-5B9100CAC9A2}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="32.28515625" customWidth="1"/>
     <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
@@ -11677,7 +11674,7 @@
         <v>Sent;Received;Clicked</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15">
+    <row r="18" spans="2:8">
       <c r="B18" t="s">
         <v>746</v>
       </c>
@@ -11695,7 +11692,7 @@
         <v>Attempted;Answered;Conversed</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15">
+    <row r="19" spans="2:8">
       <c r="B19" t="s">
         <v>748</v>
       </c>
@@ -11804,7 +11801,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAF728D-8DC4-43CB-A2BE-8E22F440F4CC}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="61.85546875" bestFit="1" customWidth="1"/>
@@ -11816,7 +11813,7 @@
     <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15">
+    <row r="1" spans="1:10">
       <c r="A1" s="40" t="s">
         <v>755</v>
       </c>
@@ -11848,7 +11845,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15">
+    <row r="2" spans="1:10">
       <c r="A2" s="44" t="s">
         <v>716</v>
       </c>
@@ -11871,7 +11868,7 @@
         <v>Paid Digital Ads</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15">
+    <row r="3" spans="1:10">
       <c r="A3" s="44" t="s">
         <v>721</v>
       </c>
@@ -11894,7 +11891,7 @@
         <v>Content Syndication</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15">
+    <row r="4" spans="1:10">
       <c r="A4" s="44" t="s">
         <v>724</v>
       </c>
@@ -11926,7 +11923,7 @@
         <v>Web</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15">
+    <row r="5" spans="1:10">
       <c r="A5" s="44" t="s">
         <v>726</v>
       </c>
@@ -11943,7 +11940,7 @@
         <v>Above the Line - Non Digital</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15">
+    <row r="6" spans="1:10">
       <c r="A6" s="44" t="s">
         <v>729</v>
       </c>
@@ -11966,7 +11963,7 @@
         <v>Social Posts</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15">
+    <row r="7" spans="1:10">
       <c r="A7" s="44" t="s">
         <v>730</v>
       </c>
@@ -11992,7 +11989,7 @@
         <v>Social Outbound Messages</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15">
+    <row r="8" spans="1:10">
       <c r="A8" s="44" t="s">
         <v>734</v>
       </c>
@@ -12015,7 +12012,7 @@
         <v>Virtual Events</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15">
+    <row r="9" spans="1:10">
       <c r="A9" s="44" t="s">
         <v>737</v>
       </c>
@@ -12035,7 +12032,7 @@
         <v>F2F Events</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15">
+    <row r="10" spans="1:10">
       <c r="A10" s="44" t="s">
         <v>738</v>
       </c>
@@ -12058,7 +12055,7 @@
         <v>Webinars</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15">
+    <row r="11" spans="1:10">
       <c r="A11" s="44" t="s">
         <v>739</v>
       </c>
@@ -12081,7 +12078,7 @@
         <v>Direct Mail</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15">
+    <row r="12" spans="1:10">
       <c r="A12" s="44" t="s">
         <v>740</v>
       </c>
@@ -12113,7 +12110,7 @@
         <v>Whatsapp</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15">
+    <row r="13" spans="1:10">
       <c r="A13" s="44" t="s">
         <v>741</v>
       </c>
@@ -12145,7 +12142,7 @@
         <v>RCS</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15">
+    <row r="14" spans="1:10">
       <c r="A14" s="44" t="s">
         <v>742</v>
       </c>
@@ -12179,7 +12176,7 @@
         <v>Email</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15">
+    <row r="15" spans="1:10">
       <c r="A15" s="44" t="s">
         <v>743</v>
       </c>
@@ -12211,7 +12208,7 @@
         <v>SMS</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15">
+    <row r="16" spans="1:10">
       <c r="A16" s="44" t="s">
         <v>744</v>
       </c>
@@ -12243,7 +12240,7 @@
         <v>MMS</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15">
+    <row r="17" spans="1:10">
       <c r="A17" s="44" t="s">
         <v>745</v>
       </c>
@@ -12266,7 +12263,7 @@
         <v>App Push Notification</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15">
+    <row r="18" spans="1:10">
       <c r="A18" s="44" t="s">
         <v>750</v>
       </c>
@@ -12286,7 +12283,7 @@
         <v>Sales Meetings</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15">
+    <row r="19" spans="1:10">
       <c r="A19" s="44" t="s">
         <v>752</v>
       </c>
@@ -12309,7 +12306,7 @@
         <v>Sales Calls</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15">
+    <row r="20" spans="1:10">
       <c r="A20" s="44" t="s">
         <v>753</v>
       </c>
@@ -12343,7 +12340,7 @@
         <v>Sales Email</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15">
+    <row r="21" spans="1:10">
       <c r="A21" s="45" t="s">
         <v>754</v>
       </c>
@@ -12365,7 +12362,7 @@
         <v>Inbound Calls</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15">
+    <row r="22" spans="1:10">
       <c r="A22" s="44" t="s">
         <v>746</v>
       </c>
@@ -12420,6 +12417,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D1F78A46A5B61544A3F5E5F9D558353B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cd5889db134979e54dcf054cdc4727ec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a7019f60-298e-442e-b6f6-687001478962" xmlns:ns3="244a3a2d-c3b8-4eaa-9334-4c3b8cbc7cc9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fdf5543a8e45e11fa247a01810ff6e7b" ns2:_="" ns3:_="">
     <xsd:import namespace="a7019f60-298e-442e-b6f6-687001478962"/>
@@ -12620,29 +12632,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{981D98BA-C602-41F7-9CF6-ADC2B2B0572D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51BB428E-D1CA-47E8-B784-F33B49A13D8D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51BB428E-D1CA-47E8-B784-F33B49A13D8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{221E8208-2559-4473-AFD3-FB4000FD0DD1}"/>
 </file>